--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -26,13 +26,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +54,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,82 +438,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D129</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D129</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -5436,92 +5448,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D123</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D123</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R3_D124</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R3_D124</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D125</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D125</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D126</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D126</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -9502,82 +9514,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -15268,82 +15280,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -21844,72 +21856,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -24570,92 +24582,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R3_D129</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R3_D129</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -33856,62 +33868,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -35108,72 +35120,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>
@@ -37834,72 +37846,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -41088,82 +41100,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D129</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D129</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -5851,40 +5851,40 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.983051</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.016949</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.983051</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.016949</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.983051</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.016949</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.983051</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.016949</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.983051</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.016949</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.983051</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.016949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6571,40 +6571,40 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.116279</v>
+        <v>0.09589</v>
       </c>
       <c r="H19" t="n">
-        <v>0.883721</v>
+        <v>0.90411</v>
       </c>
       <c r="I19" t="n">
-        <v>0.116279</v>
+        <v>0.09589</v>
       </c>
       <c r="J19" t="n">
-        <v>0.883721</v>
+        <v>0.90411</v>
       </c>
       <c r="K19" t="n">
-        <v>0.116279</v>
+        <v>0.09589</v>
       </c>
       <c r="L19" t="n">
-        <v>0.883721</v>
+        <v>0.90411</v>
       </c>
       <c r="M19" t="n">
-        <v>0.116279</v>
+        <v>0.09589</v>
       </c>
       <c r="N19" t="n">
-        <v>0.883721</v>
+        <v>0.90411</v>
       </c>
       <c r="O19" t="n">
-        <v>0.116279</v>
+        <v>0.09589</v>
       </c>
       <c r="P19" t="n">
-        <v>0.883721</v>
+        <v>0.90411</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.116279</v>
+        <v>0.09589</v>
       </c>
       <c r="R19" t="n">
-        <v>0.883721</v>
+        <v>0.90411</v>
       </c>
     </row>
     <row r="20">
@@ -6637,34 +6637,34 @@
         <v>0.561847</v>
       </c>
       <c r="I20" t="n">
-        <v>0.438153</v>
+        <v>0.411449</v>
       </c>
       <c r="J20" t="n">
-        <v>0.561847</v>
+        <v>0.588551</v>
       </c>
       <c r="K20" t="n">
-        <v>0.438153</v>
+        <v>0.411449</v>
       </c>
       <c r="L20" t="n">
-        <v>0.561847</v>
+        <v>0.588551</v>
       </c>
       <c r="M20" t="n">
-        <v>0.438153</v>
+        <v>0.411449</v>
       </c>
       <c r="N20" t="n">
-        <v>0.561847</v>
+        <v>0.588551</v>
       </c>
       <c r="O20" t="n">
-        <v>0.438153</v>
+        <v>0.411449</v>
       </c>
       <c r="P20" t="n">
-        <v>0.561847</v>
+        <v>0.588551</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.438153</v>
+        <v>0.411449</v>
       </c>
       <c r="R20" t="n">
-        <v>0.561847</v>
+        <v>0.588551</v>
       </c>
     </row>
     <row r="21">
@@ -6991,40 +6991,40 @@
         <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.714286</v>
       </c>
       <c r="H26" t="n">
-        <v>0.286916</v>
+        <v>0.285714</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.714286</v>
       </c>
       <c r="J26" t="n">
-        <v>0.286916</v>
+        <v>0.285714</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.714286</v>
       </c>
       <c r="L26" t="n">
-        <v>0.286916</v>
+        <v>0.285714</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.714286</v>
       </c>
       <c r="N26" t="n">
-        <v>0.286916</v>
+        <v>0.285714</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.714286</v>
       </c>
       <c r="P26" t="n">
-        <v>0.286916</v>
+        <v>0.285714</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.714286</v>
       </c>
       <c r="R26" t="n">
-        <v>0.286916</v>
+        <v>0.285714</v>
       </c>
     </row>
     <row r="27">
@@ -7411,40 +7411,40 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>0.714286</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.285714</v>
+        <v>0.286916</v>
       </c>
       <c r="I33" t="n">
-        <v>0.714286</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.285714</v>
+        <v>0.286916</v>
       </c>
       <c r="K33" t="n">
-        <v>0.714286</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>0.285714</v>
+        <v>0.286916</v>
       </c>
       <c r="M33" t="n">
-        <v>0.714286</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>0.285714</v>
+        <v>0.286916</v>
       </c>
       <c r="O33" t="n">
-        <v>0.714286</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="P33" t="n">
-        <v>0.285714</v>
+        <v>0.286916</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.714286</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="R33" t="n">
-        <v>0.285714</v>
+        <v>0.286916</v>
       </c>
     </row>
     <row r="34">
@@ -7471,40 +7471,40 @@
         <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>0.74026</v>
+        <v>0.721311</v>
       </c>
       <c r="H34" t="n">
-        <v>0.25974</v>
+        <v>0.278689</v>
       </c>
       <c r="I34" t="n">
-        <v>0.74026</v>
+        <v>0.721311</v>
       </c>
       <c r="J34" t="n">
-        <v>0.25974</v>
+        <v>0.278689</v>
       </c>
       <c r="K34" t="n">
-        <v>0.74026</v>
+        <v>0.721311</v>
       </c>
       <c r="L34" t="n">
-        <v>0.25974</v>
+        <v>0.278689</v>
       </c>
       <c r="M34" t="n">
-        <v>0.74026</v>
+        <v>0.721311</v>
       </c>
       <c r="N34" t="n">
-        <v>0.25974</v>
+        <v>0.278689</v>
       </c>
       <c r="O34" t="n">
-        <v>0.74026</v>
+        <v>0.721311</v>
       </c>
       <c r="P34" t="n">
-        <v>0.25974</v>
+        <v>0.278689</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.74026</v>
+        <v>0.721311</v>
       </c>
       <c r="R34" t="n">
-        <v>0.25974</v>
+        <v>0.278689</v>
       </c>
     </row>
     <row r="35">
@@ -7837,34 +7837,34 @@
         <v>0.588551</v>
       </c>
       <c r="I40" t="n">
-        <v>0.411449</v>
+        <v>0.366834</v>
       </c>
       <c r="J40" t="n">
-        <v>0.588551</v>
+        <v>0.633166</v>
       </c>
       <c r="K40" t="n">
-        <v>0.411449</v>
+        <v>0.366834</v>
       </c>
       <c r="L40" t="n">
-        <v>0.588551</v>
+        <v>0.633166</v>
       </c>
       <c r="M40" t="n">
-        <v>0.411449</v>
+        <v>0.366834</v>
       </c>
       <c r="N40" t="n">
-        <v>0.588551</v>
+        <v>0.633166</v>
       </c>
       <c r="O40" t="n">
-        <v>0.411449</v>
+        <v>0.366834</v>
       </c>
       <c r="P40" t="n">
-        <v>0.588551</v>
+        <v>0.633166</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.411449</v>
+        <v>0.366834</v>
       </c>
       <c r="R40" t="n">
-        <v>0.588551</v>
+        <v>0.633166</v>
       </c>
     </row>
     <row r="41">
@@ -7891,40 +7891,40 @@
         <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>0.447458</v>
+        <v>0.438153</v>
       </c>
       <c r="H41" t="n">
-        <v>0.552542</v>
+        <v>0.561847</v>
       </c>
       <c r="I41" t="n">
-        <v>0.447458</v>
+        <v>0.438153</v>
       </c>
       <c r="J41" t="n">
-        <v>0.552542</v>
+        <v>0.561847</v>
       </c>
       <c r="K41" t="n">
-        <v>0.447458</v>
+        <v>0.438153</v>
       </c>
       <c r="L41" t="n">
-        <v>0.552542</v>
+        <v>0.561847</v>
       </c>
       <c r="M41" t="n">
-        <v>0.447458</v>
+        <v>0.438153</v>
       </c>
       <c r="N41" t="n">
-        <v>0.552542</v>
+        <v>0.561847</v>
       </c>
       <c r="O41" t="n">
-        <v>0.447458</v>
+        <v>0.438153</v>
       </c>
       <c r="P41" t="n">
-        <v>0.552542</v>
+        <v>0.561847</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.447458</v>
+        <v>0.438153</v>
       </c>
       <c r="R41" t="n">
-        <v>0.552542</v>
+        <v>0.561847</v>
       </c>
     </row>
     <row r="42">
@@ -8191,40 +8191,40 @@
         <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>0.262146</v>
+        <v>0.187907</v>
       </c>
       <c r="H46" t="n">
-        <v>0.737854</v>
+        <v>0.812093</v>
       </c>
       <c r="I46" t="n">
-        <v>0.262146</v>
+        <v>0.187907</v>
       </c>
       <c r="J46" t="n">
-        <v>0.737854</v>
+        <v>0.812093</v>
       </c>
       <c r="K46" t="n">
-        <v>0.262146</v>
+        <v>0.187907</v>
       </c>
       <c r="L46" t="n">
-        <v>0.737854</v>
+        <v>0.812093</v>
       </c>
       <c r="M46" t="n">
-        <v>0.262146</v>
+        <v>0.187907</v>
       </c>
       <c r="N46" t="n">
-        <v>0.737854</v>
+        <v>0.812093</v>
       </c>
       <c r="O46" t="n">
-        <v>0.262146</v>
+        <v>0.187907</v>
       </c>
       <c r="P46" t="n">
-        <v>0.737854</v>
+        <v>0.812093</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.262146</v>
+        <v>0.187907</v>
       </c>
       <c r="R46" t="n">
-        <v>0.737854</v>
+        <v>0.812093</v>
       </c>
     </row>
     <row r="47">
@@ -24865,40 +24865,40 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.366834</v>
+        <v>0.411449</v>
       </c>
       <c r="H5" t="n">
-        <v>0.633166</v>
+        <v>0.588551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.366834</v>
+        <v>0.411449</v>
       </c>
       <c r="J5" t="n">
-        <v>0.633166</v>
+        <v>0.588551</v>
       </c>
       <c r="K5" t="n">
-        <v>0.366834</v>
+        <v>0.411449</v>
       </c>
       <c r="L5" t="n">
-        <v>0.633166</v>
+        <v>0.588551</v>
       </c>
       <c r="M5" t="n">
-        <v>0.366834</v>
+        <v>0.411449</v>
       </c>
       <c r="N5" t="n">
-        <v>0.633166</v>
+        <v>0.588551</v>
       </c>
       <c r="O5" t="n">
-        <v>0.366834</v>
+        <v>0.411449</v>
       </c>
       <c r="P5" t="n">
-        <v>0.633166</v>
+        <v>0.588551</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.366834</v>
+        <v>0.411449</v>
       </c>
       <c r="R5" t="n">
-        <v>0.633166</v>
+        <v>0.588551</v>
       </c>
     </row>
     <row r="6">
@@ -24925,40 +24925,40 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5580580000000001</v>
+        <v>0.522414</v>
       </c>
       <c r="H6" t="n">
-        <v>0.441942</v>
+        <v>0.477586</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5580580000000001</v>
+        <v>0.522414</v>
       </c>
       <c r="J6" t="n">
-        <v>0.441942</v>
+        <v>0.477586</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5580580000000001</v>
+        <v>0.522414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.441942</v>
+        <v>0.477586</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5580580000000001</v>
+        <v>0.522414</v>
       </c>
       <c r="N6" t="n">
-        <v>0.441942</v>
+        <v>0.477586</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5580580000000001</v>
+        <v>0.522414</v>
       </c>
       <c r="P6" t="n">
-        <v>0.441942</v>
+        <v>0.477586</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5580580000000001</v>
+        <v>0.522414</v>
       </c>
       <c r="R6" t="n">
-        <v>0.441942</v>
+        <v>0.477586</v>
       </c>
     </row>
     <row r="7">
@@ -25405,40 +25405,40 @@
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.941176</v>
+        <v>0.961977</v>
       </c>
       <c r="H14" t="n">
-        <v>0.058824</v>
+        <v>0.038023</v>
       </c>
       <c r="I14" t="n">
-        <v>0.941176</v>
+        <v>0.961977</v>
       </c>
       <c r="J14" t="n">
-        <v>0.058824</v>
+        <v>0.038023</v>
       </c>
       <c r="K14" t="n">
-        <v>0.941176</v>
+        <v>0.961977</v>
       </c>
       <c r="L14" t="n">
-        <v>0.058824</v>
+        <v>0.038023</v>
       </c>
       <c r="M14" t="n">
-        <v>0.941176</v>
+        <v>0.961977</v>
       </c>
       <c r="N14" t="n">
-        <v>0.058824</v>
+        <v>0.038023</v>
       </c>
       <c r="O14" t="n">
-        <v>0.941176</v>
+        <v>0.961977</v>
       </c>
       <c r="P14" t="n">
-        <v>0.058824</v>
+        <v>0.038023</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.941176</v>
+        <v>0.961977</v>
       </c>
       <c r="R14" t="n">
-        <v>0.058824</v>
+        <v>0.038023</v>
       </c>
     </row>
     <row r="15">
@@ -25825,40 +25825,40 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.09589</v>
+        <v>0.149893</v>
       </c>
       <c r="H21" t="n">
-        <v>0.90411</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09589</v>
+        <v>0.149893</v>
       </c>
       <c r="J21" t="n">
-        <v>0.90411</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09589</v>
+        <v>0.149893</v>
       </c>
       <c r="L21" t="n">
-        <v>0.90411</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.09589</v>
+        <v>0.149893</v>
       </c>
       <c r="N21" t="n">
-        <v>0.90411</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.09589</v>
+        <v>0.149893</v>
       </c>
       <c r="P21" t="n">
-        <v>0.90411</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.09589</v>
+        <v>0.149893</v>
       </c>
       <c r="R21" t="n">
-        <v>0.90411</v>
+        <v>0.8501069999999999</v>
       </c>
     </row>
     <row r="22">
@@ -26365,40 +26365,40 @@
         <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="H30" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="I30" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="J30" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="K30" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="L30" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="M30" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="N30" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="O30" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="P30" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="R30" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
     </row>
     <row r="31">
@@ -26665,40 +26665,40 @@
         <v>17</v>
       </c>
       <c r="G35" t="n">
-        <v>0.817308</v>
+        <v>0.858156</v>
       </c>
       <c r="H35" t="n">
-        <v>0.182692</v>
+        <v>0.141844</v>
       </c>
       <c r="I35" t="n">
-        <v>0.817308</v>
+        <v>0.858156</v>
       </c>
       <c r="J35" t="n">
-        <v>0.182692</v>
+        <v>0.141844</v>
       </c>
       <c r="K35" t="n">
-        <v>0.817308</v>
+        <v>0.858156</v>
       </c>
       <c r="L35" t="n">
-        <v>0.182692</v>
+        <v>0.141844</v>
       </c>
       <c r="M35" t="n">
-        <v>0.817308</v>
+        <v>0.858156</v>
       </c>
       <c r="N35" t="n">
-        <v>0.182692</v>
+        <v>0.141844</v>
       </c>
       <c r="O35" t="n">
-        <v>0.817308</v>
+        <v>0.858156</v>
       </c>
       <c r="P35" t="n">
-        <v>0.182692</v>
+        <v>0.141844</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.817308</v>
+        <v>0.858156</v>
       </c>
       <c r="R35" t="n">
-        <v>0.182692</v>
+        <v>0.141844</v>
       </c>
     </row>
     <row r="36">
@@ -26725,40 +26725,40 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.187907</v>
+        <v>0.262146</v>
       </c>
       <c r="H36" t="n">
-        <v>0.812093</v>
+        <v>0.737854</v>
       </c>
       <c r="I36" t="n">
-        <v>0.187907</v>
+        <v>0.262146</v>
       </c>
       <c r="J36" t="n">
-        <v>0.812093</v>
+        <v>0.737854</v>
       </c>
       <c r="K36" t="n">
-        <v>0.187907</v>
+        <v>0.262146</v>
       </c>
       <c r="L36" t="n">
-        <v>0.812093</v>
+        <v>0.737854</v>
       </c>
       <c r="M36" t="n">
-        <v>0.187907</v>
+        <v>0.262146</v>
       </c>
       <c r="N36" t="n">
-        <v>0.812093</v>
+        <v>0.737854</v>
       </c>
       <c r="O36" t="n">
-        <v>0.187907</v>
+        <v>0.262146</v>
       </c>
       <c r="P36" t="n">
-        <v>0.812093</v>
+        <v>0.737854</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.187907</v>
+        <v>0.262146</v>
       </c>
       <c r="R36" t="n">
-        <v>0.812093</v>
+        <v>0.737854</v>
       </c>
     </row>
     <row r="37">
@@ -26905,40 +26905,40 @@
         <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>0.466825</v>
+        <v>0.475325</v>
       </c>
       <c r="H39" t="n">
-        <v>0.533175</v>
+        <v>0.524675</v>
       </c>
       <c r="I39" t="n">
-        <v>0.466825</v>
+        <v>0.475325</v>
       </c>
       <c r="J39" t="n">
-        <v>0.533175</v>
+        <v>0.524675</v>
       </c>
       <c r="K39" t="n">
-        <v>0.466825</v>
+        <v>0.475325</v>
       </c>
       <c r="L39" t="n">
-        <v>0.533175</v>
+        <v>0.524675</v>
       </c>
       <c r="M39" t="n">
-        <v>0.466825</v>
+        <v>0.475325</v>
       </c>
       <c r="N39" t="n">
-        <v>0.533175</v>
+        <v>0.524675</v>
       </c>
       <c r="O39" t="n">
-        <v>0.466825</v>
+        <v>0.475325</v>
       </c>
       <c r="P39" t="n">
-        <v>0.533175</v>
+        <v>0.524675</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.466825</v>
+        <v>0.475325</v>
       </c>
       <c r="R39" t="n">
-        <v>0.533175</v>
+        <v>0.524675</v>
       </c>
     </row>
     <row r="40">
@@ -27565,40 +27565,40 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.066667</v>
+        <v>0.07033</v>
       </c>
       <c r="H50" t="n">
-        <v>0.933333</v>
+        <v>0.92967</v>
       </c>
       <c r="I50" t="n">
-        <v>0.066667</v>
+        <v>0.07033</v>
       </c>
       <c r="J50" t="n">
-        <v>0.933333</v>
+        <v>0.92967</v>
       </c>
       <c r="K50" t="n">
-        <v>0.066667</v>
+        <v>0.07033</v>
       </c>
       <c r="L50" t="n">
-        <v>0.933333</v>
+        <v>0.92967</v>
       </c>
       <c r="M50" t="n">
-        <v>0.066667</v>
+        <v>0.07033</v>
       </c>
       <c r="N50" t="n">
-        <v>0.933333</v>
+        <v>0.92967</v>
       </c>
       <c r="O50" t="n">
-        <v>0.066667</v>
+        <v>0.07033</v>
       </c>
       <c r="P50" t="n">
-        <v>0.933333</v>
+        <v>0.92967</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.066667</v>
+        <v>0.07033</v>
       </c>
       <c r="R50" t="n">
-        <v>0.933333</v>
+        <v>0.92967</v>
       </c>
     </row>
     <row r="51">
@@ -28405,40 +28405,40 @@
         <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>0.559322</v>
+        <v>0.636015</v>
       </c>
       <c r="H64" t="n">
-        <v>0.440678</v>
+        <v>0.363985</v>
       </c>
       <c r="I64" t="n">
-        <v>0.559322</v>
+        <v>0.636015</v>
       </c>
       <c r="J64" t="n">
-        <v>0.440678</v>
+        <v>0.363985</v>
       </c>
       <c r="K64" t="n">
-        <v>0.559322</v>
+        <v>0.636015</v>
       </c>
       <c r="L64" t="n">
-        <v>0.440678</v>
+        <v>0.363985</v>
       </c>
       <c r="M64" t="n">
-        <v>0.559322</v>
+        <v>0.636015</v>
       </c>
       <c r="N64" t="n">
-        <v>0.440678</v>
+        <v>0.363985</v>
       </c>
       <c r="O64" t="n">
-        <v>0.559322</v>
+        <v>0.636015</v>
       </c>
       <c r="P64" t="n">
-        <v>0.440678</v>
+        <v>0.363985</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.559322</v>
+        <v>0.636015</v>
       </c>
       <c r="R64" t="n">
-        <v>0.440678</v>
+        <v>0.363985</v>
       </c>
     </row>
     <row r="65">
@@ -28585,40 +28585,40 @@
         <v>15</v>
       </c>
       <c r="G67" t="n">
-        <v>0.896124</v>
+        <v>0.876457</v>
       </c>
       <c r="H67" t="n">
-        <v>0.103876</v>
+        <v>0.123543</v>
       </c>
       <c r="I67" t="n">
-        <v>0.896124</v>
+        <v>0.876457</v>
       </c>
       <c r="J67" t="n">
-        <v>0.103876</v>
+        <v>0.123543</v>
       </c>
       <c r="K67" t="n">
-        <v>0.896124</v>
+        <v>0.876457</v>
       </c>
       <c r="L67" t="n">
-        <v>0.103876</v>
+        <v>0.123543</v>
       </c>
       <c r="M67" t="n">
-        <v>0.896124</v>
+        <v>0.876457</v>
       </c>
       <c r="N67" t="n">
-        <v>0.103876</v>
+        <v>0.123543</v>
       </c>
       <c r="O67" t="n">
-        <v>0.896124</v>
+        <v>0.876457</v>
       </c>
       <c r="P67" t="n">
-        <v>0.103876</v>
+        <v>0.123543</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.896124</v>
+        <v>0.876457</v>
       </c>
       <c r="R67" t="n">
-        <v>0.103876</v>
+        <v>0.123543</v>
       </c>
     </row>
     <row r="68">
@@ -28645,40 +28645,40 @@
         <v>8</v>
       </c>
       <c r="G68" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="H68" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="I68" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="J68" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="K68" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="L68" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="M68" t="n">
-        <v>0.807065</v>
+        <v>0.802632</v>
       </c>
       <c r="N68" t="n">
-        <v>0.192935</v>
+        <v>0.197368</v>
       </c>
       <c r="O68" t="n">
-        <v>0.807065</v>
+        <v>0.802632</v>
       </c>
       <c r="P68" t="n">
-        <v>0.192935</v>
+        <v>0.197368</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.807065</v>
+        <v>0.802632</v>
       </c>
       <c r="R68" t="n">
-        <v>0.192935</v>
+        <v>0.197368</v>
       </c>
     </row>
     <row r="69">
@@ -28765,40 +28765,40 @@
         <v>18</v>
       </c>
       <c r="G70" t="n">
-        <v>0.941176</v>
+        <v>0.9375</v>
       </c>
       <c r="H70" t="n">
-        <v>0.058824</v>
+        <v>0.0625</v>
       </c>
       <c r="I70" t="n">
-        <v>0.941176</v>
+        <v>0.9375</v>
       </c>
       <c r="J70" t="n">
-        <v>0.058824</v>
+        <v>0.0625</v>
       </c>
       <c r="K70" t="n">
-        <v>0.941176</v>
+        <v>0.9375</v>
       </c>
       <c r="L70" t="n">
-        <v>0.058824</v>
+        <v>0.0625</v>
       </c>
       <c r="M70" t="n">
-        <v>0.941176</v>
+        <v>0.9375</v>
       </c>
       <c r="N70" t="n">
-        <v>0.058824</v>
+        <v>0.0625</v>
       </c>
       <c r="O70" t="n">
-        <v>0.941176</v>
+        <v>0.9375</v>
       </c>
       <c r="P70" t="n">
-        <v>0.058824</v>
+        <v>0.0625</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.941176</v>
+        <v>0.9375</v>
       </c>
       <c r="R70" t="n">
-        <v>0.058824</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="71">
@@ -28885,40 +28885,40 @@
         <v>14</v>
       </c>
       <c r="G72" t="n">
-        <v>0.961977</v>
+        <v>0.9375</v>
       </c>
       <c r="H72" t="n">
-        <v>0.038023</v>
+        <v>0.0625</v>
       </c>
       <c r="I72" t="n">
-        <v>0.961977</v>
+        <v>0.9375</v>
       </c>
       <c r="J72" t="n">
-        <v>0.038023</v>
+        <v>0.0625</v>
       </c>
       <c r="K72" t="n">
-        <v>0.961977</v>
+        <v>0.9375</v>
       </c>
       <c r="L72" t="n">
-        <v>0.038023</v>
+        <v>0.0625</v>
       </c>
       <c r="M72" t="n">
-        <v>0.961977</v>
+        <v>0.9375</v>
       </c>
       <c r="N72" t="n">
-        <v>0.038023</v>
+        <v>0.0625</v>
       </c>
       <c r="O72" t="n">
-        <v>0.961977</v>
+        <v>0.9375</v>
       </c>
       <c r="P72" t="n">
-        <v>0.038023</v>
+        <v>0.0625</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.961977</v>
+        <v>0.9375</v>
       </c>
       <c r="R72" t="n">
-        <v>0.038023</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="73">
@@ -28945,40 +28945,40 @@
         <v>7</v>
       </c>
       <c r="G73" t="n">
-        <v>0.807065</v>
+        <v>0.802632</v>
       </c>
       <c r="H73" t="n">
-        <v>0.192935</v>
+        <v>0.197368</v>
       </c>
       <c r="I73" t="n">
-        <v>0.807065</v>
+        <v>0.802632</v>
       </c>
       <c r="J73" t="n">
-        <v>0.192935</v>
+        <v>0.197368</v>
       </c>
       <c r="K73" t="n">
-        <v>0.807065</v>
+        <v>0.802632</v>
       </c>
       <c r="L73" t="n">
-        <v>0.192935</v>
+        <v>0.197368</v>
       </c>
       <c r="M73" t="n">
-        <v>0.804795</v>
+        <v>0.802632</v>
       </c>
       <c r="N73" t="n">
-        <v>0.195205</v>
+        <v>0.197368</v>
       </c>
       <c r="O73" t="n">
-        <v>0.804795</v>
+        <v>0.802632</v>
       </c>
       <c r="P73" t="n">
-        <v>0.195205</v>
+        <v>0.197368</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.804795</v>
+        <v>0.802632</v>
       </c>
       <c r="R73" t="n">
-        <v>0.195205</v>
+        <v>0.197368</v>
       </c>
     </row>
     <row r="74">
@@ -29065,40 +29065,40 @@
         <v>11</v>
       </c>
       <c r="G75" t="n">
-        <v>0.876457</v>
+        <v>0.8323700000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>0.123543</v>
+        <v>0.16763</v>
       </c>
       <c r="I75" t="n">
-        <v>0.876457</v>
+        <v>0.8323700000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>0.123543</v>
+        <v>0.16763</v>
       </c>
       <c r="K75" t="n">
-        <v>0.876457</v>
+        <v>0.8323700000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>0.123543</v>
+        <v>0.16763</v>
       </c>
       <c r="M75" t="n">
-        <v>0.876457</v>
+        <v>0.8323700000000001</v>
       </c>
       <c r="N75" t="n">
-        <v>0.123543</v>
+        <v>0.16763</v>
       </c>
       <c r="O75" t="n">
-        <v>0.876457</v>
+        <v>0.8323700000000001</v>
       </c>
       <c r="P75" t="n">
-        <v>0.123543</v>
+        <v>0.16763</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.876457</v>
+        <v>0.8323700000000001</v>
       </c>
       <c r="R75" t="n">
-        <v>0.123543</v>
+        <v>0.16763</v>
       </c>
     </row>
     <row r="76">
@@ -29245,40 +29245,40 @@
         <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>0.606481</v>
+        <v>0.636015</v>
       </c>
       <c r="H78" t="n">
-        <v>0.393519</v>
+        <v>0.363985</v>
       </c>
       <c r="I78" t="n">
-        <v>0.606481</v>
+        <v>0.636015</v>
       </c>
       <c r="J78" t="n">
-        <v>0.393519</v>
+        <v>0.363985</v>
       </c>
       <c r="K78" t="n">
-        <v>0.606481</v>
+        <v>0.636015</v>
       </c>
       <c r="L78" t="n">
-        <v>0.393519</v>
+        <v>0.363985</v>
       </c>
       <c r="M78" t="n">
-        <v>0.606481</v>
+        <v>0.636015</v>
       </c>
       <c r="N78" t="n">
-        <v>0.393519</v>
+        <v>0.363985</v>
       </c>
       <c r="O78" t="n">
-        <v>0.606481</v>
+        <v>0.636015</v>
       </c>
       <c r="P78" t="n">
-        <v>0.393519</v>
+        <v>0.363985</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.606481</v>
+        <v>0.636015</v>
       </c>
       <c r="R78" t="n">
-        <v>0.393519</v>
+        <v>0.363985</v>
       </c>
     </row>
     <row r="79">
@@ -29425,40 +29425,40 @@
         <v>16</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8323700000000001</v>
+        <v>0.858156</v>
       </c>
       <c r="H81" t="n">
-        <v>0.16763</v>
+        <v>0.141844</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8323700000000001</v>
+        <v>0.858156</v>
       </c>
       <c r="J81" t="n">
-        <v>0.16763</v>
+        <v>0.141844</v>
       </c>
       <c r="K81" t="n">
-        <v>0.8323700000000001</v>
+        <v>0.858156</v>
       </c>
       <c r="L81" t="n">
-        <v>0.16763</v>
+        <v>0.141844</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8323700000000001</v>
+        <v>0.858156</v>
       </c>
       <c r="N81" t="n">
-        <v>0.16763</v>
+        <v>0.141844</v>
       </c>
       <c r="O81" t="n">
-        <v>0.8323700000000001</v>
+        <v>0.858156</v>
       </c>
       <c r="P81" t="n">
-        <v>0.16763</v>
+        <v>0.141844</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.8323700000000001</v>
+        <v>0.858156</v>
       </c>
       <c r="R81" t="n">
-        <v>0.16763</v>
+        <v>0.141844</v>
       </c>
     </row>
     <row r="82">
@@ -29545,40 +29545,40 @@
         <v>5</v>
       </c>
       <c r="G83" t="n">
-        <v>0.438153</v>
+        <v>0.447458</v>
       </c>
       <c r="H83" t="n">
-        <v>0.561847</v>
+        <v>0.552542</v>
       </c>
       <c r="I83" t="n">
-        <v>0.438153</v>
+        <v>0.447458</v>
       </c>
       <c r="J83" t="n">
-        <v>0.561847</v>
+        <v>0.552542</v>
       </c>
       <c r="K83" t="n">
-        <v>0.438153</v>
+        <v>0.447458</v>
       </c>
       <c r="L83" t="n">
-        <v>0.561847</v>
+        <v>0.552542</v>
       </c>
       <c r="M83" t="n">
-        <v>0.438153</v>
+        <v>0.447458</v>
       </c>
       <c r="N83" t="n">
-        <v>0.561847</v>
+        <v>0.552542</v>
       </c>
       <c r="O83" t="n">
-        <v>0.438153</v>
+        <v>0.447458</v>
       </c>
       <c r="P83" t="n">
-        <v>0.561847</v>
+        <v>0.552542</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.438153</v>
+        <v>0.447458</v>
       </c>
       <c r="R83" t="n">
-        <v>0.561847</v>
+        <v>0.552542</v>
       </c>
     </row>
     <row r="84">
@@ -29785,40 +29785,40 @@
         <v>11</v>
       </c>
       <c r="G87" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="H87" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="I87" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="J87" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="K87" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="L87" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="M87" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="N87" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="O87" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="P87" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.807065</v>
+        <v>0.804795</v>
       </c>
       <c r="R87" t="n">
-        <v>0.192935</v>
+        <v>0.195205</v>
       </c>
     </row>
     <row r="88">
@@ -32305,40 +32305,40 @@
         <v>14</v>
       </c>
       <c r="G129" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.6851390000000001</v>
       </c>
       <c r="H129" t="n">
-        <v>0.286916</v>
+        <v>0.314861</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.6851390000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>0.286916</v>
+        <v>0.314861</v>
       </c>
       <c r="K129" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.6851390000000001</v>
       </c>
       <c r="L129" t="n">
-        <v>0.286916</v>
+        <v>0.314861</v>
       </c>
       <c r="M129" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.6851390000000001</v>
       </c>
       <c r="N129" t="n">
-        <v>0.286916</v>
+        <v>0.314861</v>
       </c>
       <c r="O129" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.6851390000000001</v>
       </c>
       <c r="P129" t="n">
-        <v>0.286916</v>
+        <v>0.314861</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.7130840000000001</v>
+        <v>0.6851390000000001</v>
       </c>
       <c r="R129" t="n">
-        <v>0.286916</v>
+        <v>0.314861</v>
       </c>
     </row>
     <row r="130">
@@ -33403,22 +33403,22 @@
         <v>0.696262</v>
       </c>
       <c r="M147" t="n">
-        <v>0.303738</v>
+        <v>0.3</v>
       </c>
       <c r="N147" t="n">
-        <v>0.696262</v>
+        <v>0.7</v>
       </c>
       <c r="O147" t="n">
-        <v>0.303738</v>
+        <v>0.3</v>
       </c>
       <c r="P147" t="n">
-        <v>0.696262</v>
+        <v>0.7</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.303738</v>
+        <v>0.3</v>
       </c>
       <c r="R147" t="n">
-        <v>0.696262</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="148">
@@ -35683,28 +35683,28 @@
         <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.766575</v>
+        <v>0.714286</v>
       </c>
       <c r="H12" t="n">
-        <v>0.233425</v>
+        <v>0.285714</v>
       </c>
       <c r="I12" t="n">
-        <v>0.766575</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.233425</v>
+        <v>0.286916</v>
       </c>
       <c r="K12" t="n">
-        <v>0.766575</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.233425</v>
+        <v>0.286916</v>
       </c>
       <c r="M12" t="n">
-        <v>0.766575</v>
+        <v>0.7130840000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.233425</v>
+        <v>0.286916</v>
       </c>
     </row>
     <row r="13">
@@ -36169,22 +36169,22 @@
         <v>0.696262</v>
       </c>
       <c r="I22" t="n">
-        <v>0.303738</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0.696262</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.303738</v>
+        <v>0.3</v>
       </c>
       <c r="L22" t="n">
-        <v>0.696262</v>
+        <v>0.7</v>
       </c>
       <c r="M22" t="n">
-        <v>0.303738</v>
+        <v>0.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.696262</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="23">
@@ -36259,28 +36259,28 @@
         <v>10</v>
       </c>
       <c r="G24" t="n">
+        <v>0.5580580000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.441942</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.5496180000000001</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.450382</v>
       </c>
-      <c r="I24" t="n">
-        <v>0.545455</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.454545</v>
-      </c>
       <c r="K24" t="n">
-        <v>0.545455</v>
+        <v>0.5496180000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.454545</v>
+        <v>0.450382</v>
       </c>
       <c r="M24" t="n">
-        <v>0.545455</v>
+        <v>0.5496180000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>0.454545</v>
+        <v>0.450382</v>
       </c>
     </row>
     <row r="25">
@@ -36307,28 +36307,28 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.276386</v>
+        <v>0.303738</v>
       </c>
       <c r="H25" t="n">
-        <v>0.723614</v>
+        <v>0.696262</v>
       </c>
       <c r="I25" t="n">
-        <v>0.276386</v>
+        <v>0.303738</v>
       </c>
       <c r="J25" t="n">
-        <v>0.723614</v>
+        <v>0.696262</v>
       </c>
       <c r="K25" t="n">
-        <v>0.276386</v>
+        <v>0.303738</v>
       </c>
       <c r="L25" t="n">
-        <v>0.723614</v>
+        <v>0.696262</v>
       </c>
       <c r="M25" t="n">
-        <v>0.276386</v>
+        <v>0.303738</v>
       </c>
       <c r="N25" t="n">
-        <v>0.723614</v>
+        <v>0.696262</v>
       </c>
     </row>
     <row r="26">
@@ -36403,28 +36403,28 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.303738</v>
+        <v>0.313131</v>
       </c>
       <c r="H27" t="n">
-        <v>0.696262</v>
+        <v>0.686869</v>
       </c>
       <c r="I27" t="n">
-        <v>0.303738</v>
+        <v>0.313131</v>
       </c>
       <c r="J27" t="n">
-        <v>0.696262</v>
+        <v>0.686869</v>
       </c>
       <c r="K27" t="n">
-        <v>0.303738</v>
+        <v>0.313131</v>
       </c>
       <c r="L27" t="n">
-        <v>0.696262</v>
+        <v>0.686869</v>
       </c>
       <c r="M27" t="n">
-        <v>0.303738</v>
+        <v>0.313131</v>
       </c>
       <c r="N27" t="n">
-        <v>0.696262</v>
+        <v>0.686869</v>
       </c>
     </row>
     <row r="28">
@@ -36451,28 +36451,28 @@
         <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.36067</v>
+        <v>0.366834</v>
       </c>
       <c r="H28" t="n">
-        <v>0.63933</v>
+        <v>0.633166</v>
       </c>
       <c r="I28" t="n">
-        <v>0.36067</v>
+        <v>0.366834</v>
       </c>
       <c r="J28" t="n">
-        <v>0.63933</v>
+        <v>0.633166</v>
       </c>
       <c r="K28" t="n">
-        <v>0.36067</v>
+        <v>0.366834</v>
       </c>
       <c r="L28" t="n">
-        <v>0.63933</v>
+        <v>0.633166</v>
       </c>
       <c r="M28" t="n">
-        <v>0.36067</v>
+        <v>0.366834</v>
       </c>
       <c r="N28" t="n">
-        <v>0.63933</v>
+        <v>0.633166</v>
       </c>
     </row>
     <row r="29">
@@ -36499,28 +36499,28 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.116279</v>
+        <v>0.149893</v>
       </c>
       <c r="H29" t="n">
-        <v>0.883721</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.116279</v>
+        <v>0.149893</v>
       </c>
       <c r="J29" t="n">
-        <v>0.883721</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.116279</v>
+        <v>0.149893</v>
       </c>
       <c r="L29" t="n">
-        <v>0.883721</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>0.116279</v>
+        <v>0.149893</v>
       </c>
       <c r="N29" t="n">
-        <v>0.883721</v>
+        <v>0.8501069999999999</v>
       </c>
     </row>
     <row r="30">
@@ -37123,28 +37123,28 @@
         <v>10</v>
       </c>
       <c r="G42" t="n">
-        <v>0.804795</v>
+        <v>0.807065</v>
       </c>
       <c r="H42" t="n">
-        <v>0.195205</v>
+        <v>0.192935</v>
       </c>
       <c r="I42" t="n">
-        <v>0.804795</v>
+        <v>0.807065</v>
       </c>
       <c r="J42" t="n">
-        <v>0.195205</v>
+        <v>0.192935</v>
       </c>
       <c r="K42" t="n">
-        <v>0.804795</v>
+        <v>0.807065</v>
       </c>
       <c r="L42" t="n">
-        <v>0.195205</v>
+        <v>0.192935</v>
       </c>
       <c r="M42" t="n">
-        <v>0.804795</v>
+        <v>0.807065</v>
       </c>
       <c r="N42" t="n">
-        <v>0.195205</v>
+        <v>0.192935</v>
       </c>
     </row>
     <row r="43">
@@ -37417,22 +37417,22 @@
         <v>0.737854</v>
       </c>
       <c r="I48" t="n">
-        <v>0.225</v>
+        <v>0.262146</v>
       </c>
       <c r="J48" t="n">
-        <v>0.775</v>
+        <v>0.737854</v>
       </c>
       <c r="K48" t="n">
-        <v>0.225</v>
+        <v>0.262146</v>
       </c>
       <c r="L48" t="n">
-        <v>0.775</v>
+        <v>0.737854</v>
       </c>
       <c r="M48" t="n">
-        <v>0.225</v>
+        <v>0.262146</v>
       </c>
       <c r="N48" t="n">
-        <v>0.775</v>
+        <v>0.737854</v>
       </c>
     </row>
     <row r="49">
@@ -37459,10 +37459,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.297668</v>
+        <v>0.276386</v>
       </c>
       <c r="H49" t="n">
-        <v>0.702332</v>
+        <v>0.723614</v>
       </c>
       <c r="I49" t="n">
         <v>0.276386</v>
@@ -37651,28 +37651,28 @@
         <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>0.64191</v>
+        <v>0.636015</v>
       </c>
       <c r="H53" t="n">
-        <v>0.35809</v>
+        <v>0.363985</v>
       </c>
       <c r="I53" t="n">
-        <v>0.64191</v>
+        <v>0.636015</v>
       </c>
       <c r="J53" t="n">
-        <v>0.35809</v>
+        <v>0.363985</v>
       </c>
       <c r="K53" t="n">
-        <v>0.64191</v>
+        <v>0.636015</v>
       </c>
       <c r="L53" t="n">
-        <v>0.35809</v>
+        <v>0.363985</v>
       </c>
       <c r="M53" t="n">
-        <v>0.64191</v>
+        <v>0.636015</v>
       </c>
       <c r="N53" t="n">
-        <v>0.35809</v>
+        <v>0.363985</v>
       </c>
     </row>
     <row r="54">
@@ -37699,28 +37699,28 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6851390000000001</v>
+        <v>0.64191</v>
       </c>
       <c r="H54" t="n">
-        <v>0.314861</v>
+        <v>0.35809</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6851390000000001</v>
+        <v>0.64191</v>
       </c>
       <c r="J54" t="n">
-        <v>0.314861</v>
+        <v>0.35809</v>
       </c>
       <c r="K54" t="n">
-        <v>0.6851390000000001</v>
+        <v>0.64191</v>
       </c>
       <c r="L54" t="n">
-        <v>0.314861</v>
+        <v>0.35809</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6851390000000001</v>
+        <v>0.64191</v>
       </c>
       <c r="N54" t="n">
-        <v>0.314861</v>
+        <v>0.35809</v>
       </c>
     </row>
     <row r="55">

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -1186,34 +1186,34 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="H14" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="J14" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="L14" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="N14" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.243295</v>
+        <v>0.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0.756705</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15">
@@ -1240,34 +1240,34 @@
         <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="I15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="K15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="M15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="O15" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="16">
@@ -1402,34 +1402,34 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H18" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I18" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J18" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K18" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="L18" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="M18" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="N18" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="O18" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="P18" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="19">
@@ -1618,34 +1618,34 @@
         <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="23">
@@ -1726,10 +1726,10 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I24" t="n">
         <v>0.6787069999999999</v>
@@ -1780,34 +1780,34 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="26">
@@ -3886,16 +3886,16 @@
         <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>0.262122</v>
+        <v>0.260417</v>
       </c>
       <c r="H64" t="n">
-        <v>0.737878</v>
+        <v>0.739583</v>
       </c>
       <c r="I64" t="n">
-        <v>0.262122</v>
+        <v>0.260417</v>
       </c>
       <c r="J64" t="n">
-        <v>0.737878</v>
+        <v>0.739583</v>
       </c>
       <c r="K64" t="n">
         <v>0.260417</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="I2" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="K2" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="3">
@@ -5570,16 +5570,16 @@
         <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.882667</v>
+        <v>0.913043</v>
       </c>
       <c r="H3" t="n">
-        <v>0.117333</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.882667</v>
+        <v>0.913043</v>
       </c>
       <c r="J3" t="n">
-        <v>0.117333</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.882667</v>
@@ -5624,10 +5624,10 @@
         <v>0.19214</v>
       </c>
       <c r="K4" t="n">
-        <v>0.803419</v>
+        <v>0.80786</v>
       </c>
       <c r="L4" t="n">
-        <v>0.196581</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="5">
@@ -5696,22 +5696,22 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="H6" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="I6" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="J6" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="K6" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="7">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0.882667</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>1138</v>
@@ -5850,7 +5850,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>1245</v>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>1269</v>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>1275</v>
@@ -5948,22 +5948,22 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.263158</v>
+        <v>0.243295</v>
       </c>
       <c r="H12" t="n">
-        <v>0.736842</v>
+        <v>0.756705</v>
       </c>
       <c r="I12" t="n">
-        <v>0.263158</v>
+        <v>0.243295</v>
       </c>
       <c r="J12" t="n">
-        <v>0.736842</v>
+        <v>0.756705</v>
       </c>
       <c r="K12" t="n">
-        <v>0.263158</v>
+        <v>0.243295</v>
       </c>
       <c r="L12" t="n">
-        <v>0.736842</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="13">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>1325</v>
@@ -5987,25 +5987,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0.659498</v>
+        <v>0.636364</v>
       </c>
       <c r="H13" t="n">
-        <v>0.340502</v>
+        <v>0.363636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.659498</v>
+        <v>0.636364</v>
       </c>
       <c r="J13" t="n">
-        <v>0.340502</v>
+        <v>0.363636</v>
       </c>
       <c r="K13" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="L13" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
     </row>
     <row r="14">
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>1405</v>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>0.533435</v>
@@ -6206,16 +6206,16 @@
         <v>0.466565</v>
       </c>
       <c r="I18" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J18" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K18" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L18" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="19">
@@ -6242,22 +6242,22 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="H19" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="I19" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="J19" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="K19" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="L19" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="20">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
         <v>0.7241379999999999</v>
@@ -6410,22 +6410,22 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H23" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I23" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J23" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K23" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L23" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="24">
@@ -6491,25 +6491,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H25" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I25" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J25" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K25" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L25" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="26">
@@ -6536,22 +6536,22 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="H26" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="I26" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="J26" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="K26" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="L26" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="27">
@@ -6575,25 +6575,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I27" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K27" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="28">
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
         <v>1405</v>
@@ -6790,28 +6790,28 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H2" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I2" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K2" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="L2" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="M2" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N2" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="3">
@@ -6838,28 +6838,28 @@
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.862069</v>
+        <v>0.803419</v>
       </c>
       <c r="H3" t="n">
-        <v>0.137931</v>
+        <v>0.196581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.862069</v>
+        <v>0.803419</v>
       </c>
       <c r="J3" t="n">
-        <v>0.137931</v>
+        <v>0.196581</v>
       </c>
       <c r="K3" t="n">
-        <v>0.862069</v>
+        <v>0.803419</v>
       </c>
       <c r="L3" t="n">
-        <v>0.137931</v>
+        <v>0.196581</v>
       </c>
       <c r="M3" t="n">
-        <v>0.862069</v>
+        <v>0.803419</v>
       </c>
       <c r="N3" t="n">
-        <v>0.137931</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="4">
@@ -6892,22 +6892,22 @@
         <v>0.05848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="K4" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="M4" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="5">
@@ -6934,28 +6934,28 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H5" t="n">
-        <v>0.275862</v>
+        <v>0.3379</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J5" t="n">
-        <v>0.275862</v>
+        <v>0.3379</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.275862</v>
+        <v>0.3379</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N5" t="n">
-        <v>0.275862</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="6">
@@ -6982,28 +6982,28 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="H6" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="J6" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="N6" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="7">
@@ -7030,28 +7030,28 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="8">
@@ -7078,28 +7078,28 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="9">
@@ -7126,28 +7126,28 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H9" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I9" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J9" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K9" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="L9" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="M9" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N9" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="10">
@@ -7174,28 +7174,28 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="H10" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="J10" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="L10" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="N10" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="11">
@@ -7222,28 +7222,28 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H11" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I11" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J11" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K11" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L11" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M11" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N11" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="12">
@@ -7270,28 +7270,28 @@
         <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="13">
@@ -7558,28 +7558,28 @@
         <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H18" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I18" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J18" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K18" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L18" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M18" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N18" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="19">
@@ -7702,28 +7702,28 @@
         <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.769477</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.230523</v>
+        <v>0.173653</v>
       </c>
       <c r="I21" t="n">
-        <v>0.769477</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.230523</v>
+        <v>0.173653</v>
       </c>
       <c r="K21" t="n">
-        <v>0.769477</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.230523</v>
+        <v>0.173653</v>
       </c>
       <c r="M21" t="n">
-        <v>0.769477</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>0.230523</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="22">
@@ -7750,28 +7750,28 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H22" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I22" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J22" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K22" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L22" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M22" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N22" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="23">
@@ -7798,28 +7798,28 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H23" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I23" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J23" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K23" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L23" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M23" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="N23" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="24">
@@ -7852,22 +7852,22 @@
         <v>0.443197</v>
       </c>
       <c r="I24" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="J24" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="K24" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="L24" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="M24" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="N24" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="25">
@@ -7894,28 +7894,28 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H25" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I25" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J25" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K25" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L25" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M25" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N25" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="26">
@@ -7942,28 +7942,28 @@
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="H26" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="I26" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="J26" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="K26" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="L26" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="M26" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="N26" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="27">
@@ -7990,28 +7990,28 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="28">
@@ -8038,28 +8038,28 @@
         <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.361011</v>
+        <v>0.40884</v>
       </c>
       <c r="H28" t="n">
-        <v>0.638989</v>
+        <v>0.59116</v>
       </c>
       <c r="I28" t="n">
-        <v>0.361011</v>
+        <v>0.40884</v>
       </c>
       <c r="J28" t="n">
-        <v>0.638989</v>
+        <v>0.59116</v>
       </c>
       <c r="K28" t="n">
-        <v>0.361011</v>
+        <v>0.40884</v>
       </c>
       <c r="L28" t="n">
-        <v>0.638989</v>
+        <v>0.59116</v>
       </c>
       <c r="M28" t="n">
-        <v>0.361011</v>
+        <v>0.40884</v>
       </c>
       <c r="N28" t="n">
-        <v>0.638989</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="29">
@@ -8086,28 +8086,28 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H29" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I29" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J29" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K29" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L29" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M29" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N29" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="30">
@@ -8422,28 +8422,28 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="H36" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="I36" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J36" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K36" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L36" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M36" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N36" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="37">
@@ -8470,28 +8470,28 @@
         <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>0.769477</v>
+        <v>0.75</v>
       </c>
       <c r="H37" t="n">
-        <v>0.230523</v>
+        <v>0.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.769477</v>
+        <v>0.75</v>
       </c>
       <c r="J37" t="n">
-        <v>0.230523</v>
+        <v>0.25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.769477</v>
+        <v>0.75</v>
       </c>
       <c r="L37" t="n">
-        <v>0.230523</v>
+        <v>0.25</v>
       </c>
       <c r="M37" t="n">
-        <v>0.769477</v>
+        <v>0.75</v>
       </c>
       <c r="N37" t="n">
-        <v>0.230523</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="38">
@@ -8566,28 +8566,28 @@
         <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="40">
@@ -8854,28 +8854,28 @@
         <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="46">
@@ -8902,28 +8902,28 @@
         <v>7</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N46" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="47">
@@ -8950,28 +8950,28 @@
         <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="H47" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="I47" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="J47" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="K47" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="L47" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="M47" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="N47" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="48">
@@ -8998,28 +8998,28 @@
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="H48" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="I48" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="J48" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="K48" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="L48" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="M48" t="n">
-        <v>0.243295</v>
+        <v>0.228833</v>
       </c>
       <c r="N48" t="n">
-        <v>0.756705</v>
+        <v>0.771167</v>
       </c>
     </row>
     <row r="49">
@@ -9142,28 +9142,28 @@
         <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H51" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I51" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J51" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K51" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L51" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M51" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N51" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="52">
@@ -9238,28 +9238,28 @@
         <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H53" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I53" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J53" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K53" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="L53" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="M53" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N53" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="54">
@@ -9286,28 +9286,28 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6621</v>
+        <v>0.662226</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3379</v>
+        <v>0.337774</v>
       </c>
       <c r="K54" t="n">
-        <v>0.6621</v>
+        <v>0.662226</v>
       </c>
       <c r="L54" t="n">
-        <v>0.3379</v>
+        <v>0.337774</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="55">
@@ -9334,28 +9334,28 @@
         <v>7</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
     </row>
     <row r="56">
@@ -9382,28 +9382,28 @@
         <v>7</v>
       </c>
       <c r="G56" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H56" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I56" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J56" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K56" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L56" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M56" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N56" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
   </sheetData>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>0.036697</v>
@@ -9561,7 +9561,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>0.036697</v>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0.036697</v>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0.036697</v>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0.011765</v>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>1161</v>
@@ -10041,7 +10041,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>0.576433</v>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>1201</v>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>1213</v>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>1305</v>
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>0.556803</v>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>1307</v>
@@ -10233,7 +10233,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>0.40884</v>
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>1361</v>
@@ -10281,31 +10281,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H18" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I18" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J18" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K18" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L18" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="M18" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="N18" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="19">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>1363</v>
@@ -10366,7 +10366,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>1424</v>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>1429</v>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
         <v>1461</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>1201</v>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
         <v>1213</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>1305</v>
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0.432904</v>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>1307</v>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0.272919</v>
@@ -10702,7 +10702,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
         <v>1361</v>
@@ -10713,31 +10713,31 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H27" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I27" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J27" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K27" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L27" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M27" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N27" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="28">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
         <v>1363</v>
@@ -10798,7 +10798,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
         <v>1424</v>
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
         <v>1429</v>
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
         <v>1461</v>
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>0.243295</v>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0.162214</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
         <v>0.162214</v>
@@ -11337,7 +11337,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>0.511551</v>
@@ -11385,7 +11385,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
         <v>0.361011</v>
@@ -11433,31 +11433,31 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H42" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I42" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J42" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K42" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L42" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M42" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N42" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="43">
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
         <v>1307</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
         <v>0.361011</v>
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
         <v>1361</v>
@@ -11721,31 +11721,31 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H48" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I48" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J48" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K48" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L48" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M48" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N48" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="49">
@@ -11758,7 +11758,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
         <v>1363</v>
@@ -11806,7 +11806,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
         <v>1424</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
         <v>1429</v>
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
         <v>1461</v>
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
         <v>1361</v>
@@ -11961,31 +11961,31 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H53" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I53" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J53" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K53" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L53" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M53" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N53" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="54">
@@ -11998,7 +11998,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
         <v>1363</v>
@@ -12046,7 +12046,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>1424</v>
@@ -12094,7 +12094,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
         <v>1429</v>
@@ -12142,7 +12142,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
         <v>1461</v>
@@ -12190,7 +12190,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>1363</v>
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
         <v>1424</v>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>1429</v>
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>1461</v>
@@ -12348,10 +12348,10 @@
         <v>9</v>
       </c>
       <c r="G61" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="I61" t="n">
         <v>0.7304349999999999</v>
@@ -12366,10 +12366,10 @@
         <v>0.269565</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="62">
@@ -19628,28 +19628,28 @@
         <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I2" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J2" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K2" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L2" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M2" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N2" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="3">
@@ -19724,28 +19724,28 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I4" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J4" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K4" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L4" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M4" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N4" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="5">
@@ -19772,28 +19772,28 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I5" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J5" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K5" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L5" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M5" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N5" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="6">
@@ -19820,28 +19820,28 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="H6" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="I6" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="J6" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="K6" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="M6" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="N6" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="7">
@@ -19868,28 +19868,28 @@
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="8">
@@ -20204,28 +20204,28 @@
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="I14" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="J14" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="K14" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="L14" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="M14" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="N14" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="15">
@@ -20312,16 +20312,16 @@
         <v>0.466565</v>
       </c>
       <c r="K16" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="L16" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="M16" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="N16" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="17">
@@ -20348,28 +20348,28 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="H17" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="I17" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="J17" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="K17" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="L17" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="M17" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="N17" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="18">
@@ -20876,28 +20876,28 @@
         <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H28" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I28" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J28" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K28" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L28" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M28" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N28" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="29">
@@ -21500,28 +21500,28 @@
         <v>10</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
     </row>
     <row r="42">
@@ -21692,28 +21692,28 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="H45" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="I45" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="J45" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="K45" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="L45" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="M45" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="N45" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
     </row>
     <row r="46">
@@ -25244,40 +25244,40 @@
         <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H34" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J34" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L34" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N34" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="P34" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="R34" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="35">
@@ -25682,22 +25682,22 @@
         <v>0.567096</v>
       </c>
       <c r="M41" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N41" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="O41" t="n">
-        <v>0.429683</v>
+        <v>0.432904</v>
       </c>
       <c r="P41" t="n">
-        <v>0.570317</v>
+        <v>0.567096</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.429683</v>
+        <v>0.432904</v>
       </c>
       <c r="R41" t="n">
-        <v>0.570317</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="42">
@@ -25964,40 +25964,40 @@
         <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="H46" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="I46" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="J46" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="K46" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="L46" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="M46" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="N46" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="O46" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="P46" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="R46" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="47">
@@ -26204,40 +26204,40 @@
         <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H50" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I50" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J50" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K50" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L50" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M50" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N50" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O50" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P50" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="R50" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="51">
@@ -26324,40 +26324,40 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H52" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I52" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J52" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K52" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L52" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M52" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N52" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O52" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P52" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="R52" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="53">
@@ -26744,40 +26744,40 @@
         <v>7</v>
       </c>
       <c r="G59" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="H59" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="I59" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="J59" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="K59" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="L59" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="M59" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="N59" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="O59" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="P59" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="R59" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="60">
@@ -26924,10 +26924,10 @@
         <v>7</v>
       </c>
       <c r="G62" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="H62" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="I62" t="n">
         <v>0.769477</v>
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>0.8263470000000001</v>
@@ -36317,37 +36317,37 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="H14" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="I14" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="J14" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="K14" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="L14" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="M14" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="N14" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="O14" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="P14" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="15">
@@ -36425,37 +36425,37 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="H16" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="I16" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="J16" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="K16" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L16" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M16" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N16" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O16" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="P16" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="17">
@@ -36587,7 +36587,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
         <v>0.40884</v>
@@ -37073,37 +37073,37 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.40625</v>
+        <v>0.426966</v>
       </c>
       <c r="H28" t="n">
-        <v>0.59375</v>
+        <v>0.573034</v>
       </c>
       <c r="I28" t="n">
-        <v>0.40625</v>
+        <v>0.426966</v>
       </c>
       <c r="J28" t="n">
-        <v>0.59375</v>
+        <v>0.573034</v>
       </c>
       <c r="K28" t="n">
-        <v>0.40625</v>
+        <v>0.426966</v>
       </c>
       <c r="L28" t="n">
-        <v>0.59375</v>
+        <v>0.573034</v>
       </c>
       <c r="M28" t="n">
-        <v>0.40625</v>
+        <v>0.426966</v>
       </c>
       <c r="N28" t="n">
-        <v>0.59375</v>
+        <v>0.573034</v>
       </c>
       <c r="O28" t="n">
-        <v>0.40625</v>
+        <v>0.426966</v>
       </c>
       <c r="P28" t="n">
-        <v>0.59375</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="29">
@@ -37181,37 +37181,37 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H30" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I30" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J30" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K30" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L30" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="M30" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="N30" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="O30" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="P30" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="31">
@@ -37289,7 +37289,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>0.511551</v>
@@ -37775,37 +37775,37 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H41" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I41" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J41" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K41" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L41" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M41" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N41" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="O41" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="P41" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="42">
@@ -37883,37 +37883,37 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="44">
@@ -37937,7 +37937,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G44" t="n">
         <v>0.659498</v>
@@ -38423,7 +38423,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G53" t="n">
         <v>0.6621</v>
@@ -38531,7 +38531,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G55" t="n">
         <v>0.6787069999999999</v>
@@ -38574,7 +38574,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
         <v>1160</v>
@@ -38628,7 +38628,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
         <v>1222</v>
@@ -38682,7 +38682,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
         <v>1235</v>
@@ -38736,7 +38736,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
         <v>1242</v>
@@ -38790,7 +38790,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
         <v>1243</v>
@@ -38844,7 +38844,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
         <v>1329</v>
@@ -38898,7 +38898,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
         <v>1395</v>
@@ -38952,7 +38952,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
         <v>1403</v>
@@ -39006,7 +39006,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
         <v>1416</v>
@@ -39017,37 +39017,37 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G64" t="n">
-        <v>0.460746</v>
+        <v>0.532905</v>
       </c>
       <c r="H64" t="n">
-        <v>0.539254</v>
+        <v>0.467095</v>
       </c>
       <c r="I64" t="n">
-        <v>0.460746</v>
+        <v>0.532905</v>
       </c>
       <c r="J64" t="n">
-        <v>0.539254</v>
+        <v>0.467095</v>
       </c>
       <c r="K64" t="n">
-        <v>0.460746</v>
+        <v>0.532905</v>
       </c>
       <c r="L64" t="n">
-        <v>0.539254</v>
+        <v>0.467095</v>
       </c>
       <c r="M64" t="n">
-        <v>0.460746</v>
+        <v>0.532905</v>
       </c>
       <c r="N64" t="n">
-        <v>0.539254</v>
+        <v>0.467095</v>
       </c>
       <c r="O64" t="n">
-        <v>0.460746</v>
+        <v>0.532905</v>
       </c>
       <c r="P64" t="n">
-        <v>0.539254</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="65">
@@ -39060,7 +39060,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
         <v>1428</v>
@@ -39114,7 +39114,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
         <v>1452</v>
@@ -39125,37 +39125,37 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>0.577889</v>
+        <v>0.576433</v>
       </c>
       <c r="H66" t="n">
-        <v>0.422111</v>
+        <v>0.423567</v>
       </c>
       <c r="I66" t="n">
-        <v>0.577889</v>
+        <v>0.576433</v>
       </c>
       <c r="J66" t="n">
-        <v>0.422111</v>
+        <v>0.423567</v>
       </c>
       <c r="K66" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="L66" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="M66" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="N66" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="O66" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P66" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="67">
@@ -39557,37 +39557,37 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="H74" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="I74" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="J74" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="K74" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="L74" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="M74" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="N74" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="O74" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="P74" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="75">
@@ -39665,7 +39665,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
         <v>0.432904</v>
@@ -40043,7 +40043,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G83" t="n">
         <v>0.8263470000000001</v>
@@ -40151,37 +40151,37 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="I85" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="K85" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M85" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N85" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O85" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P85" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="86">
@@ -40475,31 +40475,31 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G91" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="H91" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="I91" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="J91" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="K91" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="L91" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="M91" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="N91" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="O91" t="n">
         <v>0.769477</v>
@@ -40583,37 +40583,37 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H93" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J93" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K93" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L93" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M93" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N93" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O93" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P93" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="94">
@@ -40853,7 +40853,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G98" t="n">
         <v>0.659498</v>
@@ -40961,37 +40961,37 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L100" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N100" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P100" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="101">
@@ -41177,7 +41177,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G104" t="n">
         <v>0.272919</v>
@@ -41285,37 +41285,37 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="H106" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="I106" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="J106" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="K106" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="L106" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="M106" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="N106" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="O106" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="P106" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="107">
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G109" t="n">
         <v>0.361011</v>
@@ -41555,7 +41555,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G111" t="n">
         <v>0.432904</v>
@@ -41663,7 +41663,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G113" t="n">
         <v>0.532905</v>
@@ -41684,16 +41684,16 @@
         <v>0.467095</v>
       </c>
       <c r="M113" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N113" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="O113" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="P113" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="114">
@@ -41771,37 +41771,37 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="H115" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="I115" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="J115" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="K115" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="L115" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="M115" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N115" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O115" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P115" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="116">
@@ -41825,37 +41825,37 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G116" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H116" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="I116" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J116" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="K116" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L116" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="M116" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N116" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="O116" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="P116" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="117">
@@ -41933,37 +41933,37 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H118" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="I118" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="K118" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L118" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="M118" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N118" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="O118" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P118" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="119">
@@ -41976,7 +41976,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D119" t="n">
         <v>1428</v>
@@ -41990,34 +41990,34 @@
         <v>16</v>
       </c>
       <c r="G119" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H119" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I119" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J119" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K119" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L119" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M119" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N119" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O119" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P119" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="120">
@@ -42030,7 +42030,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D120" t="n">
         <v>1452</v>
@@ -42041,7 +42041,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G120" t="n">
         <v>0.556803</v>
@@ -42095,37 +42095,37 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H121" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I121" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J121" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K121" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L121" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M121" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N121" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O121" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P121" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
   </sheetData>
@@ -42235,7 +42235,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0.162214</v>
@@ -42526,28 +42526,28 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="H8" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="I8" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="J8" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="K8" t="n">
-        <v>0.361446</v>
+        <v>0.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.638554</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0.361446</v>
+        <v>0.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.638554</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -42571,7 +42571,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0.162214</v>
@@ -42704,7 +42704,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>1166</v>
@@ -42752,7 +42752,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>1177</v>
@@ -42800,7 +42800,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>1207</v>
@@ -42848,7 +42848,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>1266</v>
@@ -42896,7 +42896,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>1344</v>
@@ -42944,7 +42944,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>1371</v>
@@ -42958,28 +42958,28 @@
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="H17" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="I17" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="J17" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="K17" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="L17" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="M17" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="N17" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="18">
@@ -42992,7 +42992,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>1385</v>
@@ -43003,7 +43003,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0.556803</v>
@@ -43040,7 +43040,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>1437</v>
@@ -43088,7 +43088,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>1462</v>
@@ -43387,7 +43387,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0.185358</v>
@@ -43723,7 +43723,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>0.100437</v>
@@ -44011,7 +44011,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
         <v>0.162214</v>
@@ -44251,7 +44251,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>0.162214</v>
@@ -44398,28 +44398,28 @@
         <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H47" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I47" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J47" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K47" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L47" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M47" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N47" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="48">
@@ -44443,7 +44443,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>0.162214</v>
@@ -44587,31 +44587,31 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="H51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="I51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="J51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="K51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="L51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="M51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="N51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="52">
@@ -44720,7 +44720,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>1437</v>
@@ -44768,7 +44768,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>1462</v>
@@ -45078,10 +45078,10 @@
         <v>0.488449</v>
       </c>
       <c r="M4" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="N4" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="5">
@@ -45204,28 +45204,28 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H7" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6402099999999999</v>
+        <v>0.577889</v>
       </c>
       <c r="J7" t="n">
-        <v>0.35979</v>
+        <v>0.422111</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6402099999999999</v>
+        <v>0.577889</v>
       </c>
       <c r="L7" t="n">
-        <v>0.35979</v>
+        <v>0.422111</v>
       </c>
       <c r="M7" t="n">
-        <v>0.594595</v>
+        <v>0.577889</v>
       </c>
       <c r="N7" t="n">
-        <v>0.405405</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="8">
@@ -45252,28 +45252,28 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H8" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I8" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J8" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K8" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L8" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="M8" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="N8" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="9">
@@ -45300,28 +45300,28 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H9" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I9" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J9" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K9" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L9" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M9" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N9" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="10">
@@ -45636,28 +45636,28 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.045455</v>
+        <v>0.07567599999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.954545</v>
+        <v>0.924324</v>
       </c>
       <c r="I16" t="n">
-        <v>0.045455</v>
+        <v>0.07567599999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.954545</v>
+        <v>0.924324</v>
       </c>
       <c r="K16" t="n">
-        <v>0.045455</v>
+        <v>0.07567599999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.954545</v>
+        <v>0.924324</v>
       </c>
       <c r="M16" t="n">
-        <v>0.045455</v>
+        <v>0.07567599999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.954545</v>
+        <v>0.924324</v>
       </c>
     </row>
     <row r="17">
@@ -45876,28 +45876,28 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="I21" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="K21" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="M21" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="N21" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="22">
@@ -45972,28 +45972,28 @@
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H23" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I23" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J23" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K23" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L23" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M23" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N23" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="24">
@@ -46164,28 +46164,28 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="H27" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
       <c r="I27" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="J27" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
       <c r="K27" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="L27" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
       <c r="M27" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="N27" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="28">
@@ -46404,28 +46404,28 @@
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N32" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="33">
@@ -46452,28 +46452,28 @@
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H33" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I33" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J33" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K33" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L33" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M33" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N33" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="34">
@@ -46548,10 +46548,10 @@
         <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H35" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I35" t="n">
         <v>0.361011</v>
@@ -46596,28 +46596,28 @@
         <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>0.125</v>
+        <v>0.140351</v>
       </c>
       <c r="H36" t="n">
-        <v>0.875</v>
+        <v>0.859649</v>
       </c>
       <c r="I36" t="n">
-        <v>0.125</v>
+        <v>0.140351</v>
       </c>
       <c r="J36" t="n">
-        <v>0.875</v>
+        <v>0.859649</v>
       </c>
       <c r="K36" t="n">
-        <v>0.125</v>
+        <v>0.140351</v>
       </c>
       <c r="L36" t="n">
-        <v>0.875</v>
+        <v>0.859649</v>
       </c>
       <c r="M36" t="n">
-        <v>0.125</v>
+        <v>0.140351</v>
       </c>
       <c r="N36" t="n">
-        <v>0.875</v>
+        <v>0.859649</v>
       </c>
     </row>
     <row r="37">
@@ -56452,34 +56452,34 @@
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="10">
@@ -57046,34 +57046,34 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H20" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J20" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L20" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N20" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P20" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="21">
@@ -58018,34 +58018,34 @@
         <v>12</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P38" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="39">
@@ -59152,34 +59152,34 @@
         <v>12</v>
       </c>
       <c r="G59" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H59" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I59" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J59" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K59" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L59" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M59" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N59" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="O59" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="P59" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="60">
@@ -59476,10 +59476,10 @@
         <v>13</v>
       </c>
       <c r="G65" t="n">
-        <v>0.533406</v>
+        <v>0.532905</v>
       </c>
       <c r="H65" t="n">
-        <v>0.466594</v>
+        <v>0.467095</v>
       </c>
       <c r="I65" t="n">
         <v>0.532905</v>

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -56108,7 +56108,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>1270</v>
@@ -56156,7 +56156,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>1309</v>
@@ -56204,7 +56204,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>1311</v>
@@ -56252,7 +56252,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>1322</v>
@@ -56263,7 +56263,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>0.432904</v>
@@ -56300,7 +56300,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>1372</v>
@@ -56348,7 +56348,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>1394</v>
@@ -56396,7 +56396,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>1410</v>
@@ -56551,7 +56551,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
         <v>0.95</v>
@@ -56791,7 +56791,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
         <v>0.7241379999999999</v>
@@ -56983,7 +56983,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
         <v>0.6621</v>
@@ -57164,7 +57164,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
         <v>1372</v>
@@ -57212,7 +57212,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>1394</v>
@@ -57260,7 +57260,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>1410</v>

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -5572,40 +5572,40 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H2" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I2" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="J2" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="K2" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="M2" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="N2" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="O2" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P2" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="R2" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="3">
@@ -5692,40 +5692,40 @@
         <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="K4" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="O4" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="5">
@@ -5752,40 +5752,40 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H5" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I5" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J5" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K5" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M5" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N5" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O5" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P5" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="R5" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="6">
@@ -5890,22 +5890,22 @@
         <v>0.117333</v>
       </c>
       <c r="M7" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="N7" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="O7" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="P7" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="R7" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
     </row>
     <row r="8">
@@ -5932,40 +5932,40 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="H8" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="J8" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="N8" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="P8" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="R8" t="n">
-        <v>0.275862</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="9">
@@ -5992,40 +5992,40 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H9" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I9" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K9" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L9" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M9" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N9" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O9" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="10">
@@ -6082,10 +6082,10 @@
         <v>0.25731</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
     </row>
     <row r="11">
@@ -6172,40 +6172,40 @@
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="K12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="M12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="O12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="P12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="R12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="13">
@@ -6232,40 +6232,40 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="R13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="14">
@@ -6352,40 +6352,40 @@
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="I15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="K15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="M15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="O15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="16">
@@ -6472,40 +6472,40 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H17" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I17" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J17" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K17" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L17" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M17" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="O17" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="18">
@@ -6532,40 +6532,40 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="19">
@@ -6652,40 +6652,40 @@
         <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H20" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I20" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J20" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K20" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L20" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M20" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N20" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O20" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P20" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="R20" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="21">
@@ -6772,40 +6772,40 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="H22" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="I22" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="J22" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="K22" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="L22" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="M22" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="N22" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="O22" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="P22" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="R22" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="23">
@@ -6892,40 +6892,40 @@
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H24" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I24" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J24" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K24" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L24" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M24" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N24" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O24" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P24" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="R24" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="25">
@@ -7552,40 +7552,40 @@
         <v>17</v>
       </c>
       <c r="G35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="36">
@@ -7612,40 +7612,40 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H36" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I36" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J36" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K36" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L36" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M36" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N36" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O36" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="P36" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="R36" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="37">
@@ -7792,40 +7792,40 @@
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H39" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I39" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J39" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K39" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L39" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M39" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N39" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="O39" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="P39" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="R39" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="40">
@@ -7852,28 +7852,28 @@
         <v>15</v>
       </c>
       <c r="G40" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H40" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I40" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J40" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K40" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L40" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M40" t="n">
-        <v>0.75</v>
+        <v>0.74269</v>
       </c>
       <c r="N40" t="n">
-        <v>0.25</v>
+        <v>0.25731</v>
       </c>
       <c r="O40" t="n">
         <v>0.74269</v>
@@ -8170,22 +8170,22 @@
         <v>0.117333</v>
       </c>
       <c r="M45" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="N45" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="O45" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="P45" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="R45" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
     </row>
     <row r="46">
@@ -8296,16 +8296,16 @@
         <v>0.230523</v>
       </c>
       <c r="O47" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P47" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="R47" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="48">
@@ -8572,40 +8572,40 @@
         <v>11</v>
       </c>
       <c r="G52" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H52" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I52" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="J52" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="K52" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L52" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="M52" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="N52" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="O52" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="P52" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="R52" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="53">
@@ -8632,40 +8632,40 @@
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="H53" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="I53" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="J53" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="K53" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="L53" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="M53" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="N53" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="O53" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="P53" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="R53" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="54">
@@ -8692,40 +8692,40 @@
         <v>15</v>
       </c>
       <c r="G54" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H54" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I54" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J54" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K54" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L54" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M54" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N54" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O54" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="P54" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="R54" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="55">
@@ -8752,40 +8752,40 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H55" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I55" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J55" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K55" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L55" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M55" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N55" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="O55" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="P55" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="R55" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="56">
@@ -8872,40 +8872,40 @@
         <v>18</v>
       </c>
       <c r="G57" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="H57" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="I57" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="J57" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="K57" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="L57" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="M57" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="N57" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="O57" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="P57" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="R57" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="58">
@@ -9172,40 +9172,40 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="R62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="63">
@@ -9532,40 +9532,40 @@
         <v>8</v>
       </c>
       <c r="G68" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="H68" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="I68" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="J68" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="K68" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="L68" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="M68" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="N68" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="O68" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="P68" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="R68" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="69">
@@ -9652,16 +9652,16 @@
         <v>18</v>
       </c>
       <c r="G70" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="H70" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
       <c r="I70" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="J70" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
       <c r="K70" t="n">
         <v>0.94152</v>
@@ -9952,34 +9952,34 @@
         <v>12</v>
       </c>
       <c r="G75" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="H75" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="I75" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="J75" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="K75" t="n">
-        <v>0.853147</v>
+        <v>0.862069</v>
       </c>
       <c r="L75" t="n">
-        <v>0.146853</v>
+        <v>0.137931</v>
       </c>
       <c r="M75" t="n">
-        <v>0.853147</v>
+        <v>0.862069</v>
       </c>
       <c r="N75" t="n">
-        <v>0.146853</v>
+        <v>0.137931</v>
       </c>
       <c r="O75" t="n">
-        <v>0.853147</v>
+        <v>0.862069</v>
       </c>
       <c r="P75" t="n">
-        <v>0.146853</v>
+        <v>0.137931</v>
       </c>
       <c r="Q75" t="n">
         <v>0.853147</v>
@@ -10012,40 +10012,40 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H76" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I76" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J76" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K76" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L76" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M76" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N76" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="O76" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="P76" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="R76" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="77">
@@ -10072,40 +10072,40 @@
         <v>11</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="R77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="78">
@@ -10132,40 +10132,40 @@
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="H78" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="I78" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="J78" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="K78" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="L78" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="M78" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="N78" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="O78" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="P78" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="R78" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="79">
@@ -10222,10 +10222,10 @@
         <v>0.19214</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="R79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="80">
@@ -10312,40 +10312,40 @@
         <v>16</v>
       </c>
       <c r="G81" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="I81" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="K81" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="M81" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="O81" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P81" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="82">
@@ -10432,40 +10432,40 @@
         <v>7</v>
       </c>
       <c r="G83" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="H83" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="I83" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="J83" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="K83" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="L83" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="M83" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="N83" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="O83" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="P83" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="R83" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="84">
@@ -10612,40 +10612,40 @@
         <v>13</v>
       </c>
       <c r="G86" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H86" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I86" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J86" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K86" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L86" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M86" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N86" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O86" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R86" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="87">
@@ -10672,40 +10672,40 @@
         <v>12</v>
       </c>
       <c r="G87" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H87" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I87" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="J87" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="K87" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="L87" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="M87" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="N87" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="O87" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="P87" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="R87" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="88">
@@ -10792,40 +10792,40 @@
         <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="H89" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="I89" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="J89" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="K89" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="L89" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="M89" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="N89" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="O89" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="P89" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="R89" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="90">
@@ -11512,40 +11512,40 @@
         <v>8</v>
       </c>
       <c r="G101" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H101" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I101" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J101" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K101" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L101" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M101" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N101" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="O101" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="P101" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="R101" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="102">
@@ -11752,40 +11752,40 @@
         <v>14</v>
       </c>
       <c r="G105" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="H105" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="I105" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="J105" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="K105" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="L105" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="M105" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="N105" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="O105" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="P105" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="R105" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="106">
@@ -11932,40 +11932,40 @@
         <v>12</v>
       </c>
       <c r="G108" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H108" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J108" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="K108" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L108" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="M108" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N108" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="O108" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="P108" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="R108" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="109">
@@ -11992,40 +11992,40 @@
         <v>5</v>
       </c>
       <c r="G109" t="n">
-        <v>0.511551</v>
+        <v>0.533435</v>
       </c>
       <c r="H109" t="n">
-        <v>0.488449</v>
+        <v>0.466565</v>
       </c>
       <c r="I109" t="n">
-        <v>0.511551</v>
+        <v>0.533435</v>
       </c>
       <c r="J109" t="n">
-        <v>0.488449</v>
+        <v>0.466565</v>
       </c>
       <c r="K109" t="n">
-        <v>0.511551</v>
+        <v>0.533435</v>
       </c>
       <c r="L109" t="n">
-        <v>0.488449</v>
+        <v>0.466565</v>
       </c>
       <c r="M109" t="n">
-        <v>0.511551</v>
+        <v>0.533435</v>
       </c>
       <c r="N109" t="n">
-        <v>0.488449</v>
+        <v>0.466565</v>
       </c>
       <c r="O109" t="n">
-        <v>0.511551</v>
+        <v>0.533435</v>
       </c>
       <c r="P109" t="n">
-        <v>0.488449</v>
+        <v>0.466565</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.511551</v>
+        <v>0.533435</v>
       </c>
       <c r="R109" t="n">
-        <v>0.488449</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="110">
@@ -12172,40 +12172,40 @@
         <v>18</v>
       </c>
       <c r="G112" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H112" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J112" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K112" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L112" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M112" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N112" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O112" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P112" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="R112" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="113">
@@ -13612,40 +13612,40 @@
         <v>6</v>
       </c>
       <c r="G136" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="H136" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="I136" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="J136" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="K136" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="L136" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="M136" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="N136" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="O136" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="P136" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="R136" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="137">
@@ -13672,28 +13672,28 @@
         <v>13</v>
       </c>
       <c r="G137" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H137" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I137" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J137" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K137" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L137" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M137" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N137" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O137" t="n">
         <v>0.283654</v>
@@ -13792,40 +13792,40 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H139" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I139" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J139" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K139" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L139" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M139" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N139" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="O139" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="P139" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="R139" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="140">
@@ -16278,34 +16278,34 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.40625</v>
+        <v>0.426966</v>
       </c>
       <c r="H2" t="n">
-        <v>0.59375</v>
+        <v>0.573034</v>
       </c>
       <c r="I2" t="n">
-        <v>0.40625</v>
+        <v>0.426966</v>
       </c>
       <c r="J2" t="n">
-        <v>0.59375</v>
+        <v>0.573034</v>
       </c>
       <c r="K2" t="n">
-        <v>0.361446</v>
+        <v>0.426966</v>
       </c>
       <c r="L2" t="n">
-        <v>0.638554</v>
+        <v>0.573034</v>
       </c>
       <c r="M2" t="n">
-        <v>0.361446</v>
+        <v>0.426966</v>
       </c>
       <c r="N2" t="n">
-        <v>0.638554</v>
+        <v>0.573034</v>
       </c>
       <c r="O2" t="n">
-        <v>0.361446</v>
+        <v>0.426966</v>
       </c>
       <c r="P2" t="n">
-        <v>0.638554</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="3">
@@ -16386,34 +16386,34 @@
         <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="H4" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="J4" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="K4" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="L4" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="M4" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="N4" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="O4" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="P4" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="5">
@@ -16440,34 +16440,34 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="6">
@@ -16602,34 +16602,34 @@
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H8" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I8" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J8" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K8" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M8" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N8" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="O8" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="P8" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="9">
@@ -16656,34 +16656,34 @@
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H9" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J9" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N9" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="P9" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="10">
@@ -16710,34 +16710,34 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="H10" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="I10" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="J10" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="K10" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="L10" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="M10" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="N10" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="O10" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="P10" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="11">
@@ -16764,34 +16764,34 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H11" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J11" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K11" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L11" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M11" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N11" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O11" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="P11" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="12">
@@ -16818,34 +16818,34 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.230483</v>
+        <v>0.272919</v>
       </c>
       <c r="H12" t="n">
-        <v>0.769517</v>
+        <v>0.727081</v>
       </c>
       <c r="I12" t="n">
-        <v>0.230483</v>
+        <v>0.272919</v>
       </c>
       <c r="J12" t="n">
-        <v>0.769517</v>
+        <v>0.727081</v>
       </c>
       <c r="K12" t="n">
-        <v>0.230483</v>
+        <v>0.272919</v>
       </c>
       <c r="L12" t="n">
-        <v>0.769517</v>
+        <v>0.727081</v>
       </c>
       <c r="M12" t="n">
-        <v>0.230483</v>
+        <v>0.272919</v>
       </c>
       <c r="N12" t="n">
-        <v>0.769517</v>
+        <v>0.727081</v>
       </c>
       <c r="O12" t="n">
-        <v>0.230483</v>
+        <v>0.272919</v>
       </c>
       <c r="P12" t="n">
-        <v>0.769517</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="13">
@@ -16872,34 +16872,34 @@
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H13" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I13" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="J13" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="K13" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L13" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="M13" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="N13" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="O13" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="P13" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="14">
@@ -16926,34 +16926,34 @@
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6717689999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H14" t="n">
-        <v>0.328231</v>
+        <v>0.3379</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6717689999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J14" t="n">
-        <v>0.328231</v>
+        <v>0.3379</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L14" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N14" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P14" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="15">
@@ -17088,34 +17088,34 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.361011</v>
+        <v>0.308594</v>
       </c>
       <c r="H17" t="n">
-        <v>0.638989</v>
+        <v>0.691406</v>
       </c>
       <c r="I17" t="n">
-        <v>0.361011</v>
+        <v>0.308594</v>
       </c>
       <c r="J17" t="n">
-        <v>0.638989</v>
+        <v>0.691406</v>
       </c>
       <c r="K17" t="n">
-        <v>0.361011</v>
+        <v>0.308594</v>
       </c>
       <c r="L17" t="n">
-        <v>0.638989</v>
+        <v>0.691406</v>
       </c>
       <c r="M17" t="n">
-        <v>0.361011</v>
+        <v>0.308594</v>
       </c>
       <c r="N17" t="n">
-        <v>0.638989</v>
+        <v>0.691406</v>
       </c>
       <c r="O17" t="n">
-        <v>0.361011</v>
+        <v>0.308594</v>
       </c>
       <c r="P17" t="n">
-        <v>0.638989</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="18">
@@ -17142,34 +17142,34 @@
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="H18" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="I18" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="J18" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="K18" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="L18" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="M18" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="N18" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="O18" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="P18" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="19">
@@ -17196,34 +17196,34 @@
         <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="20">
@@ -17250,34 +17250,34 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H20" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I20" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J20" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K20" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L20" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M20" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N20" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O20" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P20" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="21">
@@ -17358,34 +17358,34 @@
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H22" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I22" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J22" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K22" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L22" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M22" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N22" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O22" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="P22" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="23">
@@ -17466,34 +17466,34 @@
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="M24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="N24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="O24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="P24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="25">
@@ -17526,28 +17526,28 @@
         <v>0.492424</v>
       </c>
       <c r="I25" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="J25" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="K25" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="L25" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="M25" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="N25" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="O25" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="P25" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="26">
@@ -17628,34 +17628,34 @@
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H27" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I27" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J27" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K27" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L27" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M27" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N27" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O27" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P27" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="28">
@@ -17844,34 +17844,34 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H31" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I31" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J31" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K31" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L31" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M31" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N31" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O31" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P31" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="32">
@@ -17898,34 +17898,34 @@
         <v>7</v>
       </c>
       <c r="G32" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H32" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I32" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J32" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K32" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L32" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M32" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N32" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O32" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="P32" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="33">
@@ -18114,34 +18114,34 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="H36" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="I36" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="J36" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="K36" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="L36" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="M36" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="N36" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="O36" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="P36" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="37">
@@ -18384,34 +18384,34 @@
         <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H41" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I41" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J41" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K41" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L41" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M41" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N41" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O41" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P41" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="42">
@@ -18438,34 +18438,34 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H42" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I42" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J42" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K42" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L42" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M42" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N42" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="O42" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="P42" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="43">
@@ -18492,34 +18492,34 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H43" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I43" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J43" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K43" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L43" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M43" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N43" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O43" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P43" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="44">
@@ -18546,34 +18546,34 @@
         <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H44" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I44" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J44" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K44" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L44" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M44" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N44" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="O44" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="P44" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="45">
@@ -18816,34 +18816,34 @@
         <v>7</v>
       </c>
       <c r="G49" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="I49" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="K49" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="M49" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="N49" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="O49" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="P49" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="50">
@@ -18870,34 +18870,34 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H50" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I50" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J50" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K50" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L50" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M50" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="N50" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="O50" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="P50" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="51">
@@ -18924,34 +18924,34 @@
         <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="H51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="I51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="J51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="K51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="L51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="M51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="N51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="O51" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="P51" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="52">
@@ -18978,34 +18978,34 @@
         <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H52" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I52" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J52" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K52" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L52" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M52" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N52" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="O52" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="P52" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="53">
@@ -19032,34 +19032,34 @@
         <v>12</v>
       </c>
       <c r="G53" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="H53" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="I53" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="J53" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="K53" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="L53" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="M53" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="N53" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="O53" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="P53" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="54">
@@ -19140,34 +19140,34 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.80786</v>
+        <v>0.882667</v>
       </c>
       <c r="H55" t="n">
-        <v>0.19214</v>
+        <v>0.117333</v>
       </c>
       <c r="I55" t="n">
-        <v>0.80786</v>
+        <v>0.882667</v>
       </c>
       <c r="J55" t="n">
-        <v>0.19214</v>
+        <v>0.117333</v>
       </c>
       <c r="K55" t="n">
-        <v>0.80786</v>
+        <v>0.882667</v>
       </c>
       <c r="L55" t="n">
-        <v>0.19214</v>
+        <v>0.117333</v>
       </c>
       <c r="M55" t="n">
-        <v>0.80786</v>
+        <v>0.882667</v>
       </c>
       <c r="N55" t="n">
-        <v>0.19214</v>
+        <v>0.117333</v>
       </c>
       <c r="O55" t="n">
-        <v>0.80786</v>
+        <v>0.882667</v>
       </c>
       <c r="P55" t="n">
-        <v>0.19214</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="56">
@@ -19248,34 +19248,34 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.511551</v>
+        <v>0.556803</v>
       </c>
       <c r="H57" t="n">
-        <v>0.488449</v>
+        <v>0.443197</v>
       </c>
       <c r="I57" t="n">
-        <v>0.511551</v>
+        <v>0.556803</v>
       </c>
       <c r="J57" t="n">
-        <v>0.488449</v>
+        <v>0.443197</v>
       </c>
       <c r="K57" t="n">
-        <v>0.511551</v>
+        <v>0.556803</v>
       </c>
       <c r="L57" t="n">
-        <v>0.488449</v>
+        <v>0.443197</v>
       </c>
       <c r="M57" t="n">
-        <v>0.511551</v>
+        <v>0.556803</v>
       </c>
       <c r="N57" t="n">
-        <v>0.488449</v>
+        <v>0.443197</v>
       </c>
       <c r="O57" t="n">
-        <v>0.511551</v>
+        <v>0.556803</v>
       </c>
       <c r="P57" t="n">
-        <v>0.488449</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="58">
@@ -19302,34 +19302,34 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
       <c r="K58" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
       <c r="O58" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P58" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="59">
@@ -19410,34 +19410,34 @@
         <v>13</v>
       </c>
       <c r="G60" t="n">
-        <v>0.74269</v>
+        <v>0.75</v>
       </c>
       <c r="H60" t="n">
-        <v>0.25731</v>
+        <v>0.25</v>
       </c>
       <c r="I60" t="n">
-        <v>0.74269</v>
+        <v>0.75</v>
       </c>
       <c r="J60" t="n">
-        <v>0.25731</v>
+        <v>0.25</v>
       </c>
       <c r="K60" t="n">
-        <v>0.74269</v>
+        <v>0.75</v>
       </c>
       <c r="L60" t="n">
-        <v>0.25731</v>
+        <v>0.25</v>
       </c>
       <c r="M60" t="n">
-        <v>0.74269</v>
+        <v>0.75</v>
       </c>
       <c r="N60" t="n">
-        <v>0.25731</v>
+        <v>0.25</v>
       </c>
       <c r="O60" t="n">
-        <v>0.74269</v>
+        <v>0.75</v>
       </c>
       <c r="P60" t="n">
-        <v>0.25731</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="61">
@@ -19518,34 +19518,34 @@
         <v>7</v>
       </c>
       <c r="G62" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H62" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I62" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J62" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K62" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L62" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M62" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N62" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O62" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="P62" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="63">
@@ -19572,34 +19572,34 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="H63" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
       <c r="I63" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="J63" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
       <c r="K63" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="L63" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
       <c r="M63" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="N63" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
       <c r="O63" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="P63" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="64">
@@ -19626,34 +19626,34 @@
         <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H64" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I64" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J64" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K64" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L64" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M64" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N64" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O64" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="P64" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="65">
@@ -19788,34 +19788,34 @@
         <v>7</v>
       </c>
       <c r="G67" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H67" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I67" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J67" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K67" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L67" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M67" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N67" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O67" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P67" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="68">
@@ -20004,34 +20004,34 @@
         <v>7</v>
       </c>
       <c r="G71" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H71" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I71" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J71" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K71" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L71" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M71" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N71" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O71" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P71" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="72">
@@ -20166,34 +20166,34 @@
         <v>7</v>
       </c>
       <c r="G74" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="H74" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="I74" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="J74" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="K74" t="n">
-        <v>0.332008</v>
+        <v>0.272919</v>
       </c>
       <c r="L74" t="n">
-        <v>0.667992</v>
+        <v>0.727081</v>
       </c>
       <c r="M74" t="n">
-        <v>0.332008</v>
+        <v>0.272919</v>
       </c>
       <c r="N74" t="n">
-        <v>0.667992</v>
+        <v>0.727081</v>
       </c>
       <c r="O74" t="n">
-        <v>0.332008</v>
+        <v>0.272919</v>
       </c>
       <c r="P74" t="n">
-        <v>0.667992</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="75">
@@ -20220,34 +20220,34 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H75" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I75" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J75" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K75" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L75" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M75" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N75" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="O75" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="P75" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="76">
@@ -20274,34 +20274,34 @@
         <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H76" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I76" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J76" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K76" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L76" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M76" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N76" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O76" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P76" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="77">
@@ -20328,34 +20328,34 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="H77" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="I77" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="J77" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="K77" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="L77" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="M77" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="N77" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="O77" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="P77" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="78">
@@ -20382,34 +20382,34 @@
         <v>6</v>
       </c>
       <c r="G78" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="H78" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="I78" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="J78" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="K78" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="L78" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="M78" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="N78" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="O78" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="P78" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="79">
@@ -20436,34 +20436,34 @@
         <v>6</v>
       </c>
       <c r="G79" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M79" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N79" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="O79" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="P79" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
   </sheetData>
@@ -22994,34 +22994,34 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H5" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I5" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J5" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K5" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L5" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M5" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N5" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O5" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P5" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="6">
@@ -23156,34 +23156,34 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="H8" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="I8" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="J8" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="K8" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="L8" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="M8" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="N8" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="O8" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="P8" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="9">
@@ -23912,10 +23912,10 @@
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H22" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I22" t="n">
         <v>0.308594</v>
@@ -24074,34 +24074,34 @@
         <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H25" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I25" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="J25" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="K25" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L25" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="M25" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="N25" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="O25" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="P25" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="26">
@@ -24776,34 +24776,34 @@
         <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="H38" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="I38" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="J38" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="K38" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="L38" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="M38" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="N38" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
       <c r="O38" t="n">
-        <v>0.576433</v>
+        <v>0.659498</v>
       </c>
       <c r="P38" t="n">
-        <v>0.423567</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="39">
@@ -25262,34 +25262,34 @@
         <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H47" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I47" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J47" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K47" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L47" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M47" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N47" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="O47" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="P47" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="48">
@@ -25532,34 +25532,34 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H52" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I52" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J52" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K52" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L52" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M52" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N52" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O52" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P52" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="53">
@@ -25586,34 +25586,34 @@
         <v>9</v>
       </c>
       <c r="G53" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="H53" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
       <c r="I53" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="J53" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
       <c r="K53" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="L53" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
       <c r="M53" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="N53" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
       <c r="O53" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="P53" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="54">
@@ -26170,28 +26170,28 @@
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H2" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I2" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J2" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K2" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L2" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="M2" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="N2" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="3">
@@ -26218,28 +26218,28 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="I3" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="K3" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="M3" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="4">
@@ -26266,10 +26266,10 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I4" t="n">
         <v>0.361011</v>
@@ -26410,28 +26410,28 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="8">
@@ -26512,22 +26512,22 @@
         <v>0.573034</v>
       </c>
       <c r="I9" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J9" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K9" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L9" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M9" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N9" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="10">
@@ -26938,28 +26938,28 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="19">
@@ -26986,28 +26986,28 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H19" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I19" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J19" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K19" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L19" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M19" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N19" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="20">
@@ -27178,28 +27178,28 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="H23" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="I23" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="J23" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="K23" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="L23" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="M23" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="N23" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="24">
@@ -27322,28 +27322,28 @@
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="27">
@@ -27466,28 +27466,28 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H29" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I29" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J29" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K29" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L29" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="M29" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="N29" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="30">
@@ -30770,28 +30770,28 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="6">
@@ -30962,28 +30962,28 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H9" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I9" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J9" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K9" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L9" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M9" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N9" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="10">
@@ -31202,28 +31202,28 @@
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H14" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I14" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J14" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K14" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L14" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M14" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N14" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="15">
@@ -31394,28 +31394,28 @@
         <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H18" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I18" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J18" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K18" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L18" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M18" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N18" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="19">
@@ -31778,10 +31778,10 @@
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="I26" t="n">
         <v>0.243295</v>
@@ -31922,28 +31922,28 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H29" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I29" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J29" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K29" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L29" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M29" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="N29" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="30">
@@ -32354,16 +32354,16 @@
         <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H38" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I38" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J38" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K38" t="n">
         <v>0.511551</v>
@@ -32450,28 +32450,28 @@
         <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H40" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I40" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J40" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K40" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L40" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M40" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N40" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="41">
@@ -32642,28 +32642,28 @@
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>0.432904</v>
+        <v>0.40884</v>
       </c>
       <c r="H44" t="n">
-        <v>0.567096</v>
+        <v>0.59116</v>
       </c>
       <c r="I44" t="n">
-        <v>0.432904</v>
+        <v>0.40884</v>
       </c>
       <c r="J44" t="n">
-        <v>0.567096</v>
+        <v>0.59116</v>
       </c>
       <c r="K44" t="n">
-        <v>0.432904</v>
+        <v>0.40884</v>
       </c>
       <c r="L44" t="n">
-        <v>0.567096</v>
+        <v>0.59116</v>
       </c>
       <c r="M44" t="n">
-        <v>0.432904</v>
+        <v>0.40884</v>
       </c>
       <c r="N44" t="n">
-        <v>0.567096</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="45">
@@ -33122,28 +33122,28 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K54" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="55">
@@ -45198,28 +45198,28 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H5" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I5" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J5" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K5" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L5" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M5" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N5" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="6">
@@ -45870,28 +45870,28 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="20">
@@ -45918,28 +45918,28 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H20" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I20" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J20" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K20" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L20" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="M20" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="N20" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="21">
@@ -45966,28 +45966,28 @@
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="I21" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="K21" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="M21" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="22">
@@ -46014,28 +46014,28 @@
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="23">
@@ -46110,28 +46110,28 @@
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="25">
@@ -46350,28 +46350,28 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="H29" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="I29" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="J29" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="K29" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="L29" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="M29" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="N29" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="30">
@@ -46686,28 +46686,28 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="H36" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="I36" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="J36" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="K36" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="L36" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="M36" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="N36" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="37">
@@ -47070,28 +47070,28 @@
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H44" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I44" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J44" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K44" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L44" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M44" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N44" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="45">
@@ -54224,16 +54224,16 @@
         <v>0.691406</v>
       </c>
       <c r="K9" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L9" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M9" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N9" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="10">
@@ -54836,28 +54836,28 @@
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I22" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K22" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M22" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="23">
@@ -55028,28 +55028,28 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H26" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I26" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="J26" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="K26" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L26" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="M26" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="N26" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="27">
@@ -56218,28 +56218,28 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H4" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I4" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J4" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K4" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L4" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M4" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N4" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="5">
@@ -56554,28 +56554,28 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="I11" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="K11" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="M11" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="N11" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
     </row>
     <row r="12">
@@ -56986,28 +56986,28 @@
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="21">
@@ -57082,28 +57082,28 @@
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="H22" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="I22" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="J22" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="K22" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="L22" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="M22" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="N22" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="23">
@@ -57274,28 +57274,28 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="H26" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="I26" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="J26" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="K26" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="L26" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="M26" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="N26" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="27">
@@ -58032,28 +58032,28 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H12" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I12" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J12" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K12" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L12" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M12" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N12" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="13">
@@ -58800,28 +58800,28 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="H28" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="I28" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="K28" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L28" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M28" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N28" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="29">
@@ -58896,16 +58896,16 @@
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H30" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I30" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J30" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K30" t="n">
         <v>0.511551</v>
@@ -60074,28 +60074,28 @@
         <v>0.667992</v>
       </c>
       <c r="M12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="P12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="R12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="S12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="T12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="13">
@@ -60716,46 +60716,46 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="23">
@@ -61838,46 +61838,46 @@
         <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="P39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="R39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="S39" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="T39" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="40">
@@ -61970,28 +61970,28 @@
         <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H41" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I41" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J41" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K41" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L41" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M41" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N41" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O41" t="n">
         <v>0.511551</v>
@@ -62102,22 +62102,22 @@
         <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H43" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I43" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J43" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K43" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L43" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M43" t="n">
         <v>0.40884</v>
@@ -63356,34 +63356,34 @@
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H62" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I62" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J62" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K62" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L62" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M62" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N62" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O62" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P62" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="Q62" t="n">
         <v>0.308594</v>
@@ -63554,46 +63554,46 @@
         <v>11</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H65" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J65" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K65" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L65" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M65" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N65" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O65" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P65" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="R65" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="S65" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="T65" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="66">
@@ -63620,46 +63620,46 @@
         <v>6</v>
       </c>
       <c r="G66" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H66" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I66" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J66" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K66" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L66" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="M66" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="N66" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="O66" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="P66" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="R66" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="S66" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="T66" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="67">
@@ -65270,46 +65270,46 @@
         <v>14</v>
       </c>
       <c r="G91" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="H91" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
       <c r="I91" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="J91" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
       <c r="K91" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="L91" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
       <c r="M91" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="N91" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
       <c r="O91" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="P91" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="R91" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
       <c r="S91" t="n">
-        <v>0.94152</v>
+        <v>0.95</v>
       </c>
       <c r="T91" t="n">
-        <v>0.05848</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="92">
@@ -69158,16 +69158,16 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H2" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I2" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J2" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K2" t="n">
         <v>0.308594</v>
@@ -69224,22 +69224,22 @@
         <v>0.691406</v>
       </c>
       <c r="K3" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M3" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N3" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O3" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P3" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="4">
@@ -69428,34 +69428,34 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="8">
@@ -69500,10 +69500,10 @@
         <v>0.837786</v>
       </c>
       <c r="M8" t="n">
-        <v>0.162214</v>
+        <v>0.140351</v>
       </c>
       <c r="N8" t="n">
-        <v>0.837786</v>
+        <v>0.859649</v>
       </c>
       <c r="O8" t="n">
         <v>0.162214</v>
@@ -69644,34 +69644,34 @@
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H11" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I11" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J11" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K11" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L11" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M11" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N11" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O11" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="P11" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="12">
@@ -69716,16 +69716,16 @@
         <v>0.443197</v>
       </c>
       <c r="M12" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N12" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O12" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P12" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="13">
@@ -69860,28 +69860,28 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="I15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="K15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="M15" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="O15" t="n">
         <v>0.7304349999999999</v>
@@ -70100,10 +70100,10 @@
         <v>0.443197</v>
       </c>
       <c r="O19" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P19" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="20">
@@ -70130,34 +70130,34 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="H20" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="I20" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="J20" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="K20" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="L20" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="M20" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="N20" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="O20" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="P20" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="21">
@@ -70346,34 +70346,34 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="H24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="I24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="J24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="K24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="L24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="M24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="N24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="O24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="P24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="25">
@@ -70616,22 +70616,22 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="H29" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="I29" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="J29" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="K29" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="L29" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="M29" t="n">
         <v>0.230483</v>
@@ -70640,10 +70640,10 @@
         <v>0.769517</v>
       </c>
       <c r="O29" t="n">
-        <v>0.230483</v>
+        <v>0.230993</v>
       </c>
       <c r="P29" t="n">
-        <v>0.769517</v>
+        <v>0.769007</v>
       </c>
     </row>
     <row r="30">
@@ -70778,34 +70778,34 @@
         <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.882667</v>
       </c>
       <c r="H32" t="n">
-        <v>0.173653</v>
+        <v>0.117333</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.882667</v>
       </c>
       <c r="J32" t="n">
-        <v>0.173653</v>
+        <v>0.117333</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.882667</v>
       </c>
       <c r="L32" t="n">
-        <v>0.173653</v>
+        <v>0.117333</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.882667</v>
       </c>
       <c r="N32" t="n">
-        <v>0.173653</v>
+        <v>0.117333</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.882667</v>
       </c>
       <c r="P32" t="n">
-        <v>0.173653</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="33">
@@ -70940,34 +70940,34 @@
         <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H35" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I35" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J35" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K35" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L35" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M35" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N35" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="O35" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="P35" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="36">
@@ -70994,34 +70994,34 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
       <c r="I36" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
       <c r="K36" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
       <c r="M36" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
       <c r="O36" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P36" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="37">
@@ -71048,34 +71048,34 @@
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>0.659498</v>
+        <v>0.636364</v>
       </c>
       <c r="H37" t="n">
-        <v>0.340502</v>
+        <v>0.363636</v>
       </c>
       <c r="I37" t="n">
-        <v>0.659498</v>
+        <v>0.636364</v>
       </c>
       <c r="J37" t="n">
-        <v>0.340502</v>
+        <v>0.363636</v>
       </c>
       <c r="K37" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="L37" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="M37" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N37" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="O37" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="P37" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="38">
@@ -71318,34 +71318,34 @@
         <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H42" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I42" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J42" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K42" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L42" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M42" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N42" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O42" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P42" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="43">
@@ -71534,34 +71534,34 @@
         <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="P46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
   </sheetData>
@@ -73208,40 +73208,40 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.74269</v>
+        <v>0.76606</v>
       </c>
       <c r="H9" t="n">
-        <v>0.25731</v>
+        <v>0.23394</v>
       </c>
       <c r="I9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="O9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="P9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="R9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="10">
@@ -74228,40 +74228,40 @@
         <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="I26" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="K26" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="M26" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="O26" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="27">
@@ -74768,40 +74768,40 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="H35" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="I35" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J35" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K35" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L35" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M35" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N35" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="O35" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="P35" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="R35" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="36">
@@ -74828,40 +74828,40 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="H36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="I36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="J36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="K36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="L36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="M36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="N36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="O36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="P36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="R36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="37">
@@ -74888,40 +74888,40 @@
         <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H37" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I37" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J37" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K37" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L37" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M37" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N37" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="O37" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="P37" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="R37" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="38">
@@ -75008,40 +75008,40 @@
         <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="H39" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="I39" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="J39" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="K39" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="L39" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="M39" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="N39" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="O39" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="P39" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="R39" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="40">
@@ -75908,40 +75908,40 @@
         <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>0.036697</v>
+        <v>0.045455</v>
       </c>
       <c r="H54" t="n">
-        <v>0.963303</v>
+        <v>0.954545</v>
       </c>
       <c r="I54" t="n">
-        <v>0.036697</v>
+        <v>0.045455</v>
       </c>
       <c r="J54" t="n">
-        <v>0.963303</v>
+        <v>0.954545</v>
       </c>
       <c r="K54" t="n">
-        <v>0.036697</v>
+        <v>0.045455</v>
       </c>
       <c r="L54" t="n">
-        <v>0.963303</v>
+        <v>0.954545</v>
       </c>
       <c r="M54" t="n">
-        <v>0.036697</v>
+        <v>0.045455</v>
       </c>
       <c r="N54" t="n">
-        <v>0.963303</v>
+        <v>0.954545</v>
       </c>
       <c r="O54" t="n">
-        <v>0.036697</v>
+        <v>0.045455</v>
       </c>
       <c r="P54" t="n">
-        <v>0.963303</v>
+        <v>0.954545</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.036697</v>
+        <v>0.045455</v>
       </c>
       <c r="R54" t="n">
-        <v>0.963303</v>
+        <v>0.954545</v>
       </c>
     </row>
     <row r="55">
@@ -76388,40 +76388,40 @@
         <v>7</v>
       </c>
       <c r="G62" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H62" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I62" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="J62" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="K62" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="L62" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="M62" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="N62" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="O62" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="P62" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="R62" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="63">
@@ -78710,28 +78710,28 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H15" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I15" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J15" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K15" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L15" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M15" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N15" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="16">
@@ -78902,28 +78902,28 @@
         <v>12</v>
       </c>
       <c r="G19" t="n">
+        <v>0.853147</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.146853</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.862069</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.137931</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.882667</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.117333</v>
-      </c>
       <c r="K19" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="L19" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="M19" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="N19" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
     </row>
     <row r="20">
@@ -92370,28 +92370,28 @@
         <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="H38" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="I38" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="J38" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="K38" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="L38" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="M38" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="N38" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
     </row>
     <row r="39">
@@ -92418,28 +92418,28 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H39" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I39" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J39" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K39" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L39" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M39" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N39" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="40">
@@ -92466,28 +92466,28 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H40" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I40" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J40" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K40" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="L40" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="M40" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N40" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="41">
@@ -93224,28 +93224,28 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="H9" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="I9" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="J9" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="K9" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="L9" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="M9" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="N9" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="10">
@@ -93848,10 +93848,10 @@
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>0.762039</v>
+        <v>0.769477</v>
       </c>
       <c r="H22" t="n">
-        <v>0.237961</v>
+        <v>0.230523</v>
       </c>
       <c r="I22" t="n">
         <v>0.769477</v>
@@ -93860,16 +93860,16 @@
         <v>0.230523</v>
       </c>
       <c r="K22" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L22" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M22" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N22" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="23">
@@ -94088,28 +94088,28 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H27" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I27" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J27" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K27" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L27" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M27" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N27" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="28">
@@ -94280,28 +94280,28 @@
         <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H31" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I31" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J31" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K31" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L31" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M31" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N31" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="32">
@@ -94424,28 +94424,28 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.244898</v>
+        <v>0.263158</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.736842</v>
       </c>
       <c r="I34" t="n">
-        <v>0.244898</v>
+        <v>0.263158</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.736842</v>
       </c>
       <c r="K34" t="n">
-        <v>0.244898</v>
+        <v>0.263158</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.736842</v>
       </c>
       <c r="M34" t="n">
-        <v>0.244898</v>
+        <v>0.263158</v>
       </c>
       <c r="N34" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="35">
@@ -94520,28 +94520,28 @@
         <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="H36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="I36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="J36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="K36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="L36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="M36" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="N36" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="37">
@@ -94568,28 +94568,28 @@
         <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="H37" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="J37" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="L37" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="N37" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
   </sheetData>

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -39115,7 +39115,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>0.011765</v>
@@ -39307,7 +39307,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0.036697</v>
@@ -39632,7 +39632,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>1161</v>
@@ -39680,7 +39680,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>1201</v>
@@ -39728,7 +39728,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>1213</v>
@@ -39776,7 +39776,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>1305</v>
@@ -39787,7 +39787,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0.576433</v>
@@ -39824,7 +39824,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>1307</v>
@@ -39872,7 +39872,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>1361</v>
@@ -39920,7 +39920,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>1363</v>
@@ -39968,7 +39968,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>1424</v>
@@ -40016,7 +40016,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>1429</v>
@@ -40064,7 +40064,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
         <v>1461</v>
@@ -40219,7 +40219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0.426966</v>
@@ -40603,7 +40603,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>0.243295</v>
@@ -40939,7 +40939,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>0.511551</v>
@@ -41264,7 +41264,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
         <v>1307</v>
@@ -41312,7 +41312,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
         <v>1361</v>
@@ -41360,7 +41360,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
         <v>1363</v>
@@ -41408,7 +41408,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
         <v>1424</v>
@@ -41456,7 +41456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
         <v>1429</v>
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
         <v>1461</v>

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -69144,7 +69144,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>1194</v>
@@ -69155,7 +69155,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>0.308594</v>
@@ -69198,7 +69198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>1272</v>
@@ -69252,7 +69252,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>1317</v>
@@ -69263,7 +69263,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>0.308594</v>
@@ -69306,7 +69306,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>1378</v>
@@ -69360,7 +69360,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1396</v>
@@ -69414,7 +69414,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>1408</v>
@@ -69468,7 +69468,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>1409</v>
@@ -69479,7 +69479,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0.100437</v>
@@ -69522,7 +69522,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>1412</v>
@@ -69576,7 +69576,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>1455</v>
@@ -69587,7 +69587,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>0.162214</v>
@@ -69630,7 +69630,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>1272</v>
@@ -69684,7 +69684,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>1317</v>
@@ -69695,7 +69695,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>0.533435</v>
@@ -69738,7 +69738,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>1378</v>
@@ -69792,7 +69792,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>1396</v>
@@ -69846,7 +69846,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>1408</v>
@@ -69900,7 +69900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>1409</v>
@@ -69911,7 +69911,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0.283654</v>
@@ -69954,7 +69954,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>1412</v>
@@ -70008,7 +70008,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>1455</v>
@@ -70019,7 +70019,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>0.361011</v>
@@ -70073,7 +70073,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>0.533435</v>
@@ -70289,7 +70289,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0.272919</v>
@@ -70397,7 +70397,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
         <v>0.361011</v>
@@ -70440,7 +70440,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
         <v>1378</v>
@@ -70494,7 +70494,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
         <v>1396</v>
@@ -70548,7 +70548,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>1408</v>
@@ -70602,7 +70602,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
         <v>1409</v>
@@ -70613,7 +70613,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0.243295</v>
@@ -70656,7 +70656,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
         <v>1412</v>
@@ -70710,7 +70710,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
         <v>1455</v>
@@ -70721,7 +70721,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
         <v>0.283654</v>
@@ -70883,7 +70883,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0.577889</v>
@@ -70991,7 +70991,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
         <v>0.6787069999999999</v>
@@ -71099,7 +71099,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
         <v>0.162214</v>
@@ -71207,7 +71207,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>0.260417</v>
@@ -71261,7 +71261,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
         <v>0.100437</v>
@@ -71369,7 +71369,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
         <v>0.185358</v>
@@ -71412,7 +71412,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
         <v>1412</v>
@@ -71466,7 +71466,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
         <v>1455</v>
@@ -71477,7 +71477,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
         <v>0.576433</v>
@@ -71531,7 +71531,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
         <v>0.332008</v>

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -20562,7 +20562,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>1240</v>
@@ -20610,7 +20610,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>1244</v>
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>0.40884</v>
@@ -20658,7 +20658,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>1251</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>1256</v>
@@ -20717,7 +20717,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0.460746</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>1283</v>
@@ -20765,7 +20765,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
         <v>0.556803</v>
@@ -20802,7 +20802,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>1292</v>
@@ -20813,7 +20813,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>0.361446</v>
@@ -20850,7 +20850,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>1308</v>
@@ -20898,7 +20898,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>1358</v>
@@ -20946,7 +20946,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>1443</v>
@@ -21005,7 +21005,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>0.361011</v>
@@ -21101,7 +21101,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>0.432904</v>
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
         <v>0.556803</v>
@@ -21197,7 +21197,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0.361011</v>
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>1251</v>
@@ -21426,7 +21426,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>1256</v>
@@ -21437,7 +21437,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0.556803</v>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>1283</v>
@@ -21485,7 +21485,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
         <v>0.6787069999999999</v>
@@ -21522,7 +21522,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
         <v>1292</v>
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0.432904</v>
@@ -21570,7 +21570,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
         <v>1308</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
         <v>1358</v>
@@ -21666,7 +21666,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>1443</v>
@@ -21725,7 +21725,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0.6787069999999999</v>
@@ -21773,7 +21773,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
         <v>0.769477</v>
@@ -21821,7 +21821,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0.659498</v>
@@ -22002,7 +22002,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
         <v>1283</v>
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
         <v>0.659498</v>
@@ -22050,7 +22050,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
         <v>1292</v>
@@ -22061,7 +22061,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>0.361446</v>
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
         <v>1308</v>
@@ -22146,7 +22146,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
         <v>1358</v>
@@ -22194,7 +22194,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
         <v>1443</v>
@@ -22242,7 +22242,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
         <v>1292</v>
@@ -22253,7 +22253,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>0.332008</v>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
         <v>1308</v>
@@ -22338,7 +22338,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
         <v>1358</v>
@@ -22386,7 +22386,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
         <v>1443</v>
@@ -22434,7 +22434,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
         <v>1308</v>
@@ -22482,7 +22482,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
         <v>1358</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
         <v>1443</v>

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -16278,34 +16278,34 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H2" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I2" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J2" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K2" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L2" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M2" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N2" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="O2" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="P2" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="3">
@@ -16332,34 +16332,34 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H3" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J3" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K3" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="L3" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="M3" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N3" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="O3" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="P3" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="4">
@@ -16404,16 +16404,16 @@
         <v>0.3379</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N4" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P4" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="5">
@@ -16548,34 +16548,34 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H7" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I7" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J7" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K7" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="M7" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="N7" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="O7" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="P7" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="8">
@@ -16656,34 +16656,34 @@
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="10">
@@ -16710,34 +16710,34 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H10" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J10" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N10" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P10" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="11">
@@ -16818,34 +16818,34 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O12" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="P12" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="13">
@@ -17088,34 +17088,34 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H17" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I17" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J17" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K17" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L17" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M17" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N17" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O17" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P17" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="18">
@@ -17682,34 +17682,34 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H28" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I28" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J28" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K28" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L28" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M28" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N28" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O28" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="P28" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="29">
@@ -17898,34 +17898,34 @@
         <v>7</v>
       </c>
       <c r="G32" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H32" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I32" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J32" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K32" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L32" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M32" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N32" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O32" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P32" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="33">
@@ -18600,34 +18600,34 @@
         <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H45" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I45" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J45" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K45" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L45" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M45" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N45" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O45" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P45" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="46">
@@ -18978,34 +18978,34 @@
         <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H52" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I52" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J52" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K52" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L52" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M52" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N52" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O52" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P52" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="53">
@@ -19032,34 +19032,34 @@
         <v>12</v>
       </c>
       <c r="G53" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="H53" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="I53" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="J53" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="K53" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="L53" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="M53" t="n">
-        <v>0.94152</v>
+        <v>0.890166</v>
       </c>
       <c r="N53" t="n">
-        <v>0.05848</v>
+        <v>0.109834</v>
       </c>
       <c r="O53" t="n">
-        <v>0.94152</v>
+        <v>0.890166</v>
       </c>
       <c r="P53" t="n">
-        <v>0.05848</v>
+        <v>0.109834</v>
       </c>
     </row>
     <row r="54">
@@ -19140,34 +19140,34 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H55" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I55" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J55" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K55" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L55" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M55" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N55" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O55" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="P55" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="56">
@@ -19248,34 +19248,34 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="H57" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="I57" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="J57" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="K57" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="L57" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="M57" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="N57" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="O57" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="P57" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="58">
@@ -19302,34 +19302,34 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="I58" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="K58" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="M58" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="O58" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P58" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="59">
@@ -19356,34 +19356,34 @@
         <v>12</v>
       </c>
       <c r="G59" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="H59" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="I59" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="J59" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="K59" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="L59" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="M59" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="N59" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="O59" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="P59" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="60">
@@ -19518,34 +19518,34 @@
         <v>7</v>
       </c>
       <c r="G62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O62" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P62" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="63">
@@ -19572,34 +19572,34 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H63" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I63" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J63" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K63" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L63" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M63" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N63" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O63" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P63" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="64">
@@ -19626,34 +19626,34 @@
         <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H64" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I64" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="J64" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="K64" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L64" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="M64" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="N64" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="O64" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="P64" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="65">
@@ -19788,34 +19788,34 @@
         <v>7</v>
       </c>
       <c r="G67" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="H67" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="I67" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="J67" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="K67" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="L67" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="M67" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="N67" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="O67" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="P67" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="68">
@@ -20328,34 +20328,34 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H77" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I77" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J77" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K77" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L77" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M77" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N77" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O77" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P77" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="78">
@@ -23102,34 +23102,34 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J7" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L7" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="N7" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="P7" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="8">
@@ -23696,34 +23696,34 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="O18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="P18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="19">
@@ -23804,34 +23804,34 @@
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="H20" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
       <c r="I20" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="J20" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
       <c r="K20" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="L20" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
       <c r="M20" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="N20" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
       <c r="O20" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="P20" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="21">
@@ -24020,34 +24020,34 @@
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0.185358</v>
+        <v>0.243295</v>
       </c>
       <c r="H24" t="n">
-        <v>0.814642</v>
+        <v>0.756705</v>
       </c>
       <c r="I24" t="n">
-        <v>0.185358</v>
+        <v>0.243295</v>
       </c>
       <c r="J24" t="n">
-        <v>0.814642</v>
+        <v>0.756705</v>
       </c>
       <c r="K24" t="n">
-        <v>0.185358</v>
+        <v>0.243295</v>
       </c>
       <c r="L24" t="n">
-        <v>0.814642</v>
+        <v>0.756705</v>
       </c>
       <c r="M24" t="n">
-        <v>0.185358</v>
+        <v>0.243295</v>
       </c>
       <c r="N24" t="n">
-        <v>0.814642</v>
+        <v>0.756705</v>
       </c>
       <c r="O24" t="n">
-        <v>0.185358</v>
+        <v>0.243295</v>
       </c>
       <c r="P24" t="n">
-        <v>0.814642</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="25">
@@ -24884,34 +24884,34 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="H40" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="I40" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="J40" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="K40" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="L40" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="M40" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="N40" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="O40" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="P40" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="41">
@@ -24938,34 +24938,34 @@
         <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N41" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="P41" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="42">
@@ -24992,34 +24992,34 @@
         <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="P42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="43">
@@ -25316,34 +25316,34 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H48" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J48" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L48" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N48" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P48" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="49">
@@ -25370,34 +25370,34 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H49" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I49" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J49" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K49" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L49" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M49" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N49" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O49" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P49" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="50">
@@ -25424,34 +25424,34 @@
         <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H50" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I50" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J50" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K50" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L50" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M50" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N50" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O50" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P50" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="51">
@@ -25640,34 +25640,34 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="H54" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="J54" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="L54" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="N54" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="P54" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="55">
@@ -25748,34 +25748,34 @@
         <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I56" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K56" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M56" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O56" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P56" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
   </sheetData>
@@ -53972,28 +53972,28 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="H4" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="I4" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="J4" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="K4" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="L4" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="M4" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="N4" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="5">
@@ -54788,28 +54788,28 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H21" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J21" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L21" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N21" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="22">
@@ -54884,28 +54884,28 @@
         <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.94152</v>
+        <v>0.889624</v>
       </c>
       <c r="H23" t="n">
-        <v>0.05848</v>
+        <v>0.110376</v>
       </c>
       <c r="I23" t="n">
-        <v>0.94152</v>
+        <v>0.889624</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05848</v>
+        <v>0.110376</v>
       </c>
       <c r="K23" t="n">
-        <v>0.94152</v>
+        <v>0.898925</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05848</v>
+        <v>0.101075</v>
       </c>
       <c r="M23" t="n">
-        <v>0.94152</v>
+        <v>0.898925</v>
       </c>
       <c r="N23" t="n">
-        <v>0.05848</v>
+        <v>0.101075</v>
       </c>
     </row>
     <row r="24">
@@ -55028,28 +55028,28 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H26" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I26" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J26" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K26" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L26" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M26" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N26" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="27">
@@ -55124,28 +55124,28 @@
         <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H28" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I28" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J28" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K28" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L28" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M28" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N28" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="29">
@@ -55226,22 +55226,22 @@
         <v>0.423567</v>
       </c>
       <c r="I30" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J30" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K30" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L30" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M30" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N30" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="31">
@@ -56218,28 +56218,28 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I4" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J4" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K4" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L4" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M4" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N4" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="5">
@@ -56410,28 +56410,28 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H8" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I8" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J8" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K8" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L8" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M8" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N8" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="9">
@@ -56890,28 +56890,28 @@
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H18" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I18" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J18" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K18" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L18" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M18" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N18" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="19">
@@ -57082,28 +57082,28 @@
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H22" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I22" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J22" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K22" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L22" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M22" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N22" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="23">
@@ -57130,28 +57130,28 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H23" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I23" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J23" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K23" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L23" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M23" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N23" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="24">
@@ -57370,28 +57370,28 @@
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.677665</v>
+        <v>0.6621</v>
       </c>
       <c r="H28" t="n">
-        <v>0.322335</v>
+        <v>0.3379</v>
       </c>
       <c r="I28" t="n">
-        <v>0.677665</v>
+        <v>0.6621</v>
       </c>
       <c r="J28" t="n">
-        <v>0.322335</v>
+        <v>0.3379</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L28" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N28" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="29">
@@ -60056,46 +60056,46 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H12" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I12" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J12" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K12" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L12" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M12" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N12" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O12" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P12" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="R12" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="S12" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="T12" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="13">
@@ -61772,46 +61772,46 @@
         <v>13</v>
       </c>
       <c r="G38" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H38" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I38" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J38" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K38" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L38" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M38" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N38" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O38" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P38" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="R38" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="S38" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="T38" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="39">
@@ -61904,46 +61904,46 @@
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H40" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I40" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J40" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K40" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L40" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M40" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N40" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="O40" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="P40" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="R40" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="S40" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="T40" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="41">
@@ -61970,46 +61970,46 @@
         <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="H41" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="I41" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="J41" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="K41" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="L41" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="M41" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="N41" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="O41" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="P41" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="R41" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="S41" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="T41" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="42">
@@ -62066,16 +62066,16 @@
         <v>0.638554</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="R42" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="S42" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="T42" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="43">
@@ -62300,46 +62300,46 @@
         <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H46" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I46" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J46" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K46" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L46" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M46" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N46" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O46" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P46" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="R46" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="S46" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="T46" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="47">
@@ -62828,46 +62828,46 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H54" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I54" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J54" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K54" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L54" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M54" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N54" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="O54" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="P54" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="R54" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="S54" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="T54" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="55">
@@ -63818,46 +63818,46 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H69" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I69" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J69" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K69" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L69" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M69" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N69" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O69" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P69" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="R69" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="S69" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="T69" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="70">
@@ -64214,46 +64214,46 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="H75" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="I75" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="J75" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="K75" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="L75" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="M75" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="N75" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="O75" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="P75" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="R75" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="S75" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="T75" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="76">
@@ -64544,46 +64544,46 @@
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H80" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I80" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J80" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K80" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L80" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M80" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N80" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O80" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P80" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="R80" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="S80" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="T80" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="81">
@@ -64808,46 +64808,46 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H84" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I84" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J84" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K84" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L84" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M84" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N84" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O84" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P84" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="R84" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="S84" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="T84" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="85">
@@ -65006,46 +65006,46 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="H87" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="I87" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="J87" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="K87" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="L87" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="M87" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="N87" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="O87" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="P87" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="R87" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="S87" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="T87" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="88">
@@ -65270,46 +65270,46 @@
         <v>14</v>
       </c>
       <c r="G91" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="H91" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="I91" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="J91" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="K91" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="L91" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="M91" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="N91" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="O91" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="P91" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="R91" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="S91" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="T91" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
     </row>
     <row r="92">
@@ -65876,34 +65876,34 @@
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="M9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="O9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="10">
@@ -66200,34 +66200,34 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H15" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I15" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J15" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K15" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L15" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M15" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N15" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O15" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P15" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="16">
@@ -66632,34 +66632,34 @@
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H23" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I23" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="J23" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="K23" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L23" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="M23" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="N23" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="O23" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="P23" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="24">
@@ -66686,34 +66686,34 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.243295</v>
+        <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>0.756705</v>
+        <v>0.75</v>
       </c>
       <c r="I24" t="n">
-        <v>0.243295</v>
+        <v>0.25</v>
       </c>
       <c r="J24" t="n">
-        <v>0.756705</v>
+        <v>0.75</v>
       </c>
       <c r="K24" t="n">
-        <v>0.243295</v>
+        <v>0.25</v>
       </c>
       <c r="L24" t="n">
-        <v>0.756705</v>
+        <v>0.75</v>
       </c>
       <c r="M24" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="N24" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="O24" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="P24" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="25">
@@ -66740,34 +66740,34 @@
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="26">
@@ -66794,34 +66794,34 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H26" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J26" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K26" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L26" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M26" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N26" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O26" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P26" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="27">
@@ -66848,34 +66848,34 @@
         <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H27" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J27" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K27" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L27" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M27" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N27" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="O27" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="P27" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="28">
@@ -66902,34 +66902,34 @@
         <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="29">
@@ -66956,34 +66956,34 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="30">
@@ -67010,34 +67010,34 @@
         <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="H30" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="I30" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="J30" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="K30" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="L30" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="M30" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="N30" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="O30" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="P30" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="31">
@@ -67226,34 +67226,34 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H34" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I34" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J34" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K34" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L34" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M34" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N34" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="O34" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="P34" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="35">
@@ -67334,34 +67334,34 @@
         <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="H36" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="I36" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="J36" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="K36" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="L36" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="M36" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="N36" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
       <c r="O36" t="n">
-        <v>0.769477</v>
+        <v>0.80786</v>
       </c>
       <c r="P36" t="n">
-        <v>0.230523</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="37">
@@ -68306,34 +68306,34 @@
         <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="I54" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="K54" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="M54" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="O54" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P54" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="55">
@@ -68522,22 +68522,22 @@
         <v>12</v>
       </c>
       <c r="G58" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="K58" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="M58" t="n">
         <v>0.7241379999999999</v>
@@ -68546,10 +68546,10 @@
         <v>0.275862</v>
       </c>
       <c r="O58" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.729978</v>
       </c>
       <c r="P58" t="n">
-        <v>0.275862</v>
+        <v>0.270022</v>
       </c>
     </row>
     <row r="59">
@@ -68846,34 +68846,34 @@
         <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H64" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I64" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J64" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K64" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L64" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M64" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N64" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O64" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P64" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="65">
@@ -73208,40 +73208,40 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="R9" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="10">
@@ -73388,10 +73388,10 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.952055</v>
+        <v>0.971631</v>
       </c>
       <c r="H12" t="n">
-        <v>0.047945</v>
+        <v>0.028369</v>
       </c>
       <c r="I12" t="n">
         <v>0.971631</v>
@@ -74048,40 +74048,40 @@
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="H23" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="I23" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J23" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K23" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L23" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M23" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N23" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="O23" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="P23" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="R23" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="24">
@@ -74288,40 +74288,40 @@
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="R27" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="28">
@@ -74408,40 +74408,40 @@
         <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="H29" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="I29" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J29" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K29" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L29" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M29" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N29" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="O29" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="P29" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="R29" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="30">
@@ -74468,40 +74468,40 @@
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="H30" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="I30" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="J30" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="K30" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="L30" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="N30" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="O30" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="P30" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="R30" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="31">
@@ -74528,10 +74528,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H31" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I31" t="n">
         <v>0.460746</v>
@@ -74828,40 +74828,40 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="H36" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="I36" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="J36" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="K36" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="L36" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="M36" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="N36" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="O36" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="P36" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="R36" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="37">
@@ -76148,22 +76148,22 @@
         <v>3</v>
       </c>
       <c r="G58" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="H58" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="I58" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="J58" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="K58" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="L58" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="M58" t="n">
         <v>0.185358</v>
@@ -76448,40 +76448,40 @@
         <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>0.361011</v>
+        <v>0.40625</v>
       </c>
       <c r="H63" t="n">
-        <v>0.638989</v>
+        <v>0.59375</v>
       </c>
       <c r="I63" t="n">
-        <v>0.361011</v>
+        <v>0.40625</v>
       </c>
       <c r="J63" t="n">
-        <v>0.638989</v>
+        <v>0.59375</v>
       </c>
       <c r="K63" t="n">
-        <v>0.361011</v>
+        <v>0.40625</v>
       </c>
       <c r="L63" t="n">
-        <v>0.638989</v>
+        <v>0.59375</v>
       </c>
       <c r="M63" t="n">
-        <v>0.361011</v>
+        <v>0.4</v>
       </c>
       <c r="N63" t="n">
-        <v>0.638989</v>
+        <v>0.6</v>
       </c>
       <c r="O63" t="n">
-        <v>0.361011</v>
+        <v>0.4</v>
       </c>
       <c r="P63" t="n">
-        <v>0.638989</v>
+        <v>0.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.361011</v>
+        <v>0.4</v>
       </c>
       <c r="R63" t="n">
-        <v>0.638989</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="64">
@@ -76688,40 +76688,40 @@
         <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="H67" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="I67" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="J67" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="K67" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="L67" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="M67" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="N67" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="O67" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="P67" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="R67" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
     </row>
   </sheetData>
@@ -91266,28 +91266,28 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="H15" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="I15" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="J15" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="K15" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="L15" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="M15" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="N15" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="16">
@@ -91746,28 +91746,28 @@
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H25" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I25" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J25" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K25" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L25" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M25" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N25" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="26">
@@ -91890,28 +91890,28 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="H28" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="I28" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="J28" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="K28" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="L28" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="M28" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="N28" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="29">
@@ -92082,28 +92082,28 @@
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H32" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I32" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J32" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K32" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L32" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M32" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N32" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="33">
@@ -92130,28 +92130,28 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="H33" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="I33" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="J33" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="K33" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="L33" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="M33" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="N33" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="34">
@@ -92178,28 +92178,28 @@
         <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H34" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J34" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L34" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N34" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="35">
@@ -92226,28 +92226,28 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H35" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I35" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J35" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K35" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L35" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M35" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N35" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="36">
@@ -92274,28 +92274,28 @@
         <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H36" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I36" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J36" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K36" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L36" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M36" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N36" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="37">
@@ -92562,28 +92562,28 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="H42" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
       <c r="I42" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="J42" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
       <c r="K42" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="L42" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
       <c r="M42" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="N42" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="43">
@@ -92610,28 +92610,28 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H43" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J43" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L43" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N43" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="44">

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -6022,10 +6022,10 @@
         <v>0.146853</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="10">
@@ -7072,40 +7072,40 @@
         <v>16</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="28">
@@ -7552,22 +7552,22 @@
         <v>17</v>
       </c>
       <c r="G35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K35" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M35" t="n">
         <v>0.8263470000000001</v>
@@ -7852,22 +7852,22 @@
         <v>15</v>
       </c>
       <c r="G40" t="n">
-        <v>0.74269</v>
+        <v>0.749711</v>
       </c>
       <c r="H40" t="n">
-        <v>0.25731</v>
+        <v>0.250289</v>
       </c>
       <c r="I40" t="n">
-        <v>0.74269</v>
+        <v>0.749711</v>
       </c>
       <c r="J40" t="n">
-        <v>0.25731</v>
+        <v>0.250289</v>
       </c>
       <c r="K40" t="n">
-        <v>0.74269</v>
+        <v>0.749711</v>
       </c>
       <c r="L40" t="n">
-        <v>0.25731</v>
+        <v>0.250289</v>
       </c>
       <c r="M40" t="n">
         <v>0.74269</v>
@@ -8632,40 +8632,40 @@
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="H53" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="I53" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="J53" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="K53" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="L53" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="M53" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="N53" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="O53" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="P53" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="R53" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
     </row>
     <row r="54">
@@ -8812,40 +8812,40 @@
         <v>16</v>
       </c>
       <c r="G56" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="H56" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="I56" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="J56" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="K56" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="L56" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="M56" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="N56" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="O56" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="P56" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="R56" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="57">
@@ -10192,34 +10192,34 @@
         <v>15</v>
       </c>
       <c r="G79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="J79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="K79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="L79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="M79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="N79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="O79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="P79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="Q79" t="n">
         <v>0.803419</v>
@@ -10312,40 +10312,40 @@
         <v>16</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="H81" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="J81" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="K81" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="L81" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="N81" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="O81" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="P81" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="R81" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="82">
@@ -11452,34 +11452,34 @@
         <v>15</v>
       </c>
       <c r="G100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="I100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="K100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L100" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="M100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N100" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="O100" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="P100" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="Q100" t="n">
         <v>0.7241379999999999</v>
@@ -12292,22 +12292,22 @@
         <v>14</v>
       </c>
       <c r="G114" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H114" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I114" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J114" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K114" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L114" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="M114" t="n">
         <v>0.659498</v>
@@ -12532,40 +12532,40 @@
         <v>5</v>
       </c>
       <c r="G118" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="H118" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="I118" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="J118" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="K118" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="L118" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="M118" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="N118" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="O118" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="P118" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.244898</v>
+        <v>0.263158</v>
       </c>
       <c r="R118" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="119">
@@ -12592,40 +12592,40 @@
         <v>16</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="K119" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L119" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="M119" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N119" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="O119" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="P119" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="R119" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
     </row>
     <row r="120">
@@ -12652,40 +12652,40 @@
         <v>18</v>
       </c>
       <c r="G120" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="H120" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="I120" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="J120" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="K120" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="L120" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="M120" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="N120" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="O120" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="P120" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="R120" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="121">
@@ -13252,40 +13252,40 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>0.272919</v>
+        <v>0.244898</v>
       </c>
       <c r="H130" t="n">
-        <v>0.727081</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>0.272919</v>
+        <v>0.244898</v>
       </c>
       <c r="J130" t="n">
-        <v>0.727081</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K130" t="n">
-        <v>0.272919</v>
+        <v>0.244898</v>
       </c>
       <c r="L130" t="n">
-        <v>0.727081</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M130" t="n">
-        <v>0.272919</v>
+        <v>0.244898</v>
       </c>
       <c r="N130" t="n">
-        <v>0.727081</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="O130" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="P130" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="R130" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="131">
@@ -13312,40 +13312,40 @@
         <v>13</v>
       </c>
       <c r="G131" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="H131" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="I131" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="J131" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="K131" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="L131" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="M131" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="N131" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="O131" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="P131" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="R131" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="132">
@@ -13372,40 +13372,40 @@
         <v>12</v>
       </c>
       <c r="G132" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H132" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I132" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J132" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K132" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L132" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M132" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N132" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O132" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P132" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="R132" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="133">
@@ -13432,40 +13432,40 @@
         <v>5</v>
       </c>
       <c r="G133" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="H133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="I133" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="J133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="K133" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="L133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="M133" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="N133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="O133" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="P133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="R133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="134">
@@ -16548,34 +16548,34 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="H7" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="I7" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="J7" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="K7" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="M7" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="N7" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="O7" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="P7" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="8">
@@ -17088,34 +17088,34 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H17" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I17" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J17" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K17" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L17" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M17" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N17" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O17" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P17" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="18">
@@ -18600,34 +18600,34 @@
         <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H45" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I45" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J45" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K45" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L45" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M45" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N45" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O45" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P45" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="46">
@@ -19050,16 +19050,16 @@
         <v>0.117333</v>
       </c>
       <c r="M53" t="n">
-        <v>0.890166</v>
+        <v>0.882667</v>
       </c>
       <c r="N53" t="n">
-        <v>0.109834</v>
+        <v>0.117333</v>
       </c>
       <c r="O53" t="n">
-        <v>0.890166</v>
+        <v>0.882667</v>
       </c>
       <c r="P53" t="n">
-        <v>0.109834</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="54">
@@ -19356,34 +19356,34 @@
         <v>12</v>
       </c>
       <c r="G59" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H59" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I59" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J59" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K59" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L59" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M59" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N59" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O59" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P59" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="60">
@@ -19464,34 +19464,34 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H61" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J61" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L61" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M61" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N61" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P61" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="62">
@@ -19572,34 +19572,34 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H63" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I63" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J63" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K63" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L63" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M63" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N63" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O63" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P63" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="64">
@@ -19626,34 +19626,34 @@
         <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H64" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I64" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J64" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K64" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L64" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M64" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N64" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O64" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P64" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="65">
@@ -21056,28 +21056,28 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H12" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I12" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J12" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K12" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L12" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M12" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N12" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="13">
@@ -21122,10 +21122,10 @@
         <v>0.567096</v>
       </c>
       <c r="M13" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="N13" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="14">
@@ -21152,28 +21152,28 @@
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H14" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I14" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J14" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K14" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L14" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M14" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N14" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="15">
@@ -22304,28 +22304,28 @@
         <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H38" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I38" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J38" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K38" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L38" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M38" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N38" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="39">
@@ -22352,22 +22352,22 @@
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="H39" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="J39" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="L39" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M39" t="n">
         <v>0.243295</v>
@@ -22400,28 +22400,28 @@
         <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H40" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I40" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J40" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K40" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L40" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M40" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N40" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="41">
@@ -23696,34 +23696,34 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="19">
@@ -23816,22 +23816,22 @@
         <v>0.492424</v>
       </c>
       <c r="K20" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="L20" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="M20" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="N20" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="O20" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="P20" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="21">
@@ -24884,34 +24884,34 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="H40" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="I40" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="J40" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="K40" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="L40" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="M40" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="N40" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="O40" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="P40" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="41">
@@ -25640,34 +25640,34 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.244898</v>
+        <v>0.260417</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.739583</v>
       </c>
       <c r="I54" t="n">
-        <v>0.244898</v>
+        <v>0.260417</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.739583</v>
       </c>
       <c r="K54" t="n">
-        <v>0.244898</v>
+        <v>0.25</v>
       </c>
       <c r="L54" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.75</v>
       </c>
       <c r="M54" t="n">
-        <v>0.244898</v>
+        <v>0.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.75</v>
       </c>
       <c r="O54" t="n">
-        <v>0.244898</v>
+        <v>0.25</v>
       </c>
       <c r="P54" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="55">
@@ -25748,34 +25748,34 @@
         <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M56" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O56" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P56" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
   </sheetData>
@@ -26458,28 +26458,28 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H8" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I8" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J8" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K8" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L8" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M8" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N8" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="9">
@@ -26554,28 +26554,28 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I10" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J10" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K10" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L10" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M10" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N10" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="11">
@@ -26842,28 +26842,28 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H16" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I16" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J16" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K16" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L16" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M16" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N16" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="17">
@@ -26938,28 +26938,28 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="19">
@@ -27562,28 +27562,28 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="H31" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="I31" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J31" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K31" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L31" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M31" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N31" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="32">
@@ -27994,28 +27994,28 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="H40" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="I40" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J40" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K40" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L40" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M40" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N40" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="41">
@@ -28042,28 +28042,28 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="H41" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="J41" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="L41" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="N41" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="42">
@@ -28240,22 +28240,22 @@
         <v>0.539254</v>
       </c>
       <c r="I45" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J45" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K45" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L45" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M45" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N45" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="46">
@@ -33794,34 +33794,34 @@
         <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H10" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I10" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J10" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K10" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L10" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M10" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N10" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O10" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P10" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="11">
@@ -33848,34 +33848,34 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="H11" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="I11" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="J11" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="K11" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="L11" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="M11" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="N11" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="O11" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="P11" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="12">
@@ -33902,34 +33902,34 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H12" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I12" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J12" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K12" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L12" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M12" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N12" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="O12" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="P12" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="13">
@@ -34496,34 +34496,34 @@
         <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H23" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I23" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J23" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K23" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L23" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M23" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N23" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O23" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="P23" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="24">
@@ -34550,34 +34550,34 @@
         <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="H24" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="I24" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="J24" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="K24" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="L24" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="M24" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="N24" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="O24" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="P24" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="25">
@@ -34712,34 +34712,34 @@
         <v>12</v>
       </c>
       <c r="G27" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="H27" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="I27" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="J27" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="K27" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="L27" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="M27" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="N27" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="O27" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="P27" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="28">
@@ -35252,28 +35252,28 @@
         <v>14</v>
       </c>
       <c r="G37" t="n">
-        <v>0.952055</v>
+        <v>0.95</v>
       </c>
       <c r="H37" t="n">
-        <v>0.047945</v>
+        <v>0.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.952055</v>
+        <v>0.95</v>
       </c>
       <c r="J37" t="n">
-        <v>0.047945</v>
+        <v>0.05</v>
       </c>
       <c r="K37" t="n">
-        <v>0.952055</v>
+        <v>0.95</v>
       </c>
       <c r="L37" t="n">
-        <v>0.047945</v>
+        <v>0.05</v>
       </c>
       <c r="M37" t="n">
-        <v>0.952055</v>
+        <v>0.95</v>
       </c>
       <c r="N37" t="n">
-        <v>0.047945</v>
+        <v>0.05</v>
       </c>
       <c r="O37" t="n">
         <v>0.95</v>
@@ -35414,34 +35414,34 @@
         <v>13</v>
       </c>
       <c r="G40" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="I40" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="J40" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="K40" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="L40" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="M40" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="N40" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="O40" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="P40" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="41">
@@ -35738,34 +35738,34 @@
         <v>11</v>
       </c>
       <c r="G46" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H46" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I46" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J46" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K46" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L46" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M46" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N46" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O46" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="P46" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="47">
@@ -35846,34 +35846,34 @@
         <v>14</v>
       </c>
       <c r="G48" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="H48" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="I48" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="J48" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="K48" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="L48" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="M48" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="N48" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="O48" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="P48" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="49">
@@ -35954,34 +35954,34 @@
         <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H50" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I50" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J50" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K50" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L50" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M50" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N50" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="O50" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="P50" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="51">
@@ -36008,34 +36008,34 @@
         <v>13</v>
       </c>
       <c r="G51" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H51" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I51" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J51" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K51" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L51" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M51" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N51" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O51" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="P51" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="52">
@@ -36224,34 +36224,34 @@
         <v>15</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="H55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="J55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="L55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="N55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="P55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="56">
@@ -37196,34 +37196,34 @@
         <v>11</v>
       </c>
       <c r="G73" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H73" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I73" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J73" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K73" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L73" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M73" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N73" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O73" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P73" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="74">
@@ -37790,34 +37790,34 @@
         <v>12</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K84" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N84" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O84" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P84" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="85">
@@ -38114,34 +38114,34 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H90" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I90" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J90" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K90" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L90" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M90" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N90" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O90" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P90" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="91">
@@ -38168,34 +38168,34 @@
         <v>13</v>
       </c>
       <c r="G91" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="H91" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="I91" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="J91" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="K91" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="L91" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="M91" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="N91" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="O91" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="P91" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="92">
@@ -38222,34 +38222,34 @@
         <v>10</v>
       </c>
       <c r="G92" t="n">
-        <v>0.556803</v>
+        <v>0.577889</v>
       </c>
       <c r="H92" t="n">
-        <v>0.443197</v>
+        <v>0.422111</v>
       </c>
       <c r="I92" t="n">
-        <v>0.556803</v>
+        <v>0.577889</v>
       </c>
       <c r="J92" t="n">
-        <v>0.443197</v>
+        <v>0.422111</v>
       </c>
       <c r="K92" t="n">
-        <v>0.556803</v>
+        <v>0.577889</v>
       </c>
       <c r="L92" t="n">
-        <v>0.443197</v>
+        <v>0.422111</v>
       </c>
       <c r="M92" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N92" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="O92" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="P92" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="93">
@@ -38276,34 +38276,34 @@
         <v>14</v>
       </c>
       <c r="G93" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J93" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L93" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M93" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N93" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O93" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P93" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="94">
@@ -38330,34 +38330,34 @@
         <v>2</v>
       </c>
       <c r="G94" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H94" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I94" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J94" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K94" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L94" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M94" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N94" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O94" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P94" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="95">
@@ -38384,34 +38384,34 @@
         <v>12</v>
       </c>
       <c r="G95" t="n">
-        <v>0.556803</v>
+        <v>0.577889</v>
       </c>
       <c r="H95" t="n">
-        <v>0.443197</v>
+        <v>0.422111</v>
       </c>
       <c r="I95" t="n">
-        <v>0.556803</v>
+        <v>0.577889</v>
       </c>
       <c r="J95" t="n">
-        <v>0.443197</v>
+        <v>0.422111</v>
       </c>
       <c r="K95" t="n">
-        <v>0.556803</v>
+        <v>0.577889</v>
       </c>
       <c r="L95" t="n">
-        <v>0.443197</v>
+        <v>0.422111</v>
       </c>
       <c r="M95" t="n">
-        <v>0.556803</v>
+        <v>0.577889</v>
       </c>
       <c r="N95" t="n">
-        <v>0.443197</v>
+        <v>0.422111</v>
       </c>
       <c r="O95" t="n">
-        <v>0.556803</v>
+        <v>0.577889</v>
       </c>
       <c r="P95" t="n">
-        <v>0.443197</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="96">
@@ -38546,34 +38546,34 @@
         <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="H98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="J98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="L98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="N98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="O98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="P98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="99">
@@ -38600,28 +38600,28 @@
         <v>12</v>
       </c>
       <c r="G99" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H99" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I99" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J99" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K99" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L99" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M99" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N99" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O99" t="n">
         <v>0.511551</v>
@@ -38654,34 +38654,34 @@
         <v>13</v>
       </c>
       <c r="G100" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="H100" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
       <c r="I100" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="J100" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
       <c r="K100" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="L100" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
       <c r="M100" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="N100" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
       <c r="O100" t="n">
-        <v>0.533435</v>
+        <v>0.511551</v>
       </c>
       <c r="P100" t="n">
-        <v>0.466565</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="101">
@@ -38762,34 +38762,34 @@
         <v>12</v>
       </c>
       <c r="G102" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H102" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I102" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J102" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K102" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L102" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M102" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N102" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O102" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="P102" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="103">
@@ -38816,34 +38816,34 @@
         <v>13</v>
       </c>
       <c r="G103" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H103" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I103" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J103" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K103" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L103" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M103" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N103" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O103" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P103" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="104">
@@ -42446,22 +42446,22 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H4" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I4" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J4" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K4" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L4" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="5">
@@ -42866,22 +42866,22 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H14" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I14" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J14" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K14" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L14" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="15">
@@ -43076,10 +43076,10 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H19" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I19" t="n">
         <v>0.308594</v>
@@ -43202,22 +43202,22 @@
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H22" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J22" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L22" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="23">
@@ -43244,22 +43244,22 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H23" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I23" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J23" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K23" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L23" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="24">
@@ -56410,28 +56410,28 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H8" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I8" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K8" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M8" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N8" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="9">
@@ -56554,22 +56554,22 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.952055</v>
+        <v>0.95</v>
       </c>
       <c r="H11" t="n">
-        <v>0.047945</v>
+        <v>0.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.952055</v>
+        <v>0.95</v>
       </c>
       <c r="J11" t="n">
-        <v>0.047945</v>
+        <v>0.05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.952055</v>
+        <v>0.95</v>
       </c>
       <c r="L11" t="n">
-        <v>0.047945</v>
+        <v>0.05</v>
       </c>
       <c r="M11" t="n">
         <v>0.952055</v>
@@ -56650,28 +56650,28 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H13" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I13" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J13" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K13" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L13" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M13" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N13" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="14">
@@ -57130,28 +57130,28 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H23" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I23" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J23" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K23" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L23" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M23" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N23" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="24">
@@ -57226,28 +57226,28 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M25" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N25" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="26">
@@ -57418,28 +57418,28 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H29" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I29" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="J29" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="K29" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L29" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="M29" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="N29" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
   </sheetData>
@@ -66632,34 +66632,34 @@
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H23" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I23" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J23" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K23" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L23" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M23" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N23" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O23" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P23" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="24">
@@ -66686,34 +66686,34 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.25</v>
+        <v>0.243295</v>
       </c>
       <c r="H24" t="n">
-        <v>0.75</v>
+        <v>0.756705</v>
       </c>
       <c r="I24" t="n">
-        <v>0.25</v>
+        <v>0.243295</v>
       </c>
       <c r="J24" t="n">
-        <v>0.75</v>
+        <v>0.756705</v>
       </c>
       <c r="K24" t="n">
-        <v>0.25</v>
+        <v>0.243295</v>
       </c>
       <c r="L24" t="n">
-        <v>0.75</v>
+        <v>0.756705</v>
       </c>
       <c r="M24" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="N24" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="O24" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="25">
@@ -66740,34 +66740,34 @@
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H25" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I25" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J25" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K25" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L25" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M25" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N25" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O25" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P25" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="26">
@@ -66848,34 +66848,34 @@
         <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H27" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J27" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K27" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L27" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M27" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N27" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="O27" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="P27" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="28">
@@ -67010,34 +67010,34 @@
         <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="H30" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="I30" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="J30" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="K30" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="L30" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="M30" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="N30" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="O30" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="P30" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="31">
@@ -67064,34 +67064,34 @@
         <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H31" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I31" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J31" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K31" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L31" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M31" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N31" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O31" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="P31" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="32">
@@ -67226,34 +67226,34 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="H34" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="I34" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="J34" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="K34" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="L34" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="M34" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="N34" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="O34" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="P34" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="35">
@@ -67280,34 +67280,34 @@
         <v>7</v>
       </c>
       <c r="G35" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H35" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I35" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J35" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K35" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L35" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M35" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N35" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O35" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P35" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="36">
@@ -67388,34 +67388,34 @@
         <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H37" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I37" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J37" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K37" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L37" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M37" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N37" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O37" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P37" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="38">
@@ -67766,34 +67766,34 @@
         <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N44" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="P44" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="45">
@@ -68522,34 +68522,34 @@
         <v>12</v>
       </c>
       <c r="G58" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H58" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J58" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="K58" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L58" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N58" t="n">
-        <v>0.275862</v>
+        <v>0.25731</v>
       </c>
       <c r="O58" t="n">
-        <v>0.729978</v>
+        <v>0.74269</v>
       </c>
       <c r="P58" t="n">
-        <v>0.270022</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="59">
@@ -68684,34 +68684,34 @@
         <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>0.361011</v>
+        <v>0.40625</v>
       </c>
       <c r="H61" t="n">
-        <v>0.638989</v>
+        <v>0.59375</v>
       </c>
       <c r="I61" t="n">
-        <v>0.361011</v>
+        <v>0.40625</v>
       </c>
       <c r="J61" t="n">
-        <v>0.638989</v>
+        <v>0.59375</v>
       </c>
       <c r="K61" t="n">
-        <v>0.361011</v>
+        <v>0.40625</v>
       </c>
       <c r="L61" t="n">
-        <v>0.638989</v>
+        <v>0.59375</v>
       </c>
       <c r="M61" t="n">
-        <v>0.361011</v>
+        <v>0.40625</v>
       </c>
       <c r="N61" t="n">
-        <v>0.638989</v>
+        <v>0.59375</v>
       </c>
       <c r="O61" t="n">
-        <v>0.361011</v>
+        <v>0.40625</v>
       </c>
       <c r="P61" t="n">
-        <v>0.638989</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="62">
@@ -73208,40 +73208,40 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="O9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="P9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="R9" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="10">
@@ -73268,40 +73268,40 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="I10" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="M10" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="O10" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="P10" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="R10" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="11">
@@ -73328,40 +73328,40 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="12">
@@ -73388,10 +73388,10 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.971631</v>
+        <v>0.952055</v>
       </c>
       <c r="H12" t="n">
-        <v>0.028369</v>
+        <v>0.047945</v>
       </c>
       <c r="I12" t="n">
         <v>0.971631</v>
@@ -74828,40 +74828,40 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="H36" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="I36" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="J36" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="K36" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="L36" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="M36" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="N36" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="O36" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="P36" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="R36" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="37">
@@ -76388,40 +76388,40 @@
         <v>7</v>
       </c>
       <c r="G62" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H62" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I62" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J62" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K62" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L62" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M62" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N62" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O62" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P62" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="R62" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="63">
@@ -76448,40 +76448,40 @@
         <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="H63" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="I63" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="J63" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="K63" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="L63" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="M63" t="n">
-        <v>0.4</v>
+        <v>0.361446</v>
       </c>
       <c r="N63" t="n">
-        <v>0.6</v>
+        <v>0.638554</v>
       </c>
       <c r="O63" t="n">
-        <v>0.4</v>
+        <v>0.361446</v>
       </c>
       <c r="P63" t="n">
-        <v>0.6</v>
+        <v>0.638554</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.4</v>
+        <v>0.361446</v>
       </c>
       <c r="R63" t="n">
-        <v>0.6</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="64">
@@ -77088,10 +77088,10 @@
         <v>0.727081</v>
       </c>
       <c r="K8" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="L8" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="9">
@@ -77244,22 +77244,22 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H12" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I12" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J12" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K12" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L12" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="13">
@@ -77412,22 +77412,22 @@
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H16" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J16" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="17">
@@ -77454,22 +77454,22 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H17" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I17" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J17" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K17" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="L17" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="18">
@@ -77538,22 +77538,22 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H19" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I19" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J19" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K19" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L19" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="20">
@@ -77916,16 +77916,16 @@
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H28" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I28" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J28" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K28" t="n">
         <v>0.185358</v>
@@ -77958,22 +77958,22 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>0.532905</v>
+        <v>0.556803</v>
       </c>
       <c r="H29" t="n">
-        <v>0.467095</v>
+        <v>0.443197</v>
       </c>
       <c r="I29" t="n">
-        <v>0.532905</v>
+        <v>0.556803</v>
       </c>
       <c r="J29" t="n">
-        <v>0.467095</v>
+        <v>0.443197</v>
       </c>
       <c r="K29" t="n">
-        <v>0.532905</v>
+        <v>0.556803</v>
       </c>
       <c r="L29" t="n">
-        <v>0.467095</v>
+        <v>0.443197</v>
       </c>
     </row>
   </sheetData>
@@ -81782,22 +81782,22 @@
         <v>15</v>
       </c>
       <c r="G10" t="n">
-        <v>0.94152</v>
+        <v>0.947985</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05848</v>
+        <v>0.052015</v>
       </c>
       <c r="I10" t="n">
-        <v>0.94152</v>
+        <v>0.948279</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05848</v>
+        <v>0.051721</v>
       </c>
       <c r="K10" t="n">
-        <v>0.94152</v>
+        <v>0.948279</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05848</v>
+        <v>0.051721</v>
       </c>
       <c r="M10" t="n">
         <v>0.94152</v>
@@ -82214,34 +82214,34 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="H18" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="I18" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="J18" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="K18" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="L18" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="M18" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="N18" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="O18" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="P18" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="19">
@@ -82322,34 +82322,34 @@
         <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="H20" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="I20" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="J20" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="K20" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="L20" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="M20" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="N20" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="O20" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="P20" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="21">
@@ -82556,16 +82556,16 @@
         <v>0.3379</v>
       </c>
       <c r="M24" t="n">
-        <v>0.66055</v>
+        <v>0.6621</v>
       </c>
       <c r="N24" t="n">
-        <v>0.33945</v>
+        <v>0.3379</v>
       </c>
       <c r="O24" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="P24" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="25">
@@ -82754,34 +82754,34 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="H28" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="I28" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J28" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K28" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L28" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M28" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N28" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="O28" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="P28" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="29">
@@ -82808,28 +82808,28 @@
         <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="O29" t="n">
         <v>0.7241379999999999</v>
@@ -83132,34 +83132,34 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="I35" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="K35" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="M35" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="O35" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="P35" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="36">
@@ -83240,34 +83240,34 @@
         <v>15</v>
       </c>
       <c r="G37" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H37" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I37" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J37" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K37" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L37" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M37" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N37" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O37" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P37" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="38">
@@ -83402,34 +83402,34 @@
         <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="H40" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="I40" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="J40" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="K40" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="L40" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="M40" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="N40" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="O40" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="P40" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="41">
@@ -83456,34 +83456,34 @@
         <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H41" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I41" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J41" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K41" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L41" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M41" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N41" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O41" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P41" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="42">
@@ -83528,16 +83528,16 @@
         <v>0.19214</v>
       </c>
       <c r="M42" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="N42" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="O42" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="P42" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="43">
@@ -83564,34 +83564,34 @@
         <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O43" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P43" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="44">
@@ -83618,28 +83618,28 @@
         <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H44" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I44" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J44" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K44" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L44" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="M44" t="n">
-        <v>0.659498</v>
+        <v>0.6595760000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>0.340502</v>
+        <v>0.340424</v>
       </c>
       <c r="O44" t="n">
         <v>0.659498</v>
@@ -83942,34 +83942,34 @@
         <v>14</v>
       </c>
       <c r="G50" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="I50" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="K50" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="O50" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="51">
@@ -84050,34 +84050,34 @@
         <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H52" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I52" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J52" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K52" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L52" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M52" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N52" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="O52" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="P52" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="53">
@@ -84428,34 +84428,34 @@
         <v>3</v>
       </c>
       <c r="G59" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H59" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I59" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J59" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K59" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L59" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M59" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N59" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O59" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P59" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="60">
@@ -84482,34 +84482,34 @@
         <v>15</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K60" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M60" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="O60" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P60" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="61">
@@ -84536,34 +84536,34 @@
         <v>14</v>
       </c>
       <c r="G61" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="H61" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="I61" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="J61" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="K61" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="L61" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="M61" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="N61" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
       <c r="O61" t="n">
-        <v>0.659498</v>
+        <v>0.576433</v>
       </c>
       <c r="P61" t="n">
-        <v>0.340502</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="62">
@@ -84590,34 +84590,34 @@
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H62" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I62" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J62" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K62" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L62" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M62" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N62" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="O62" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="P62" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="63">
@@ -84644,34 +84644,34 @@
         <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H63" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I63" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J63" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K63" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L63" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M63" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N63" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O63" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="P63" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="64">
@@ -84968,34 +84968,34 @@
         <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H69" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I69" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J69" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K69" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L69" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M69" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N69" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O69" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="P69" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="70">
@@ -85022,34 +85022,34 @@
         <v>15</v>
       </c>
       <c r="G70" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="H70" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="I70" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="J70" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="K70" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="L70" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="M70" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N70" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="O70" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="P70" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="71">
@@ -85238,34 +85238,34 @@
         <v>8</v>
       </c>
       <c r="G74" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H74" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I74" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J74" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K74" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L74" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M74" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="N74" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="O74" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="P74" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="75">
@@ -85292,34 +85292,34 @@
         <v>16</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N75" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O75" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P75" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="76">
@@ -85346,22 +85346,22 @@
         <v>7</v>
       </c>
       <c r="G76" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H76" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I76" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J76" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K76" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L76" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M76" t="n">
         <v>0.432904</v>
@@ -86588,22 +86588,22 @@
         <v>16</v>
       </c>
       <c r="G99" t="n">
+        <v>0.882667</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.117333</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.882667</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.117333</v>
+      </c>
+      <c r="K99" t="n">
         <v>0.862069</v>
       </c>
-      <c r="H99" t="n">
+      <c r="L99" t="n">
         <v>0.137931</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0.862069</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0.137931</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0.853147</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0.146853</v>
       </c>
       <c r="M99" t="n">
         <v>0.862069</v>
@@ -86612,10 +86612,10 @@
         <v>0.137931</v>
       </c>
       <c r="O99" t="n">
-        <v>0.853147</v>
+        <v>0.862069</v>
       </c>
       <c r="P99" t="n">
-        <v>0.146853</v>
+        <v>0.137931</v>
       </c>
     </row>
     <row r="100">
@@ -86696,34 +86696,34 @@
         <v>14</v>
       </c>
       <c r="G101" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="H101" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="I101" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="J101" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="K101" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="L101" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="M101" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="N101" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="O101" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="P101" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="102">
@@ -86912,34 +86912,34 @@
         <v>16</v>
       </c>
       <c r="G105" t="n">
-        <v>0.636364</v>
+        <v>0.659498</v>
       </c>
       <c r="H105" t="n">
-        <v>0.363636</v>
+        <v>0.340502</v>
       </c>
       <c r="I105" t="n">
-        <v>0.636364</v>
+        <v>0.659498</v>
       </c>
       <c r="J105" t="n">
-        <v>0.363636</v>
+        <v>0.340502</v>
       </c>
       <c r="K105" t="n">
-        <v>0.636364</v>
+        <v>0.659498</v>
       </c>
       <c r="L105" t="n">
-        <v>0.363636</v>
+        <v>0.340502</v>
       </c>
       <c r="M105" t="n">
-        <v>0.636364</v>
+        <v>0.659498</v>
       </c>
       <c r="N105" t="n">
-        <v>0.363636</v>
+        <v>0.340502</v>
       </c>
       <c r="O105" t="n">
-        <v>0.636364</v>
+        <v>0.659498</v>
       </c>
       <c r="P105" t="n">
-        <v>0.363636</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="106">
@@ -86966,34 +86966,34 @@
         <v>7</v>
       </c>
       <c r="G106" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H106" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I106" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J106" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K106" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L106" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M106" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N106" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O106" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="P106" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="107">
@@ -87092,16 +87092,16 @@
         <v>0.814642</v>
       </c>
       <c r="M108" t="n">
-        <v>0.181079</v>
+        <v>0.185358</v>
       </c>
       <c r="N108" t="n">
-        <v>0.818921</v>
+        <v>0.814642</v>
       </c>
       <c r="O108" t="n">
-        <v>0.182248</v>
+        <v>0.185358</v>
       </c>
       <c r="P108" t="n">
-        <v>0.817752</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="109">
@@ -87398,34 +87398,34 @@
         <v>16</v>
       </c>
       <c r="G114" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I114" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K114" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L114" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M114" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N114" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O114" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P114" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="115">
@@ -90642,28 +90642,28 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="H2" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
       <c r="I2" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="J2" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
       <c r="K2" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="L2" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
       <c r="M2" t="n">
-        <v>0.243295</v>
+        <v>0.272919</v>
       </c>
       <c r="N2" t="n">
-        <v>0.756705</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="3">
@@ -91074,28 +91074,28 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H11" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I11" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J11" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K11" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L11" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="M11" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="N11" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="12">
@@ -91122,28 +91122,28 @@
         <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="13">
@@ -91170,28 +91170,28 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M13" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N13" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="14">
@@ -91218,28 +91218,28 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H14" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I14" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J14" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K14" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L14" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M14" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N14" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="15">
@@ -91266,28 +91266,28 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H15" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I15" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J15" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K15" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L15" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M15" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N15" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="16">
@@ -91362,28 +91362,28 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H17" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I17" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J17" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K17" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L17" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="M17" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="N17" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="18">
@@ -91410,28 +91410,28 @@
         <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>0.556803</v>
+        <v>0.532905</v>
       </c>
       <c r="H18" t="n">
-        <v>0.443197</v>
+        <v>0.467095</v>
       </c>
       <c r="I18" t="n">
-        <v>0.556803</v>
+        <v>0.532905</v>
       </c>
       <c r="J18" t="n">
-        <v>0.443197</v>
+        <v>0.467095</v>
       </c>
       <c r="K18" t="n">
-        <v>0.556803</v>
+        <v>0.532905</v>
       </c>
       <c r="L18" t="n">
-        <v>0.443197</v>
+        <v>0.467095</v>
       </c>
       <c r="M18" t="n">
-        <v>0.556803</v>
+        <v>0.532905</v>
       </c>
       <c r="N18" t="n">
-        <v>0.443197</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="19">
@@ -91506,28 +91506,28 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H20" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I20" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J20" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K20" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="L20" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="M20" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N20" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="21">
@@ -91560,10 +91560,10 @@
         <v>0.567096</v>
       </c>
       <c r="I21" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J21" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K21" t="n">
         <v>0.432904</v>
@@ -91602,28 +91602,28 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H22" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I22" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J22" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K22" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L22" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M22" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N22" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="23">
@@ -92178,28 +92178,28 @@
         <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H34" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I34" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J34" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K34" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="L34" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="M34" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N34" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="35">
@@ -92418,28 +92418,28 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="H39" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
       <c r="I39" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="J39" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
       <c r="K39" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="L39" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
       <c r="M39" t="n">
-        <v>0.460746</v>
+        <v>0.507576</v>
       </c>
       <c r="N39" t="n">
-        <v>0.539254</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="40">
@@ -92562,28 +92562,28 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H42" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I42" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J42" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K42" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L42" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M42" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N42" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="43">

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -47,16 +47,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,21 +72,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,82 +447,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -5469,92 +5457,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R3_D129</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R3_D129</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -14755,72 +14743,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -16185,82 +16173,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D123</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D123</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D124</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D124</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D126</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D126</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -20493,72 +20481,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D128</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D128</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -22739,82 +22727,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D119</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D119</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D120</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D120</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D126</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D126</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -25805,52 +25793,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -26087,72 +26075,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D126</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D126</t>
         </is>
@@ -28333,62 +28321,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -29291,62 +29279,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -30543,72 +30531,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>
@@ -33269,82 +33257,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -39035,72 +39023,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -42289,62 +42277,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D121</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D121</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -43541,72 +43529,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D121</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D121</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D122</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D122</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D123</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D123</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D124</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D124</t>
         </is>
@@ -44971,72 +44959,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D120</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D120</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D122</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D122</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D128</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D128</t>
         </is>
@@ -47217,82 +47205,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -53793,72 +53781,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D123</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D123</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D124</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D124</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D126</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D126</t>
         </is>
@@ -56039,72 +56027,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D125</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D125</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D126</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D126</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D127</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D127</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D128</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D128</t>
         </is>
@@ -57469,72 +57457,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D121</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D121</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D122</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D122</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>
@@ -59283,102 +59271,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D120</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D120</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D121</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D121</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R3_D122</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R3_D122</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R4_D123</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R4_D123</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D124</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D124</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D125</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D125</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D126</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D126</t>
         </is>
@@ -65405,82 +65393,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D126</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D126</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D127</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D127</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D128</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D128</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -69065,82 +69053,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -71591,72 +71579,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -72685,92 +72673,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R3_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R3_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D125</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D126</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D126</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -76751,62 +76739,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D124</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D124</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D127</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D127</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -78003,72 +77991,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D121</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D121</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>
@@ -81257,82 +81245,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -87833,72 +87821,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -90559,72 +90547,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D124</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D124</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D125</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D125</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D127</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D127</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D128</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D128</t>
         </is>
@@ -92805,72 +92793,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -606,34 +606,34 @@
         <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I3" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J3" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K3" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L3" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M3" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N3" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O3" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P3" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="4">
@@ -768,22 +768,22 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H6" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J6" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K6" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L6" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M6" t="n">
         <v>0.40884</v>
@@ -792,10 +792,10 @@
         <v>0.59116</v>
       </c>
       <c r="O6" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P6" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="7">
@@ -822,34 +822,34 @@
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I7" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J7" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K7" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L7" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M7" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N7" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O7" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P7" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +876,28 @@
         <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I8" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K8" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M8" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O8" t="n">
         <v>0.8263470000000001</v>
@@ -930,34 +930,34 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>0.594595</v>
+        <v>0.556803</v>
       </c>
       <c r="H9" t="n">
-        <v>0.405405</v>
+        <v>0.443197</v>
       </c>
       <c r="I9" t="n">
-        <v>0.594595</v>
+        <v>0.556803</v>
       </c>
       <c r="J9" t="n">
-        <v>0.405405</v>
+        <v>0.443197</v>
       </c>
       <c r="K9" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="L9" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="M9" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="N9" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
       <c r="O9" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="P9" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="10">
@@ -1092,34 +1092,34 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H12" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I12" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J12" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K12" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L12" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M12" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N12" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O12" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P12" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="13">
@@ -1416,34 +1416,34 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="H18" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="I18" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="J18" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="K18" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="L18" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="M18" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="N18" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="O18" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="P18" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="19">
@@ -1686,34 +1686,34 @@
         <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="24">
@@ -1746,28 +1746,28 @@
         <v>0.321293</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="25">
@@ -2172,16 +2172,16 @@
         <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H32" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I32" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J32" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K32" t="n">
         <v>0.532905</v>
@@ -2388,22 +2388,22 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H36" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I36" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J36" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K36" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L36" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M36" t="n">
         <v>0.162214</v>
@@ -2496,34 +2496,34 @@
         <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="H38" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="I38" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="J38" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="K38" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="L38" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="M38" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="N38" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="O38" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="P38" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="39">
@@ -2928,22 +2928,22 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H46" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I46" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J46" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K46" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L46" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M46" t="n">
         <v>0.07783</v>
@@ -3090,34 +3090,34 @@
         <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H49" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I49" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J49" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K49" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L49" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M49" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N49" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O49" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="P49" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="50">
@@ -3252,34 +3252,34 @@
         <v>11</v>
       </c>
       <c r="G52" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="I52" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="K52" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="M52" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="O52" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P52" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="53">
@@ -3900,34 +3900,34 @@
         <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H64" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I64" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J64" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K64" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L64" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M64" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N64" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O64" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P64" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="65">
@@ -4116,34 +4116,34 @@
         <v>13</v>
       </c>
       <c r="G68" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H68" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I68" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J68" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K68" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L68" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M68" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N68" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O68" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P68" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="69">
@@ -4944,16 +4944,16 @@
         <v>0.539254</v>
       </c>
       <c r="M83" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N83" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="O83" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="P83" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="84">
@@ -5358,22 +5358,22 @@
         <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H91" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I91" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J91" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K91" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L91" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M91" t="n">
         <v>0.185358</v>
@@ -5382,10 +5382,10 @@
         <v>0.814642</v>
       </c>
       <c r="O91" t="n">
-        <v>0.185358</v>
+        <v>0.186091</v>
       </c>
       <c r="P91" t="n">
-        <v>0.814642</v>
+        <v>0.813909</v>
       </c>
     </row>
     <row r="92">
@@ -5572,40 +5572,40 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H2" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J2" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K2" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L2" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M2" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N2" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O2" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P2" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="R2" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="3">
@@ -5632,40 +5632,40 @@
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.269565</v>
+        <v>0.321293</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.269565</v>
+        <v>0.321293</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.269565</v>
+        <v>0.321293</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.269565</v>
+        <v>0.321293</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.269565</v>
+        <v>0.321293</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>0.269565</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="4">
@@ -5836,10 +5836,10 @@
         <v>0.466565</v>
       </c>
       <c r="O6" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P6" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="Q6" t="n">
         <v>0.533435</v>
@@ -5872,40 +5872,40 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="P7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="R7" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="8">
@@ -5992,34 +5992,34 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M9" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O9" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="Q9" t="n">
         <v>0.8263470000000001</v>
@@ -6172,40 +6172,40 @@
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="K12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="M12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="O12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="P12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="R12" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="13">
@@ -6232,40 +6232,40 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.556803</v>
+        <v>0.511551</v>
       </c>
       <c r="H13" t="n">
-        <v>0.443197</v>
+        <v>0.488449</v>
       </c>
       <c r="I13" t="n">
-        <v>0.556803</v>
+        <v>0.511551</v>
       </c>
       <c r="J13" t="n">
-        <v>0.443197</v>
+        <v>0.488449</v>
       </c>
       <c r="K13" t="n">
-        <v>0.556803</v>
+        <v>0.511551</v>
       </c>
       <c r="L13" t="n">
-        <v>0.443197</v>
+        <v>0.488449</v>
       </c>
       <c r="M13" t="n">
-        <v>0.556803</v>
+        <v>0.511551</v>
       </c>
       <c r="N13" t="n">
-        <v>0.443197</v>
+        <v>0.488449</v>
       </c>
       <c r="O13" t="n">
-        <v>0.556803</v>
+        <v>0.511551</v>
       </c>
       <c r="P13" t="n">
-        <v>0.443197</v>
+        <v>0.488449</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.556803</v>
+        <v>0.511551</v>
       </c>
       <c r="R13" t="n">
-        <v>0.443197</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="14">
@@ -6352,40 +6352,40 @@
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="16">
@@ -6472,40 +6472,40 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H17" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J17" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L17" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N17" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P17" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="R17" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="18">
@@ -6532,40 +6532,40 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="H18" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="J18" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="L18" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="N18" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="P18" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="R18" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="19">
@@ -6772,40 +6772,40 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="H22" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
       <c r="I22" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="J22" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
       <c r="K22" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="L22" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
       <c r="M22" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="N22" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
       <c r="O22" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="P22" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="R22" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="23">
@@ -7192,40 +7192,40 @@
         <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="H29" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="I29" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="J29" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="K29" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="L29" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="M29" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="N29" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="O29" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="P29" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="R29" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="30">
@@ -7672,40 +7672,40 @@
         <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H37" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I37" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J37" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K37" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L37" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M37" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N37" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O37" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P37" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="R37" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="38">
@@ -7792,28 +7792,28 @@
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H39" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I39" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J39" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K39" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L39" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M39" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N39" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="O39" t="n">
         <v>0.460746</v>
@@ -8092,40 +8092,40 @@
         <v>7</v>
       </c>
       <c r="G44" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="H44" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="I44" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="J44" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="K44" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="L44" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="M44" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="N44" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="O44" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="P44" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="R44" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="45">
@@ -8212,40 +8212,40 @@
         <v>6</v>
       </c>
       <c r="G46" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H46" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I46" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J46" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K46" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L46" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M46" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N46" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O46" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="P46" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="R46" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="47">
@@ -8392,40 +8392,40 @@
         <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="H49" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="I49" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="J49" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="K49" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="L49" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="M49" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="N49" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="O49" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="P49" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="R49" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="50">
@@ -8632,40 +8632,40 @@
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="H53" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="I53" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="J53" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="K53" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="L53" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="M53" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="N53" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="O53" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="P53" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.140351</v>
+        <v>0.162214</v>
       </c>
       <c r="R53" t="n">
-        <v>0.859649</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="54">
@@ -8752,40 +8752,40 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H55" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I55" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J55" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K55" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L55" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M55" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N55" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O55" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P55" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="R55" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="56">
@@ -9712,40 +9712,40 @@
         <v>7</v>
       </c>
       <c r="G71" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="H71" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="I71" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="J71" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="K71" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="L71" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="M71" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N71" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="O71" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="P71" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="R71" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="72">
@@ -9772,22 +9772,22 @@
         <v>14</v>
       </c>
       <c r="G72" t="n">
-        <v>0.911098</v>
+        <v>0.913043</v>
       </c>
       <c r="H72" t="n">
-        <v>0.08890199999999999</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>0.911098</v>
+        <v>0.913043</v>
       </c>
       <c r="J72" t="n">
-        <v>0.08890199999999999</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>0.882667</v>
+        <v>0.8880400000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>0.117333</v>
+        <v>0.11196</v>
       </c>
       <c r="M72" t="n">
         <v>0.882667</v>
@@ -10072,40 +10072,40 @@
         <v>11</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="R77" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="78">
@@ -10132,40 +10132,40 @@
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="H78" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="I78" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="J78" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="K78" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="L78" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="M78" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="N78" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="O78" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="P78" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="R78" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="79">
@@ -10192,40 +10192,40 @@
         <v>15</v>
       </c>
       <c r="G79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="J79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="K79" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="L79" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="M79" t="n">
-        <v>0.80786</v>
+        <v>0.799243</v>
       </c>
       <c r="N79" t="n">
-        <v>0.19214</v>
+        <v>0.200757</v>
       </c>
       <c r="O79" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P79" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="R79" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="80">
@@ -10252,40 +10252,40 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I80" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N80" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O80" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P80" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="R80" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="81">
@@ -10312,40 +10312,40 @@
         <v>16</v>
       </c>
       <c r="G81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="82">
@@ -10432,40 +10432,40 @@
         <v>7</v>
       </c>
       <c r="G83" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="H83" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="I83" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="J83" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="K83" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="L83" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="M83" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="N83" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="O83" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="P83" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="R83" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="84">
@@ -10552,40 +10552,40 @@
         <v>6</v>
       </c>
       <c r="G85" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M85" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O85" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P85" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="R85" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="86">
@@ -10612,40 +10612,40 @@
         <v>13</v>
       </c>
       <c r="G86" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H86" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I86" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J86" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K86" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L86" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M86" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N86" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O86" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R86" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="87">
@@ -10732,40 +10732,40 @@
         <v>5</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="H88" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="J88" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="K88" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="L88" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="M88" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="N88" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="O88" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="P88" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="R88" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="89">
@@ -10912,40 +10912,40 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H91" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I91" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J91" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K91" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L91" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M91" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N91" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O91" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="P91" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="R91" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="92">
@@ -11212,40 +11212,40 @@
         <v>6</v>
       </c>
       <c r="G96" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="H96" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="I96" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="J96" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="K96" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="L96" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="M96" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="N96" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="O96" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="P96" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="R96" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="97">
@@ -11392,40 +11392,40 @@
         <v>5</v>
       </c>
       <c r="G99" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="H99" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="I99" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="J99" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="K99" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="L99" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="M99" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="N99" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="O99" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="P99" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="R99" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="100">
@@ -11512,40 +11512,40 @@
         <v>8</v>
       </c>
       <c r="G101" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H101" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I101" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J101" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K101" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L101" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M101" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N101" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O101" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P101" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="R101" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="102">
@@ -11692,40 +11692,40 @@
         <v>7</v>
       </c>
       <c r="G104" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H104" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I104" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J104" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K104" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L104" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M104" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N104" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O104" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P104" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="R104" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="105">
@@ -11752,40 +11752,40 @@
         <v>14</v>
       </c>
       <c r="G105" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H105" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="I105" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="K105" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L105" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="M105" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N105" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="O105" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P105" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.862069</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R105" t="n">
-        <v>0.137931</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="106">
@@ -11842,10 +11842,10 @@
         <v>0.443197</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="R106" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="107">
@@ -11872,40 +11872,40 @@
         <v>13</v>
       </c>
       <c r="G107" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H107" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I107" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J107" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K107" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L107" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M107" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N107" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O107" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="P107" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="R107" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="108">
@@ -11932,40 +11932,40 @@
         <v>12</v>
       </c>
       <c r="G108" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H108" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="I108" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="K108" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L108" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="M108" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N108" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="O108" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P108" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="R108" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="109">
@@ -11992,40 +11992,40 @@
         <v>5</v>
       </c>
       <c r="G109" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H109" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I109" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J109" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K109" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L109" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M109" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N109" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O109" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="P109" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="R109" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="110">
@@ -12352,40 +12352,40 @@
         <v>6</v>
       </c>
       <c r="G115" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="H115" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="I115" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="J115" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="K115" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="L115" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="M115" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="N115" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="O115" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="P115" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="R115" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="116">
@@ -12532,40 +12532,40 @@
         <v>5</v>
       </c>
       <c r="G118" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="H118" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="I118" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="J118" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="K118" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="L118" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="M118" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="N118" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="O118" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="P118" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="R118" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="119">
@@ -12910,22 +12910,22 @@
         <v>0.25731</v>
       </c>
       <c r="M124" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N124" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="O124" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="P124" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="R124" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="125">
@@ -12952,40 +12952,40 @@
         <v>12</v>
       </c>
       <c r="G125" t="n">
+        <v>0.6787069999999999</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.321293</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.6787069999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.321293</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.6787069999999999</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.321293</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.6787069999999999</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.321293</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.6787069999999999</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.321293</v>
+      </c>
+      <c r="Q125" t="n">
         <v>0.6621</v>
       </c>
-      <c r="H125" t="n">
+      <c r="R125" t="n">
         <v>0.3379</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0.6621</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0.3379</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0.6621</v>
-      </c>
-      <c r="L125" t="n">
-        <v>0.3379</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0.6621</v>
-      </c>
-      <c r="N125" t="n">
-        <v>0.3379</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0.6621</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0.3379</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0.659498</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.340502</v>
       </c>
     </row>
     <row r="126">
@@ -13012,40 +13012,40 @@
         <v>5</v>
       </c>
       <c r="G126" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H126" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I126" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J126" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K126" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L126" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="M126" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="N126" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="O126" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="P126" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="R126" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="127">
@@ -13132,40 +13132,40 @@
         <v>7</v>
       </c>
       <c r="G128" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H128" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I128" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J128" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K128" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L128" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M128" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N128" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="O128" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="P128" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="R128" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="129">
@@ -13252,40 +13252,40 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H130" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I130" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J130" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K130" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L130" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M130" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N130" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O130" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="P130" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="R130" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="131">
@@ -13432,40 +13432,40 @@
         <v>5</v>
       </c>
       <c r="G133" t="n">
-        <v>0.244898</v>
+        <v>0.230483</v>
       </c>
       <c r="H133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.769517</v>
       </c>
       <c r="I133" t="n">
-        <v>0.244898</v>
+        <v>0.230483</v>
       </c>
       <c r="J133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.769517</v>
       </c>
       <c r="K133" t="n">
-        <v>0.244898</v>
+        <v>0.230483</v>
       </c>
       <c r="L133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.769517</v>
       </c>
       <c r="M133" t="n">
-        <v>0.244898</v>
+        <v>0.230483</v>
       </c>
       <c r="N133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.769517</v>
       </c>
       <c r="O133" t="n">
-        <v>0.244898</v>
+        <v>0.230483</v>
       </c>
       <c r="P133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.769517</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.244898</v>
+        <v>0.230483</v>
       </c>
       <c r="R133" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="134">
@@ -13492,40 +13492,40 @@
         <v>7</v>
       </c>
       <c r="G134" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.045455</v>
       </c>
       <c r="H134" t="n">
-        <v>0.924324</v>
+        <v>0.954545</v>
       </c>
       <c r="I134" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.045455</v>
       </c>
       <c r="J134" t="n">
-        <v>0.924324</v>
+        <v>0.954545</v>
       </c>
       <c r="K134" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.045455</v>
       </c>
       <c r="L134" t="n">
-        <v>0.924324</v>
+        <v>0.954545</v>
       </c>
       <c r="M134" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.045455</v>
       </c>
       <c r="N134" t="n">
-        <v>0.924324</v>
+        <v>0.954545</v>
       </c>
       <c r="O134" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.045455</v>
       </c>
       <c r="P134" t="n">
-        <v>0.924324</v>
+        <v>0.954545</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.045455</v>
       </c>
       <c r="R134" t="n">
-        <v>0.924324</v>
+        <v>0.954545</v>
       </c>
     </row>
     <row r="135">
@@ -13642,10 +13642,10 @@
         <v>0.92217</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.09604799999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="R136" t="n">
-        <v>0.903952</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="137">
@@ -13912,40 +13912,40 @@
         <v>6</v>
       </c>
       <c r="G141" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H141" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I141" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K141" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L141" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M141" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N141" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O141" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P141" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="R141" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="142">
@@ -13972,40 +13972,40 @@
         <v>13</v>
       </c>
       <c r="G142" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="H142" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="I142" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="J142" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="K142" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="L142" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="M142" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="N142" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="O142" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="P142" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="R142" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="143">
@@ -14512,40 +14512,40 @@
         <v>5</v>
       </c>
       <c r="G151" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="H151" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="I151" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="J151" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="K151" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="L151" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="M151" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="N151" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="O151" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="P151" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="R151" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="152">
@@ -14692,40 +14692,40 @@
         <v>5</v>
       </c>
       <c r="G154" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H154" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I154" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J154" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K154" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L154" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M154" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N154" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O154" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P154" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="R154" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
   </sheetData>
@@ -14940,10 +14940,10 @@
         <v>0.716346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J4" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K4" t="n">
         <v>0.283654</v>
@@ -14952,10 +14952,10 @@
         <v>0.716346</v>
       </c>
       <c r="M4" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N4" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="5">
@@ -15078,28 +15078,28 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="H7" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="I7" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="J7" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="K7" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="L7" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="M7" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="N7" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="8">
@@ -15366,28 +15366,28 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H13" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I13" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J13" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K13" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L13" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M13" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N13" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="14">
@@ -15558,28 +15558,28 @@
         <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H17" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I17" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J17" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K17" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L17" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M17" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N17" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="18">
@@ -15606,28 +15606,28 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H18" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I18" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J18" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K18" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L18" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M18" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N18" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="19">
@@ -15702,28 +15702,28 @@
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H20" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I20" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J20" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K20" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L20" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M20" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N20" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="21">
@@ -15750,28 +15750,28 @@
         <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="22">
@@ -15846,28 +15846,28 @@
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H23" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I23" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J23" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K23" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L23" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M23" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N23" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="24">
@@ -15942,28 +15942,28 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="H25" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="I25" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="J25" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="K25" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="L25" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="M25" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="N25" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="26">
@@ -16038,28 +16038,28 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H27" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I27" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J27" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K27" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L27" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M27" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N27" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="28">
@@ -20912,28 +20912,28 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="10">
@@ -21158,16 +21158,16 @@
         <v>0.467095</v>
       </c>
       <c r="I14" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J14" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K14" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L14" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M14" t="n">
         <v>0.532905</v>
@@ -21296,28 +21296,28 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="H17" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="I17" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="J17" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="K17" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="L17" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="M17" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="N17" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="18">
@@ -21488,28 +21488,28 @@
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="22">
@@ -21920,28 +21920,28 @@
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="H30" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="I30" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="J30" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="K30" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="L30" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="M30" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="N30" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="31">
@@ -22160,28 +22160,28 @@
         <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H35" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I35" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J35" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K35" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L35" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M35" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N35" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="36">
@@ -22304,28 +22304,28 @@
         <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H38" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I38" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J38" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K38" t="n">
-        <v>0.40884</v>
+        <v>0.4</v>
       </c>
       <c r="L38" t="n">
-        <v>0.59116</v>
+        <v>0.6</v>
       </c>
       <c r="M38" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N38" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="39">
@@ -22496,28 +22496,28 @@
         <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M42" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N42" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="43">
@@ -22592,28 +22592,28 @@
         <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H44" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I44" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J44" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K44" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L44" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M44" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N44" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="45">
@@ -28448,22 +28448,22 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H3" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I3" t="n">
-        <v>0.432904</v>
+        <v>0.429344</v>
       </c>
       <c r="J3" t="n">
-        <v>0.567096</v>
+        <v>0.5706560000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L3" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="4">
@@ -28532,22 +28532,22 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.432904</v>
+        <v>0.40884</v>
       </c>
       <c r="H5" t="n">
-        <v>0.567096</v>
+        <v>0.59116</v>
       </c>
       <c r="I5" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J5" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K5" t="n">
-        <v>0.432904</v>
+        <v>0.40884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.567096</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="6">
@@ -28784,22 +28784,22 @@
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I11" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J11" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K11" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L11" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="12">
@@ -28910,22 +28910,22 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H14" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I14" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J14" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K14" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L14" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="15">
@@ -28994,22 +28994,22 @@
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="H16" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="I16" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="J16" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="K16" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="L16" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="17">
@@ -29036,22 +29036,22 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H17" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I17" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J17" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K17" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L17" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="18">
@@ -29204,22 +29204,22 @@
         <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="H21" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="I21" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="J21" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="K21" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="L21" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="22">
@@ -29532,22 +29532,22 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H6" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I6" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J6" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K6" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="7">
@@ -29922,10 +29922,10 @@
         <v>0.691406</v>
       </c>
       <c r="K15" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L15" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="16">
@@ -30204,22 +30204,22 @@
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H22" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J22" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L22" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="23">
@@ -30246,22 +30246,22 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H23" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I23" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J23" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K23" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L23" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="24">
@@ -33362,34 +33362,34 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="H2" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="I2" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="J2" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="K2" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="M2" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="N2" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="O2" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="P2" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="3">
@@ -33578,34 +33578,34 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="H6" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="J6" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="K6" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="L6" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="M6" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="N6" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="O6" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="P6" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="7">
@@ -33956,34 +33956,34 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H13" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I13" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J13" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K13" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L13" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M13" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N13" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O13" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P13" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="14">
@@ -34280,34 +34280,34 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H19" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I19" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J19" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K19" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L19" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M19" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N19" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="O19" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="P19" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="20">
@@ -34658,34 +34658,34 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H26" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I26" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J26" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K26" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L26" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M26" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N26" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O26" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P26" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="27">
@@ -34874,34 +34874,34 @@
         <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H30" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I30" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J30" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K30" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L30" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M30" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N30" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O30" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P30" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="31">
@@ -35036,34 +35036,34 @@
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="I33" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="K33" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="M33" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="O33" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P33" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="34">
@@ -35090,34 +35090,34 @@
         <v>15</v>
       </c>
       <c r="G34" t="n">
-        <v>0.952055</v>
+        <v>0.94152</v>
       </c>
       <c r="H34" t="n">
-        <v>0.047945</v>
+        <v>0.05848</v>
       </c>
       <c r="I34" t="n">
-        <v>0.952055</v>
+        <v>0.94152</v>
       </c>
       <c r="J34" t="n">
-        <v>0.047945</v>
+        <v>0.05848</v>
       </c>
       <c r="K34" t="n">
-        <v>0.952055</v>
+        <v>0.94152</v>
       </c>
       <c r="L34" t="n">
-        <v>0.047945</v>
+        <v>0.05848</v>
       </c>
       <c r="M34" t="n">
-        <v>0.952055</v>
+        <v>0.94152</v>
       </c>
       <c r="N34" t="n">
-        <v>0.047945</v>
+        <v>0.05848</v>
       </c>
       <c r="O34" t="n">
-        <v>0.952055</v>
+        <v>0.94152</v>
       </c>
       <c r="P34" t="n">
-        <v>0.047945</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="35">
@@ -35252,34 +35252,34 @@
         <v>14</v>
       </c>
       <c r="G37" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="H37" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="J37" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="K37" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="L37" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="M37" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="N37" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="O37" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="P37" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="38">
@@ -35306,34 +35306,34 @@
         <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.803419</v>
       </c>
       <c r="H38" t="n">
-        <v>0.173653</v>
+        <v>0.196581</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.803419</v>
       </c>
       <c r="J38" t="n">
-        <v>0.173653</v>
+        <v>0.196581</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.803419</v>
       </c>
       <c r="L38" t="n">
-        <v>0.173653</v>
+        <v>0.196581</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.803419</v>
       </c>
       <c r="N38" t="n">
-        <v>0.173653</v>
+        <v>0.196581</v>
       </c>
       <c r="O38" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.803419</v>
       </c>
       <c r="P38" t="n">
-        <v>0.173653</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="39">
@@ -35522,34 +35522,34 @@
         <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H42" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I42" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J42" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K42" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L42" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M42" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N42" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O42" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P42" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="43">
@@ -36062,34 +36062,34 @@
         <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H52" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I52" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J52" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K52" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L52" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="M52" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="N52" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="O52" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="P52" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="53">
@@ -36602,34 +36602,34 @@
         <v>7</v>
       </c>
       <c r="G62" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H62" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I62" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J62" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K62" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L62" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M62" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N62" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O62" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P62" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="63">
@@ -36764,34 +36764,34 @@
         <v>11</v>
       </c>
       <c r="G65" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H65" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I65" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J65" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K65" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L65" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M65" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N65" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O65" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P65" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="66">
@@ -36926,34 +36926,34 @@
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="H68" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="I68" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="J68" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="K68" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="L68" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="M68" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="N68" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="O68" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="P68" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="69">
@@ -37358,34 +37358,34 @@
         <v>2</v>
       </c>
       <c r="G76" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H76" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I76" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J76" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K76" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L76" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M76" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N76" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O76" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="P76" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="77">
@@ -38060,34 +38060,34 @@
         <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="H89" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="I89" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="J89" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="K89" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="L89" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="M89" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="N89" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="O89" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="P89" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="90">
@@ -38546,34 +38546,34 @@
         <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="H98" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="I98" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="J98" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="K98" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="L98" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="M98" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="N98" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="O98" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="P98" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="99">
@@ -38894,10 +38894,10 @@
         <v>0.230523</v>
       </c>
       <c r="O104" t="n">
-        <v>0.75</v>
+        <v>0.769477</v>
       </c>
       <c r="P104" t="n">
-        <v>0.25</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="105">
@@ -39838,28 +39838,28 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H17" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I17" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J17" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K17" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L17" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="M17" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="N17" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="18">
@@ -40030,28 +40030,28 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H21" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I21" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J21" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K21" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L21" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M21" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N21" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="22">
@@ -40462,28 +40462,28 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="H30" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="I30" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="J30" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="K30" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="L30" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="M30" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="N30" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="31">
@@ -40606,28 +40606,28 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="H33" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
       <c r="I33" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="J33" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
       <c r="K33" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="L33" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
       <c r="M33" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="N33" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="34">
@@ -41038,28 +41038,28 @@
         <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H42" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I42" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="J42" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="K42" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L42" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="M42" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="N42" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="43">
@@ -41182,28 +41182,28 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="H45" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="I45" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="J45" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="K45" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="L45" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="M45" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="N45" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="46">
@@ -41470,28 +41470,28 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="H51" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="I51" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="J51" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="K51" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="L51" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="M51" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="N51" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="52">
@@ -41662,28 +41662,28 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="56">
@@ -41950,28 +41950,28 @@
         <v>9</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
     </row>
     <row r="62">
@@ -42142,28 +42142,28 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="H65" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="I65" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="J65" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="K65" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="L65" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="M65" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="N65" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="66">
@@ -47310,34 +47310,34 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="3">
@@ -47742,22 +47742,22 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M10" t="n">
         <v>0.7241379999999999</v>
@@ -47850,28 +47850,28 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O12" t="n">
         <v>0.8263470000000001</v>
@@ -48774,28 +48774,28 @@
         <v>0.3379</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="O29" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="30">
@@ -49092,34 +49092,34 @@
         <v>15</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P35" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="36">
@@ -49266,22 +49266,22 @@
         <v>0.423567</v>
       </c>
       <c r="K38" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L38" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M38" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N38" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="O38" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="P38" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="39">
@@ -49362,34 +49362,34 @@
         <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H40" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I40" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J40" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K40" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L40" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M40" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N40" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O40" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="P40" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="41">
@@ -49524,34 +49524,34 @@
         <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="H43" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="I43" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="J43" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="K43" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="L43" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="M43" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="N43" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="O43" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="P43" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="44">
@@ -49794,34 +49794,34 @@
         <v>13</v>
       </c>
       <c r="G48" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="H48" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="J48" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="L48" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="N48" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
     </row>
     <row r="49">
@@ -49902,28 +49902,28 @@
         <v>11</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H50" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J50" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L50" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N50" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O50" t="n">
         <v>0.80786</v>
@@ -50118,34 +50118,34 @@
         <v>6</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H54" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J54" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K54" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L54" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N54" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P54" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="55">
@@ -50172,34 +50172,34 @@
         <v>4</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H55" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J55" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L55" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N55" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O55" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P55" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="56">
@@ -50226,34 +50226,34 @@
         <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="H56" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="I56" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="J56" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="K56" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="L56" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="M56" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="N56" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="O56" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="P56" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="57">
@@ -50496,28 +50496,28 @@
         <v>11</v>
       </c>
       <c r="G61" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H61" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I61" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J61" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K61" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L61" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M61" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N61" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O61" t="n">
         <v>0.556803</v>
@@ -50928,34 +50928,34 @@
         <v>13</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H69" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J69" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K69" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L69" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N69" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O69" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P69" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="70">
@@ -50982,34 +50982,34 @@
         <v>8</v>
       </c>
       <c r="G70" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H70" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J70" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K70" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L70" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M70" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N70" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O70" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P70" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="71">
@@ -51090,34 +51090,34 @@
         <v>14</v>
       </c>
       <c r="G72" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H72" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I72" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J72" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K72" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L72" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M72" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N72" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O72" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P72" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="73">
@@ -51144,34 +51144,34 @@
         <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="H73" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="I73" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="J73" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="K73" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="L73" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="M73" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="N73" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="O73" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="P73" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="74">
@@ -51198,34 +51198,34 @@
         <v>10</v>
       </c>
       <c r="G74" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="H74" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="I74" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="J74" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="K74" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="L74" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="M74" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="N74" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
       <c r="O74" t="n">
-        <v>0.659498</v>
+        <v>0.556803</v>
       </c>
       <c r="P74" t="n">
-        <v>0.340502</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="75">
@@ -51306,34 +51306,34 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H76" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I76" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J76" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K76" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L76" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M76" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N76" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O76" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P76" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="77">
@@ -51360,34 +51360,34 @@
         <v>15</v>
       </c>
       <c r="G77" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H77" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I77" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J77" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K77" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L77" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M77" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N77" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O77" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P77" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="78">
@@ -51522,34 +51522,34 @@
         <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H80" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I80" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J80" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K80" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L80" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M80" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N80" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O80" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P80" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="81">
@@ -51792,34 +51792,34 @@
         <v>4</v>
       </c>
       <c r="G85" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H85" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I85" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J85" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K85" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L85" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M85" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N85" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O85" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="P85" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="86">
@@ -51954,34 +51954,34 @@
         <v>11</v>
       </c>
       <c r="G88" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H88" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I88" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J88" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K88" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L88" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M88" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N88" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O88" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P88" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="89">
@@ -52008,34 +52008,34 @@
         <v>14</v>
       </c>
       <c r="G89" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H89" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I89" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J89" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K89" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L89" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="M89" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="N89" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="O89" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="P89" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="90">
@@ -52128,22 +52128,22 @@
         <v>0.716346</v>
       </c>
       <c r="K91" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L91" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M91" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N91" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O91" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P91" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="92">
@@ -52170,34 +52170,34 @@
         <v>6</v>
       </c>
       <c r="G92" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H92" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I92" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J92" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K92" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L92" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M92" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N92" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O92" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P92" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="93">
@@ -52242,16 +52242,16 @@
         <v>0.814642</v>
       </c>
       <c r="M93" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N93" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="O93" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="P93" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="94">
@@ -52332,22 +52332,22 @@
         <v>11</v>
       </c>
       <c r="G95" t="n">
-        <v>0.260417</v>
+        <v>0.25</v>
       </c>
       <c r="H95" t="n">
-        <v>0.739583</v>
+        <v>0.75</v>
       </c>
       <c r="I95" t="n">
-        <v>0.260417</v>
+        <v>0.25</v>
       </c>
       <c r="J95" t="n">
-        <v>0.739583</v>
+        <v>0.75</v>
       </c>
       <c r="K95" t="n">
-        <v>0.260417</v>
+        <v>0.25</v>
       </c>
       <c r="L95" t="n">
-        <v>0.739583</v>
+        <v>0.75</v>
       </c>
       <c r="M95" t="n">
         <v>0.244898</v>
@@ -52356,10 +52356,10 @@
         <v>0.7551020000000001</v>
       </c>
       <c r="O95" t="n">
-        <v>0.25</v>
+        <v>0.244898</v>
       </c>
       <c r="P95" t="n">
-        <v>0.75</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="96">
@@ -53034,34 +53034,34 @@
         <v>5</v>
       </c>
       <c r="G108" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="H108" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
       <c r="I108" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="J108" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
       <c r="K108" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="L108" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
       <c r="M108" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="N108" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
       <c r="O108" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="P108" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="109">
@@ -53088,34 +53088,34 @@
         <v>10</v>
       </c>
       <c r="G109" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H109" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I109" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J109" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K109" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L109" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M109" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N109" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O109" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P109" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="110">
@@ -53142,34 +53142,34 @@
         <v>6</v>
       </c>
       <c r="G110" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="H110" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="I110" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="J110" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="K110" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="L110" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="M110" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="N110" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="O110" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="P110" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="111">
@@ -53196,34 +53196,34 @@
         <v>4</v>
       </c>
       <c r="G111" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="H111" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="I111" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="J111" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="K111" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="L111" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="M111" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="N111" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="O111" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="P111" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="112">
@@ -53250,34 +53250,34 @@
         <v>5</v>
       </c>
       <c r="G112" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H112" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I112" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J112" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K112" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L112" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M112" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="N112" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="O112" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="P112" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="113">
@@ -65498,34 +65498,34 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H2" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I2" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J2" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K2" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L2" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M2" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N2" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O2" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P2" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="3">
@@ -65552,34 +65552,34 @@
         <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="4">
@@ -65684,10 +65684,10 @@
         <v>0.638989</v>
       </c>
       <c r="O5" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P5" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="6">
@@ -65768,34 +65768,34 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H7" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I7" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J7" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K7" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L7" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M7" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N7" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="O7" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="P7" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="8">
@@ -65930,34 +65930,34 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="H10" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="I10" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="J10" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="K10" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="L10" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="M10" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="N10" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="O10" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="P10" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="11">
@@ -65990,22 +65990,22 @@
         <v>0.638989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J11" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K11" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L11" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M11" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N11" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O11" t="n">
         <v>0.361011</v>
@@ -66254,34 +66254,34 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="H16" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="I16" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="J16" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="K16" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="L16" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="M16" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="N16" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="O16" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="P16" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="17">
@@ -66494,10 +66494,10 @@
         <v>0.567096</v>
       </c>
       <c r="O20" t="n">
-        <v>0.432904</v>
+        <v>0.431735</v>
       </c>
       <c r="P20" t="n">
-        <v>0.567096</v>
+        <v>0.568265</v>
       </c>
     </row>
     <row r="21">
@@ -66740,34 +66740,34 @@
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H25" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I25" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J25" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K25" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L25" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M25" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N25" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O25" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P25" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="26">
@@ -66956,34 +66956,34 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O29" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P29" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="30">
@@ -67010,34 +67010,34 @@
         <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="H30" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="I30" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="J30" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="K30" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="L30" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="M30" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="N30" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="O30" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="P30" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="31">
@@ -67196,10 +67196,10 @@
         <v>0.567096</v>
       </c>
       <c r="O33" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="P33" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="34">
@@ -67928,34 +67928,34 @@
         <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H47" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I47" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J47" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K47" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L47" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M47" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N47" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="O47" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="P47" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="48">
@@ -68198,34 +68198,34 @@
         <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H52" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I52" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J52" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K52" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L52" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M52" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N52" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O52" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="P52" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="53">
@@ -68630,34 +68630,34 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H60" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I60" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J60" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K60" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L60" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M60" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N60" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O60" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P60" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="61">
@@ -68900,34 +68900,34 @@
         <v>3</v>
       </c>
       <c r="G65" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="H65" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="I65" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="J65" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="K65" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="L65" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="M65" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="N65" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="O65" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="P65" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="66">
@@ -69278,16 +69278,16 @@
         <v>0.667992</v>
       </c>
       <c r="K4" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L4" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M4" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N4" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O4" t="n">
         <v>0.332008</v>
@@ -69374,34 +69374,34 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="P6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="7">
@@ -69482,34 +69482,34 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="H8" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="I8" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="J8" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="K8" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="L8" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="M8" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="N8" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="O8" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="P8" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="9">
@@ -69548,22 +69548,22 @@
         <v>0.716346</v>
       </c>
       <c r="K9" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L9" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M9" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N9" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O9" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P9" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="10">
@@ -69914,34 +69914,34 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H16" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I16" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J16" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K16" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L16" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M16" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N16" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O16" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P16" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="17">
@@ -70346,34 +70346,34 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="H24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="I24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="J24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="K24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="L24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="M24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="N24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
       <c r="O24" t="n">
-        <v>0.460746</v>
+        <v>0.511551</v>
       </c>
       <c r="P24" t="n">
-        <v>0.539254</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="25">
@@ -71318,34 +71318,34 @@
         <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H42" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I42" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J42" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K42" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L42" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M42" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N42" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O42" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P42" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="43">
@@ -71426,34 +71426,34 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P44" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="45">
@@ -71480,34 +71480,34 @@
         <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="O45" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P45" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="46">
@@ -71734,10 +71734,10 @@
         <v>0.638989</v>
       </c>
       <c r="K3" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L3" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M3" t="n">
         <v>0.361011</v>
@@ -71866,28 +71866,28 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M6" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N6" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="7">
@@ -72058,28 +72058,28 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H10" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I10" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J10" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K10" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L10" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M10" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N10" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="11">
@@ -72202,28 +72202,28 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H13" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I13" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J13" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K13" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L13" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M13" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N13" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="14">
@@ -72250,28 +72250,28 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H14" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I14" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J14" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K14" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L14" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M14" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N14" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="15">
@@ -72346,28 +72346,28 @@
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H16" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I16" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J16" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K16" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="M16" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="N16" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="17">
@@ -72538,28 +72538,28 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="H20" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="I20" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="J20" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
       <c r="K20" t="n">
-        <v>0.75</v>
+        <v>0.769477</v>
       </c>
       <c r="L20" t="n">
-        <v>0.25</v>
+        <v>0.230523</v>
       </c>
       <c r="M20" t="n">
-        <v>0.74269</v>
+        <v>0.769477</v>
       </c>
       <c r="N20" t="n">
-        <v>0.25731</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="21">
@@ -81728,34 +81728,34 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="M9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="O9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="10">
@@ -81890,34 +81890,34 @@
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="13">
@@ -82376,34 +82376,34 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H21" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I21" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J21" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K21" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L21" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M21" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N21" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="O21" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="P21" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="22">
@@ -82430,34 +82430,34 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="H22" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="I22" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="J22" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="K22" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="L22" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="M22" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="N22" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="O22" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="P22" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="23">
@@ -82484,34 +82484,34 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="H23" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="I23" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="J23" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="K23" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="L23" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="M23" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="N23" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
       <c r="O23" t="n">
-        <v>0.260417</v>
+        <v>0.263158</v>
       </c>
       <c r="P23" t="n">
-        <v>0.739583</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="24">
@@ -83132,34 +83132,34 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H35" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I35" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J35" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K35" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L35" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M35" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N35" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O35" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P35" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="36">
@@ -83186,34 +83186,34 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="H36" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="I36" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="J36" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="K36" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="L36" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="M36" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="N36" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="O36" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="P36" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="37">
@@ -83726,34 +83726,34 @@
         <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="H46" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
       <c r="I46" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="J46" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
       <c r="K46" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="L46" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
       <c r="M46" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="N46" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
       <c r="O46" t="n">
-        <v>0.272919</v>
+        <v>0.260417</v>
       </c>
       <c r="P46" t="n">
-        <v>0.727081</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="47">
@@ -83780,34 +83780,34 @@
         <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="H47" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="I47" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="J47" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="K47" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="L47" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="M47" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="N47" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
       <c r="O47" t="n">
-        <v>0.332008</v>
+        <v>0.283654</v>
       </c>
       <c r="P47" t="n">
-        <v>0.667992</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="48">
@@ -83834,34 +83834,34 @@
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>0.507576</v>
+        <v>0.532905</v>
       </c>
       <c r="H48" t="n">
-        <v>0.492424</v>
+        <v>0.467095</v>
       </c>
       <c r="I48" t="n">
-        <v>0.507576</v>
+        <v>0.532905</v>
       </c>
       <c r="J48" t="n">
-        <v>0.492424</v>
+        <v>0.467095</v>
       </c>
       <c r="K48" t="n">
-        <v>0.507576</v>
+        <v>0.532905</v>
       </c>
       <c r="L48" t="n">
-        <v>0.492424</v>
+        <v>0.467095</v>
       </c>
       <c r="M48" t="n">
-        <v>0.507576</v>
+        <v>0.532905</v>
       </c>
       <c r="N48" t="n">
-        <v>0.492424</v>
+        <v>0.467095</v>
       </c>
       <c r="O48" t="n">
-        <v>0.507576</v>
+        <v>0.532905</v>
       </c>
       <c r="P48" t="n">
-        <v>0.492424</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="49">
@@ -84320,34 +84320,34 @@
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="H57" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="I57" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="J57" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="K57" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="L57" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="M57" t="n">
-        <v>0.162214</v>
+        <v>0.100437</v>
       </c>
       <c r="N57" t="n">
-        <v>0.837786</v>
+        <v>0.899563</v>
       </c>
       <c r="O57" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="P57" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="58">
@@ -84428,34 +84428,34 @@
         <v>3</v>
       </c>
       <c r="G59" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="H59" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="I59" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="J59" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="K59" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="L59" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="M59" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="N59" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="O59" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="P59" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="60">
@@ -84860,34 +84860,34 @@
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H67" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I67" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J67" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K67" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L67" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M67" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N67" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="O67" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="P67" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="68">
@@ -84968,34 +84968,34 @@
         <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="H69" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="I69" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="J69" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="K69" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="L69" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="M69" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="N69" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="O69" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="P69" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="70">
@@ -85400,34 +85400,34 @@
         <v>5</v>
       </c>
       <c r="G77" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="H77" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="I77" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="J77" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="K77" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="L77" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="M77" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="N77" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="O77" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="P77" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="78">
@@ -85454,34 +85454,34 @@
         <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H78" t="n">
-        <v>0.321293</v>
+        <v>0.25731</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J78" t="n">
-        <v>0.321293</v>
+        <v>0.25731</v>
       </c>
       <c r="K78" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L78" t="n">
-        <v>0.321293</v>
+        <v>0.25731</v>
       </c>
       <c r="M78" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N78" t="n">
-        <v>0.321293</v>
+        <v>0.25731</v>
       </c>
       <c r="O78" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="P78" t="n">
-        <v>0.321293</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="79">
@@ -85508,34 +85508,34 @@
         <v>15</v>
       </c>
       <c r="G79" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="H79" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="I79" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="J79" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="K79" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="L79" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="M79" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="N79" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="O79" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="P79" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="80">
@@ -85616,34 +85616,34 @@
         <v>6</v>
       </c>
       <c r="G81" t="n">
-        <v>0.80786</v>
+        <v>0.853147</v>
       </c>
       <c r="H81" t="n">
-        <v>0.19214</v>
+        <v>0.146853</v>
       </c>
       <c r="I81" t="n">
-        <v>0.80786</v>
+        <v>0.853147</v>
       </c>
       <c r="J81" t="n">
-        <v>0.19214</v>
+        <v>0.146853</v>
       </c>
       <c r="K81" t="n">
-        <v>0.80786</v>
+        <v>0.853147</v>
       </c>
       <c r="L81" t="n">
-        <v>0.19214</v>
+        <v>0.146853</v>
       </c>
       <c r="M81" t="n">
-        <v>0.80786</v>
+        <v>0.853147</v>
       </c>
       <c r="N81" t="n">
-        <v>0.19214</v>
+        <v>0.146853</v>
       </c>
       <c r="O81" t="n">
-        <v>0.80786</v>
+        <v>0.853147</v>
       </c>
       <c r="P81" t="n">
-        <v>0.19214</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="82">
@@ -85670,34 +85670,34 @@
         <v>4</v>
       </c>
       <c r="G82" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
       <c r="I82" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
       <c r="K82" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
       <c r="M82" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
       <c r="O82" t="n">
-        <v>0.659498</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P82" t="n">
-        <v>0.340502</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="83">
@@ -85778,34 +85778,34 @@
         <v>16</v>
       </c>
       <c r="G84" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="H84" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="I84" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="J84" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="K84" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="L84" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="M84" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="N84" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="O84" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="P84" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
     </row>
     <row r="85">
@@ -85832,34 +85832,34 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="H85" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="I85" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="J85" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="K85" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="L85" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="M85" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="N85" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="O85" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="P85" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="86">
@@ -85940,34 +85940,34 @@
         <v>15</v>
       </c>
       <c r="G87" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="H87" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="I87" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="J87" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="K87" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="L87" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="M87" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="N87" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
       <c r="O87" t="n">
-        <v>0.882667</v>
+        <v>0.94152</v>
       </c>
       <c r="P87" t="n">
-        <v>0.117333</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="88">
@@ -86102,34 +86102,34 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H90" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I90" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J90" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K90" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L90" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="M90" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="N90" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="O90" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="P90" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="91">
@@ -86156,34 +86156,34 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="H91" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="I91" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="J91" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="K91" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="L91" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="M91" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="N91" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="O91" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="P91" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="92">
@@ -86210,34 +86210,34 @@
         <v>16</v>
       </c>
       <c r="G92" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="H92" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="I92" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="J92" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="K92" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="L92" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="M92" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="N92" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
       <c r="O92" t="n">
-        <v>0.95</v>
+        <v>0.952055</v>
       </c>
       <c r="P92" t="n">
-        <v>0.05</v>
+        <v>0.047945</v>
       </c>
     </row>
     <row r="93">
@@ -86318,34 +86318,34 @@
         <v>15</v>
       </c>
       <c r="G94" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H94" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I94" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="J94" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="K94" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="L94" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="M94" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="N94" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="O94" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="P94" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="95">
@@ -86426,34 +86426,34 @@
         <v>6</v>
       </c>
       <c r="G96" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="H96" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="I96" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="J96" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="K96" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="L96" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="M96" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N96" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="O96" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="P96" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="97">
@@ -86534,34 +86534,34 @@
         <v>8</v>
       </c>
       <c r="G98" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H98" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J98" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K98" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L98" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M98" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N98" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="O98" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="P98" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="99">
@@ -86588,34 +86588,34 @@
         <v>16</v>
       </c>
       <c r="G99" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H99" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I99" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J99" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K99" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L99" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M99" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N99" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O99" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="P99" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="100">
@@ -87916,28 +87916,28 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="H2" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="I2" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="J2" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="K2" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="M2" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="N2" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="3">
@@ -88396,28 +88396,28 @@
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="H12" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="J12" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="L12" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="N12" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="13">
@@ -88492,28 +88492,28 @@
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I14" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K14" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M14" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="15">
@@ -88684,28 +88684,28 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M18" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N18" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="19">
@@ -89212,28 +89212,28 @@
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H29" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I29" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J29" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K29" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L29" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M29" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N29" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="30">
@@ -89356,28 +89356,28 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H32" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I32" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J32" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K32" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L32" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M32" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N32" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="33">
@@ -89404,28 +89404,28 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="H33" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="I33" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="J33" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="K33" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="L33" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="M33" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="N33" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="34">
@@ -89740,28 +89740,28 @@
         <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H40" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I40" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J40" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K40" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L40" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M40" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N40" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="41">
@@ -89884,16 +89884,16 @@
         <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H43" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I43" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J43" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K43" t="n">
         <v>0.361011</v>
@@ -90412,28 +90412,28 @@
         <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
       <c r="K54" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6621</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>0.3379</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="55">
@@ -90460,28 +90460,28 @@
         <v>10</v>
       </c>
       <c r="G55" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="H55" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="I55" t="n">
-        <v>0.853147</v>
+        <v>0.882667</v>
       </c>
       <c r="J55" t="n">
-        <v>0.146853</v>
+        <v>0.117333</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.882667</v>
       </c>
       <c r="L55" t="n">
-        <v>0.173653</v>
+        <v>0.117333</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.882667</v>
       </c>
       <c r="N55" t="n">
-        <v>0.173653</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="56">

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -1092,34 +1092,34 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="H12" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="I12" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="J12" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="K12" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="L12" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="M12" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="N12" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="O12" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="P12" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="13">
@@ -1200,34 +1200,34 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="H14" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="I14" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="J14" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="K14" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="L14" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="M14" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="N14" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="O14" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="P14" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="15">
@@ -1416,34 +1416,34 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="19">
@@ -1794,34 +1794,34 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="26">
@@ -2388,22 +2388,22 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H36" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I36" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J36" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K36" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L36" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M36" t="n">
         <v>0.162214</v>
@@ -2412,10 +2412,10 @@
         <v>0.837786</v>
       </c>
       <c r="O36" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="P36" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="37">
@@ -2874,34 +2874,34 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="H45" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="I45" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="J45" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="K45" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="L45" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="M45" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="N45" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="O45" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="P45" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="46">
@@ -2928,22 +2928,22 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H46" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J46" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K46" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L46" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M46" t="n">
         <v>0.07783</v>
@@ -3414,34 +3414,34 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H55" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I55" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J55" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K55" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L55" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M55" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N55" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O55" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P55" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="56">
@@ -3468,34 +3468,34 @@
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H56" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I56" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J56" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K56" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L56" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M56" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N56" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O56" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P56" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="57">
@@ -3900,34 +3900,34 @@
         <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H64" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I64" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J64" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K64" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L64" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M64" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N64" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O64" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P64" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="65">
@@ -4170,34 +4170,34 @@
         <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H69" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I69" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J69" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K69" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L69" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M69" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N69" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="O69" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="P69" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="70">
@@ -4602,34 +4602,34 @@
         <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>0.045455</v>
+        <v>0.036697</v>
       </c>
       <c r="H77" t="n">
-        <v>0.954545</v>
+        <v>0.963303</v>
       </c>
       <c r="I77" t="n">
-        <v>0.045455</v>
+        <v>0.036697</v>
       </c>
       <c r="J77" t="n">
-        <v>0.954545</v>
+        <v>0.963303</v>
       </c>
       <c r="K77" t="n">
-        <v>0.045455</v>
+        <v>0.036697</v>
       </c>
       <c r="L77" t="n">
-        <v>0.954545</v>
+        <v>0.963303</v>
       </c>
       <c r="M77" t="n">
-        <v>0.045455</v>
+        <v>0.036697</v>
       </c>
       <c r="N77" t="n">
-        <v>0.954545</v>
+        <v>0.963303</v>
       </c>
       <c r="O77" t="n">
-        <v>0.045455</v>
+        <v>0.036697</v>
       </c>
       <c r="P77" t="n">
-        <v>0.954545</v>
+        <v>0.963303</v>
       </c>
     </row>
     <row r="78">
@@ -4764,34 +4764,34 @@
         <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H80" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I80" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J80" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K80" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L80" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M80" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N80" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="O80" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="P80" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="81">
@@ -4872,34 +4872,34 @@
         <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H82" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I82" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J82" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K82" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L82" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M82" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N82" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O82" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P82" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="83">
@@ -4980,34 +4980,34 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="H84" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="I84" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="J84" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="K84" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="L84" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="M84" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="N84" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="O84" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="P84" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="85">
@@ -5358,22 +5358,22 @@
         <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="H91" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="I91" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="J91" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="K91" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="L91" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="M91" t="n">
         <v>0.185358</v>
@@ -5382,10 +5382,10 @@
         <v>0.814642</v>
       </c>
       <c r="O91" t="n">
-        <v>0.186091</v>
+        <v>0.185358</v>
       </c>
       <c r="P91" t="n">
-        <v>0.813909</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="92">
@@ -6532,22 +6532,22 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H18" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I18" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J18" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K18" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L18" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="M18" t="n">
         <v>0.659498</v>
@@ -6556,16 +6556,16 @@
         <v>0.340502</v>
       </c>
       <c r="O18" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="P18" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="R18" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="19">
@@ -8092,40 +8092,40 @@
         <v>7</v>
       </c>
       <c r="G44" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H44" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I44" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J44" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K44" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L44" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M44" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N44" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O44" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P44" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="R44" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="45">
@@ -8212,40 +8212,40 @@
         <v>6</v>
       </c>
       <c r="G46" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H46" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I46" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J46" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L46" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M46" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N46" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="O46" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="P46" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="R46" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="47">
@@ -9712,40 +9712,40 @@
         <v>7</v>
       </c>
       <c r="G71" t="n">
-        <v>0.594595</v>
+        <v>0.576433</v>
       </c>
       <c r="H71" t="n">
-        <v>0.405405</v>
+        <v>0.423567</v>
       </c>
       <c r="I71" t="n">
-        <v>0.594595</v>
+        <v>0.576433</v>
       </c>
       <c r="J71" t="n">
-        <v>0.405405</v>
+        <v>0.423567</v>
       </c>
       <c r="K71" t="n">
-        <v>0.594595</v>
+        <v>0.576433</v>
       </c>
       <c r="L71" t="n">
-        <v>0.405405</v>
+        <v>0.423567</v>
       </c>
       <c r="M71" t="n">
-        <v>0.577889</v>
+        <v>0.576433</v>
       </c>
       <c r="N71" t="n">
-        <v>0.422111</v>
+        <v>0.423567</v>
       </c>
       <c r="O71" t="n">
-        <v>0.577889</v>
+        <v>0.576433</v>
       </c>
       <c r="P71" t="n">
-        <v>0.422111</v>
+        <v>0.423567</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.577889</v>
+        <v>0.556803</v>
       </c>
       <c r="R71" t="n">
-        <v>0.422111</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="72">
@@ -9772,22 +9772,22 @@
         <v>14</v>
       </c>
       <c r="G72" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="H72" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="I72" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="J72" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="K72" t="n">
-        <v>0.8880400000000001</v>
+        <v>0.882667</v>
       </c>
       <c r="L72" t="n">
-        <v>0.11196</v>
+        <v>0.117333</v>
       </c>
       <c r="M72" t="n">
         <v>0.882667</v>
@@ -9832,40 +9832,40 @@
         <v>6</v>
       </c>
       <c r="G73" t="n">
-        <v>0.769477</v>
+        <v>0.767963</v>
       </c>
       <c r="H73" t="n">
-        <v>0.230523</v>
+        <v>0.232037</v>
       </c>
       <c r="I73" t="n">
-        <v>0.769477</v>
+        <v>0.767963</v>
       </c>
       <c r="J73" t="n">
-        <v>0.230523</v>
+        <v>0.232037</v>
       </c>
       <c r="K73" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L73" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M73" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N73" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O73" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P73" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="R73" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="74">
@@ -9952,40 +9952,40 @@
         <v>12</v>
       </c>
       <c r="G75" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I75" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K75" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M75" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N75" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O75" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P75" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R75" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="76">
@@ -11116,16 +11116,16 @@
         <v>0.899563</v>
       </c>
       <c r="O94" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="P94" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.100437</v>
+        <v>0.07783</v>
       </c>
       <c r="R94" t="n">
-        <v>0.899563</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="95">
@@ -11212,40 +11212,40 @@
         <v>6</v>
       </c>
       <c r="G96" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="H96" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="I96" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="J96" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="K96" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="L96" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="M96" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="N96" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="O96" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="P96" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="R96" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="97">
@@ -11812,34 +11812,34 @@
         <v>6</v>
       </c>
       <c r="G106" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H106" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I106" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J106" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K106" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L106" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M106" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N106" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O106" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P106" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="Q106" t="n">
         <v>0.533435</v>
@@ -11992,40 +11992,40 @@
         <v>5</v>
       </c>
       <c r="G109" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="H109" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="I109" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="J109" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="K109" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="L109" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="M109" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="N109" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="O109" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="P109" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.511551</v>
+        <v>0.460746</v>
       </c>
       <c r="R109" t="n">
-        <v>0.488449</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="110">
@@ -12352,40 +12352,40 @@
         <v>6</v>
       </c>
       <c r="G115" t="n">
-        <v>0.243295</v>
+        <v>0.259281</v>
       </c>
       <c r="H115" t="n">
-        <v>0.756705</v>
+        <v>0.740719</v>
       </c>
       <c r="I115" t="n">
-        <v>0.243295</v>
+        <v>0.259281</v>
       </c>
       <c r="J115" t="n">
-        <v>0.756705</v>
+        <v>0.740719</v>
       </c>
       <c r="K115" t="n">
-        <v>0.243295</v>
+        <v>0.259281</v>
       </c>
       <c r="L115" t="n">
-        <v>0.756705</v>
+        <v>0.740719</v>
       </c>
       <c r="M115" t="n">
-        <v>0.243295</v>
+        <v>0.25</v>
       </c>
       <c r="N115" t="n">
-        <v>0.756705</v>
+        <v>0.75</v>
       </c>
       <c r="O115" t="n">
-        <v>0.243295</v>
+        <v>0.25</v>
       </c>
       <c r="P115" t="n">
-        <v>0.756705</v>
+        <v>0.75</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="R115" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="116">
@@ -12532,40 +12532,40 @@
         <v>5</v>
       </c>
       <c r="G118" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="H118" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="J118" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K118" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="L118" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M118" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="N118" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="O118" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="P118" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="R118" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="119">
@@ -13012,40 +13012,40 @@
         <v>5</v>
       </c>
       <c r="G126" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="H126" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="I126" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J126" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K126" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L126" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M126" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N126" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="O126" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="P126" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="R126" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="127">
@@ -13252,28 +13252,28 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="H130" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="I130" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="J130" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="K130" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="L130" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="M130" t="n">
-        <v>0.230483</v>
+        <v>0.236313</v>
       </c>
       <c r="N130" t="n">
-        <v>0.769517</v>
+        <v>0.763687</v>
       </c>
       <c r="O130" t="n">
         <v>0.230483</v>
@@ -14032,40 +14032,40 @@
         <v>12</v>
       </c>
       <c r="G143" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H143" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="I143" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="K143" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L143" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="M143" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N143" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="O143" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P143" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="R143" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="144">
@@ -14092,40 +14092,40 @@
         <v>5</v>
       </c>
       <c r="G144" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H144" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K144" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L144" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M144" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N144" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O144" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P144" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="R144" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="145">
@@ -14934,10 +14934,10 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I4" t="n">
         <v>0.272919</v>
@@ -14946,10 +14946,10 @@
         <v>0.727081</v>
       </c>
       <c r="K4" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L4" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M4" t="n">
         <v>0.272919</v>
@@ -15222,28 +15222,28 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I10" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J10" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K10" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L10" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M10" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N10" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="11">
@@ -15462,28 +15462,28 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H15" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I15" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J15" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K15" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L15" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M15" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N15" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="16">
@@ -15606,28 +15606,28 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="19">
@@ -15750,28 +15750,28 @@
         <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="22">
@@ -15798,28 +15798,28 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="H22" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="I22" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="J22" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="K22" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="L22" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
       <c r="M22" t="n">
-        <v>0.432904</v>
+        <v>0.460746</v>
       </c>
       <c r="N22" t="n">
-        <v>0.567096</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="23">
@@ -15942,28 +15942,28 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H25" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I25" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J25" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K25" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L25" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M25" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N25" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="26">
@@ -20624,28 +20624,28 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I3" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J3" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K3" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M3" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N3" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="4">
@@ -21392,22 +21392,22 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H19" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I19" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J19" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K19" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L19" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M19" t="n">
         <v>0.308594</v>
@@ -21632,28 +21632,28 @@
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H24" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I24" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J24" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K24" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L24" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M24" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N24" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="25">
@@ -21728,16 +21728,16 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K26" t="n">
         <v>0.6621</v>
@@ -22160,28 +22160,28 @@
         <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H35" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I35" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J35" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K35" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L35" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M35" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N35" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="36">
@@ -25868,16 +25868,16 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="H2" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="I2" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="J2" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="3">
@@ -25976,16 +25976,16 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H5" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I5" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J5" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="6">
@@ -26012,16 +26012,16 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="H6" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="I6" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="J6" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="7">
@@ -28532,10 +28532,10 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I5" t="n">
         <v>0.426966</v>
@@ -28544,10 +28544,10 @@
         <v>0.573034</v>
       </c>
       <c r="K5" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="L5" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="6">
@@ -28742,22 +28742,22 @@
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="H10" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="I10" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="J10" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="K10" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L10" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="11">
@@ -29036,22 +29036,22 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="H17" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="I17" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="J17" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="K17" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="L17" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="18">
@@ -29364,22 +29364,22 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H2" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J2" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L2" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="3">
@@ -29616,22 +29616,22 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H8" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="J8" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="K8" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="L8" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="9">
@@ -29868,22 +29868,22 @@
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H14" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I14" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J14" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="K14" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="L14" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="15">
@@ -30078,22 +30078,22 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H19" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I19" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J19" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K19" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L19" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="20">
@@ -33416,34 +33416,34 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="H3" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="J3" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="L3" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="N3" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07567599999999999</v>
+        <v>0.07783</v>
       </c>
       <c r="P3" t="n">
-        <v>0.924324</v>
+        <v>0.92217</v>
       </c>
     </row>
     <row r="4">
@@ -34118,34 +34118,34 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="H16" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="I16" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="J16" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="K16" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="L16" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="M16" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="N16" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="O16" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="P16" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
     </row>
     <row r="17">
@@ -34928,34 +34928,34 @@
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H31" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I31" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J31" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K31" t="n">
-        <v>0.882667</v>
+        <v>0.83329</v>
       </c>
       <c r="L31" t="n">
-        <v>0.117333</v>
+        <v>0.16671</v>
       </c>
       <c r="M31" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="O31" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="32">
@@ -35306,34 +35306,34 @@
         <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="H38" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="I38" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="J38" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="K38" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="L38" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="M38" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="N38" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="O38" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="P38" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="39">
@@ -35900,34 +35900,34 @@
         <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>0.243295</v>
+        <v>0.185358</v>
       </c>
       <c r="H49" t="n">
-        <v>0.756705</v>
+        <v>0.814642</v>
       </c>
       <c r="I49" t="n">
-        <v>0.243295</v>
+        <v>0.185358</v>
       </c>
       <c r="J49" t="n">
-        <v>0.756705</v>
+        <v>0.814642</v>
       </c>
       <c r="K49" t="n">
-        <v>0.243295</v>
+        <v>0.185358</v>
       </c>
       <c r="L49" t="n">
-        <v>0.756705</v>
+        <v>0.814642</v>
       </c>
       <c r="M49" t="n">
-        <v>0.243295</v>
+        <v>0.185358</v>
       </c>
       <c r="N49" t="n">
-        <v>0.756705</v>
+        <v>0.814642</v>
       </c>
       <c r="O49" t="n">
-        <v>0.243295</v>
+        <v>0.185358</v>
       </c>
       <c r="P49" t="n">
-        <v>0.756705</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="50">
@@ -36440,34 +36440,34 @@
         <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H59" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I59" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J59" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K59" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L59" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M59" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N59" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O59" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P59" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="60">
@@ -37358,34 +37358,34 @@
         <v>2</v>
       </c>
       <c r="G76" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H76" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I76" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J76" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K76" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L76" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M76" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N76" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O76" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P76" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="77">
@@ -37736,34 +37736,34 @@
         <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="H83" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="I83" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="J83" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="K83" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L83" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="M83" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="N83" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="O83" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P83" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="84">
@@ -38546,34 +38546,34 @@
         <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H98" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I98" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J98" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K98" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L98" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M98" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N98" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O98" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="P98" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="99">
@@ -39406,28 +39406,28 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.011765</v>
+        <v>0.036697</v>
       </c>
       <c r="H8" t="n">
-        <v>0.988235</v>
+        <v>0.963303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.011765</v>
+        <v>0.036697</v>
       </c>
       <c r="J8" t="n">
-        <v>0.988235</v>
+        <v>0.963303</v>
       </c>
       <c r="K8" t="n">
-        <v>0.011765</v>
+        <v>0.036697</v>
       </c>
       <c r="L8" t="n">
-        <v>0.988235</v>
+        <v>0.963303</v>
       </c>
       <c r="M8" t="n">
-        <v>0.011765</v>
+        <v>0.034936</v>
       </c>
       <c r="N8" t="n">
-        <v>0.988235</v>
+        <v>0.965064</v>
       </c>
     </row>
     <row r="9">
@@ -40030,28 +40030,28 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H21" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I21" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J21" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K21" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L21" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M21" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N21" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="22">
@@ -40462,28 +40462,28 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="H30" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="I30" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="J30" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="K30" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="L30" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="M30" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="N30" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="31">
@@ -41470,28 +41470,28 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="H51" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="I51" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="J51" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="K51" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="L51" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="M51" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="N51" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="52">
@@ -41950,28 +41950,28 @@
         <v>9</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="62">
@@ -42142,28 +42142,28 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="H65" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="I65" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="J65" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="K65" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="L65" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="M65" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="N65" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="66">
@@ -42238,28 +42238,28 @@
         <v>9</v>
       </c>
       <c r="G67" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="H67" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="I67" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="J67" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="K67" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="L67" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
       <c r="M67" t="n">
-        <v>0.769477</v>
+        <v>0.803419</v>
       </c>
       <c r="N67" t="n">
-        <v>0.230523</v>
+        <v>0.196581</v>
       </c>
     </row>
   </sheetData>
@@ -48066,34 +48066,34 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H16" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I16" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J16" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K16" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L16" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M16" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N16" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="O16" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="P16" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="17">
@@ -48174,34 +48174,34 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O18" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P18" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="19">
@@ -48606,34 +48606,34 @@
         <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I26" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K26" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M26" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O26" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="27">
@@ -48726,22 +48726,22 @@
         <v>0.275862</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="29">
@@ -48768,10 +48768,10 @@
         <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I29" t="n">
         <v>0.659498</v>
@@ -48822,34 +48822,34 @@
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="H30" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
       <c r="I30" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="J30" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
       <c r="K30" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="L30" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
       <c r="M30" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="N30" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
       <c r="O30" t="n">
-        <v>0.532905</v>
+        <v>0.507576</v>
       </c>
       <c r="P30" t="n">
-        <v>0.467095</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="31">
@@ -49524,34 +49524,34 @@
         <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H43" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I43" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J43" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K43" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L43" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M43" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N43" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O43" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="P43" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="44">
@@ -49578,34 +49578,34 @@
         <v>7</v>
       </c>
       <c r="G44" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H44" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I44" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J44" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K44" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L44" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M44" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N44" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O44" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P44" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="45">
@@ -49632,34 +49632,34 @@
         <v>9</v>
       </c>
       <c r="G45" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H45" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I45" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J45" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K45" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L45" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M45" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N45" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O45" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P45" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="46">
@@ -49794,34 +49794,34 @@
         <v>13</v>
       </c>
       <c r="G48" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="H48" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="I48" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="J48" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="K48" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="L48" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="M48" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="N48" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
       <c r="O48" t="n">
-        <v>0.913043</v>
+        <v>0.882667</v>
       </c>
       <c r="P48" t="n">
-        <v>0.08695700000000001</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="49">
@@ -49848,34 +49848,34 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="I49" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="K49" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="M49" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
       <c r="O49" t="n">
-        <v>0.882667</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P49" t="n">
-        <v>0.117333</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="50">
@@ -49902,34 +49902,34 @@
         <v>11</v>
       </c>
       <c r="G50" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="H50" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="I50" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="J50" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="K50" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="L50" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="M50" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="N50" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
       <c r="O50" t="n">
-        <v>0.80786</v>
+        <v>0.803419</v>
       </c>
       <c r="P50" t="n">
-        <v>0.19214</v>
+        <v>0.196581</v>
       </c>
     </row>
     <row r="51">
@@ -49956,34 +49956,34 @@
         <v>14</v>
       </c>
       <c r="G51" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="H51" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="I51" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="K51" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="L51" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="M51" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="N51" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
       <c r="O51" t="n">
-        <v>0.94152</v>
+        <v>0.882667</v>
       </c>
       <c r="P51" t="n">
-        <v>0.05848</v>
+        <v>0.117333</v>
       </c>
     </row>
     <row r="52">
@@ -50010,34 +50010,34 @@
         <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="H52" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="J52" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="K52" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="L52" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="N52" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.659498</v>
       </c>
       <c r="P52" t="n">
-        <v>0.321293</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="53">
@@ -50064,34 +50064,34 @@
         <v>10</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H53" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J53" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K53" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L53" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N53" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="O53" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="P53" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="54">
@@ -50118,34 +50118,34 @@
         <v>6</v>
       </c>
       <c r="G54" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H54" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I54" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J54" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K54" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L54" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M54" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N54" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="O54" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="P54" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="55">
@@ -50172,34 +50172,34 @@
         <v>4</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L55" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N55" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="O55" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="P55" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="56">
@@ -51306,34 +51306,34 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="H76" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="I76" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="J76" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="K76" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="L76" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="M76" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="N76" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
       <c r="O76" t="n">
-        <v>0.40884</v>
+        <v>0.361011</v>
       </c>
       <c r="P76" t="n">
-        <v>0.59116</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="77">
@@ -51360,34 +51360,34 @@
         <v>15</v>
       </c>
       <c r="G77" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H77" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I77" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J77" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K77" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L77" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M77" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N77" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O77" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P77" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="78">
@@ -51792,34 +51792,34 @@
         <v>4</v>
       </c>
       <c r="G85" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="H85" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="I85" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="J85" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="K85" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="L85" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="M85" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="N85" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
       <c r="O85" t="n">
-        <v>0.230483</v>
+        <v>0.185358</v>
       </c>
       <c r="P85" t="n">
-        <v>0.769517</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="86">
@@ -52008,34 +52008,34 @@
         <v>14</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J89" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K89" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M89" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N89" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="O89" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="P89" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="90">
@@ -52062,16 +52062,16 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>0.185358</v>
+        <v>0.185912</v>
       </c>
       <c r="H90" t="n">
-        <v>0.814642</v>
+        <v>0.814088</v>
       </c>
       <c r="I90" t="n">
-        <v>0.185358</v>
+        <v>0.185912</v>
       </c>
       <c r="J90" t="n">
-        <v>0.814642</v>
+        <v>0.814088</v>
       </c>
       <c r="K90" t="n">
         <v>0.185358</v>
@@ -52086,10 +52086,10 @@
         <v>0.814642</v>
       </c>
       <c r="O90" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="P90" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="91">
@@ -52116,34 +52116,34 @@
         <v>10</v>
       </c>
       <c r="G91" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H91" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I91" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J91" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K91" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L91" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M91" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N91" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O91" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P91" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="92">
@@ -52224,34 +52224,34 @@
         <v>4</v>
       </c>
       <c r="G93" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H93" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I93" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J93" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K93" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L93" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M93" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N93" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O93" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P93" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="94">
@@ -52620,10 +52620,10 @@
         <v>0.899563</v>
       </c>
       <c r="M100" t="n">
-        <v>0.100437</v>
+        <v>0.094471</v>
       </c>
       <c r="N100" t="n">
-        <v>0.899563</v>
+        <v>0.905529</v>
       </c>
       <c r="O100" t="n">
         <v>0.100437</v>
@@ -52926,34 +52926,34 @@
         <v>4</v>
       </c>
       <c r="G106" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="H106" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="I106" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="J106" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="K106" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="L106" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="M106" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="N106" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
       <c r="O106" t="n">
-        <v>0.272919</v>
+        <v>0.243295</v>
       </c>
       <c r="P106" t="n">
-        <v>0.727081</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="107">
@@ -53574,34 +53574,34 @@
         <v>4</v>
       </c>
       <c r="G118" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H118" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I118" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J118" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K118" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L118" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M118" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N118" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O118" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P118" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="119">
@@ -53682,34 +53682,34 @@
         <v>4</v>
       </c>
       <c r="G120" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H120" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I120" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J120" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K120" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L120" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M120" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N120" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O120" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P120" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="121">
@@ -53736,34 +53736,34 @@
         <v>4</v>
       </c>
       <c r="G121" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="H121" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="I121" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="J121" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="K121" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="L121" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="M121" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="N121" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
       <c r="O121" t="n">
-        <v>0.308594</v>
+        <v>0.272919</v>
       </c>
       <c r="P121" t="n">
-        <v>0.691406</v>
+        <v>0.727081</v>
       </c>
     </row>
   </sheetData>
@@ -66494,10 +66494,10 @@
         <v>0.567096</v>
       </c>
       <c r="O20" t="n">
-        <v>0.431735</v>
+        <v>0.432904</v>
       </c>
       <c r="P20" t="n">
-        <v>0.568265</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="21">
@@ -66956,34 +66956,34 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H29" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I29" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J29" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K29" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L29" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M29" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N29" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O29" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="P29" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="30">
@@ -67388,34 +67388,34 @@
         <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="H37" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="I37" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="J37" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="K37" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="L37" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="M37" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="N37" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="O37" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="P37" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="38">
@@ -67442,34 +67442,34 @@
         <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H38" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I38" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J38" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K38" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L38" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M38" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N38" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O38" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P38" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="39">
@@ -68900,34 +68900,34 @@
         <v>3</v>
       </c>
       <c r="G65" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="H65" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="I65" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="J65" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="K65" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="L65" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="M65" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="N65" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
       <c r="O65" t="n">
-        <v>0.40884</v>
+        <v>0.361446</v>
       </c>
       <c r="P65" t="n">
-        <v>0.59116</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="66">
@@ -69266,34 +69266,34 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H4" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I4" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J4" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K4" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L4" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M4" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N4" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O4" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="P4" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="5">
@@ -69374,34 +69374,34 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="H6" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="I6" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="J6" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="K6" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="L6" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="M6" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="N6" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
       <c r="O6" t="n">
-        <v>0.361446</v>
+        <v>0.361011</v>
       </c>
       <c r="P6" t="n">
-        <v>0.638554</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="7">
@@ -69428,34 +69428,34 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O7" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P7" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="8">
@@ -69536,34 +69536,34 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O9" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P9" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="10">
@@ -69914,34 +69914,34 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="H16" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="I16" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="J16" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="K16" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="L16" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="M16" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="N16" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="O16" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="P16" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="17">
@@ -70022,34 +70022,34 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H18" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I18" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J18" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K18" t="n">
-        <v>0.361011</v>
+        <v>0.308594</v>
       </c>
       <c r="L18" t="n">
-        <v>0.638989</v>
+        <v>0.691406</v>
       </c>
       <c r="M18" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N18" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O18" t="n">
-        <v>0.361011</v>
+        <v>0.308594</v>
       </c>
       <c r="P18" t="n">
-        <v>0.638989</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="19">
@@ -70130,34 +70130,34 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="H20" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="I20" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="J20" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="K20" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="L20" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="M20" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N20" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O20" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="P20" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="21">
@@ -70298,16 +70298,16 @@
         <v>0.727081</v>
       </c>
       <c r="I23" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J23" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K23" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L23" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M23" t="n">
         <v>0.272919</v>
@@ -70616,34 +70616,34 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="H29" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="I29" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="J29" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="K29" t="n">
-        <v>0.243295</v>
+        <v>0.263158</v>
       </c>
       <c r="L29" t="n">
-        <v>0.756705</v>
+        <v>0.736842</v>
       </c>
       <c r="M29" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="N29" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="O29" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="P29" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="30">
@@ -70724,34 +70724,34 @@
         <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H31" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I31" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J31" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K31" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L31" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="M31" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="N31" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="O31" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="P31" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="32">
@@ -70802,10 +70802,10 @@
         <v>0.146853</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="P32" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="33">
@@ -70886,34 +70886,34 @@
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="H34" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="I34" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="J34" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="K34" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="L34" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="M34" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="N34" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
       <c r="O34" t="n">
-        <v>0.577889</v>
+        <v>0.659498</v>
       </c>
       <c r="P34" t="n">
-        <v>0.422111</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="35">
@@ -70994,34 +70994,34 @@
         <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H36" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J36" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L36" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N36" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P36" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="37">
@@ -71102,34 +71102,34 @@
         <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H38" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I38" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J38" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K38" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L38" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M38" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N38" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="O38" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="P38" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="39">
@@ -71210,34 +71210,34 @@
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="H40" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="I40" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="J40" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="K40" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="L40" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="M40" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="N40" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
       <c r="O40" t="n">
-        <v>0.260417</v>
+        <v>0.243295</v>
       </c>
       <c r="P40" t="n">
-        <v>0.739583</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="41">
@@ -71264,34 +71264,34 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="H41" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="I41" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="J41" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="K41" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="L41" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="M41" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="N41" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="O41" t="n">
-        <v>0.100437</v>
+        <v>0.137635</v>
       </c>
       <c r="P41" t="n">
-        <v>0.899563</v>
+        <v>0.862365</v>
       </c>
     </row>
     <row r="42">
@@ -71372,34 +71372,34 @@
         <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H43" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I43" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J43" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K43" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L43" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M43" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N43" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="O43" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="P43" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="44">
@@ -71426,34 +71426,34 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O44" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P44" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="45">
@@ -71534,34 +71534,34 @@
         <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="H46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="I46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="J46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="K46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="L46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="M46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="N46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
       <c r="O46" t="n">
-        <v>0.332008</v>
+        <v>0.308594</v>
       </c>
       <c r="P46" t="n">
-        <v>0.667992</v>
+        <v>0.691406</v>
       </c>
     </row>
   </sheetData>
@@ -72250,28 +72250,28 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H14" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I14" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J14" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K14" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L14" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="M14" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="N14" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="15">
@@ -72490,28 +72490,28 @@
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N19" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="20">
@@ -77088,10 +77088,10 @@
         <v>0.727081</v>
       </c>
       <c r="K8" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="L8" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="9">
@@ -77538,22 +77538,22 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H19" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I19" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J19" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="K19" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="L19" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
     <row r="20">
@@ -77832,22 +77832,22 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H26" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I26" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J26" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K26" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L26" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="27">
@@ -77916,22 +77916,22 @@
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="H28" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="I28" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="J28" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="K28" t="n">
-        <v>0.185358</v>
+        <v>0.230483</v>
       </c>
       <c r="L28" t="n">
-        <v>0.814642</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="29">
@@ -81782,34 +81782,34 @@
         <v>15</v>
       </c>
       <c r="G10" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="I10" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="K10" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="M10" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="O10" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="P10" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="11">
@@ -82106,34 +82106,34 @@
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H16" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I16" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J16" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K16" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L16" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M16" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N16" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O16" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="P16" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="17">
@@ -83726,34 +83726,34 @@
         <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="H46" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="I46" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="J46" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="K46" t="n">
-        <v>0.263158</v>
+        <v>0.272919</v>
       </c>
       <c r="L46" t="n">
-        <v>0.736842</v>
+        <v>0.727081</v>
       </c>
       <c r="M46" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="N46" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="O46" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="P46" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="47">
@@ -84320,34 +84320,34 @@
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="H57" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="I57" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="J57" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="K57" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="L57" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="M57" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="N57" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
       <c r="O57" t="n">
-        <v>0.100437</v>
+        <v>0.162214</v>
       </c>
       <c r="P57" t="n">
-        <v>0.899563</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="58">
@@ -85454,34 +85454,34 @@
         <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="I78" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="K78" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="M78" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N78" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
       <c r="O78" t="n">
-        <v>0.74269</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P78" t="n">
-        <v>0.25731</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="79">
@@ -85616,34 +85616,34 @@
         <v>6</v>
       </c>
       <c r="G81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="82">
@@ -85670,34 +85670,34 @@
         <v>4</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K82" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M82" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O82" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P82" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="83">
@@ -85832,34 +85832,34 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="H85" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="I85" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="J85" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="K85" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="L85" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="M85" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="N85" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
       <c r="O85" t="n">
-        <v>0.882667</v>
+        <v>0.853147</v>
       </c>
       <c r="P85" t="n">
-        <v>0.117333</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="86">
@@ -87916,28 +87916,28 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="H2" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="J2" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="K2" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="M2" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="N2" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
     </row>
     <row r="3">
@@ -88396,28 +88396,28 @@
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I12" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K12" t="n">
-        <v>0.853147</v>
+        <v>0.80786</v>
       </c>
       <c r="L12" t="n">
-        <v>0.146853</v>
+        <v>0.19214</v>
       </c>
       <c r="M12" t="n">
-        <v>0.853147</v>
+        <v>0.80786</v>
       </c>
       <c r="N12" t="n">
-        <v>0.146853</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="13">
@@ -88540,28 +88540,28 @@
         <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H15" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J15" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L15" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N15" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="16">
@@ -88588,28 +88588,28 @@
         <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I16" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K16" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M16" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="17">
@@ -88636,28 +88636,28 @@
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="H17" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="I17" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="J17" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="K17" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="L17" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
       <c r="M17" t="n">
-        <v>0.80786</v>
+        <v>0.769477</v>
       </c>
       <c r="N17" t="n">
-        <v>0.19214</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="18">
@@ -88684,28 +88684,28 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M18" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N18" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="19">
@@ -88732,28 +88732,28 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769477</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.230523</v>
+        <v>0.275862</v>
       </c>
       <c r="I19" t="n">
-        <v>0.769477</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.230523</v>
+        <v>0.275862</v>
       </c>
       <c r="K19" t="n">
-        <v>0.769477</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.230523</v>
+        <v>0.275862</v>
       </c>
       <c r="M19" t="n">
-        <v>0.769477</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.230523</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="20">
@@ -89068,28 +89068,28 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="H26" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="I26" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="J26" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="K26" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="L26" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
       <c r="M26" t="n">
-        <v>0.185358</v>
+        <v>0.162214</v>
       </c>
       <c r="N26" t="n">
-        <v>0.814642</v>
+        <v>0.837786</v>
       </c>
     </row>
     <row r="27">
@@ -90268,28 +90268,28 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="H51" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="I51" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="J51" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="K51" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="L51" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
       <c r="M51" t="n">
-        <v>0.243295</v>
+        <v>0.186916</v>
       </c>
       <c r="N51" t="n">
-        <v>0.756705</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="52">

--- a/conf_matchup_probs_2026.xlsx
+++ b/conf_matchup_probs_2026.xlsx
@@ -47,16 +47,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,21 +72,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,82 +447,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -564,34 +552,34 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H2" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I2" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J2" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K2" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L2" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M2" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N2" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O2" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P2" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="3">
@@ -726,34 +714,34 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="J5" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="K5" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="L5" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="M5" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="N5" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="O5" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="P5" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="6">
@@ -1170,22 +1158,22 @@
         <v>0.756705</v>
       </c>
       <c r="K13" t="n">
-        <v>0.243295</v>
+        <v>0.236967</v>
       </c>
       <c r="L13" t="n">
-        <v>0.756705</v>
+        <v>0.763033</v>
       </c>
       <c r="M13" t="n">
-        <v>0.243295</v>
+        <v>0.230483</v>
       </c>
       <c r="N13" t="n">
-        <v>0.756705</v>
+        <v>0.769517</v>
       </c>
       <c r="O13" t="n">
-        <v>0.243295</v>
+        <v>0.232448</v>
       </c>
       <c r="P13" t="n">
-        <v>0.756705</v>
+        <v>0.767552</v>
       </c>
     </row>
     <row r="14">
@@ -1212,34 +1200,34 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="H14" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
       <c r="I14" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="J14" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
       <c r="K14" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="L14" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
       <c r="M14" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="N14" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
       <c r="O14" t="n">
-        <v>0.186916</v>
+        <v>0.243295</v>
       </c>
       <c r="P14" t="n">
-        <v>0.813084</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="15">
@@ -1332,22 +1320,22 @@
         <v>0.230523</v>
       </c>
       <c r="K16" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L16" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M16" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N16" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O16" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P16" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="17">
@@ -1644,34 +1632,34 @@
         <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="H22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="I22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="J22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="K22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="L22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="M22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="N22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
       <c r="O22" t="n">
-        <v>0.769477</v>
+        <v>0.74269</v>
       </c>
       <c r="P22" t="n">
-        <v>0.230523</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="23">
@@ -1776,10 +1764,10 @@
         <v>0.321293</v>
       </c>
       <c r="O24" t="n">
-        <v>0.66564</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.33436</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="25">
@@ -1806,34 +1794,34 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="H25" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="I25" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="J25" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="K25" t="n">
-        <v>0.308594</v>
+        <v>0.361011</v>
       </c>
       <c r="L25" t="n">
-        <v>0.691406</v>
+        <v>0.638989</v>
       </c>
       <c r="M25" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N25" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O25" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P25" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="26">
@@ -2238,34 +2226,34 @@
         <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="H33" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="I33" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="J33" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="K33" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="L33" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="M33" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="N33" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="O33" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="P33" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="34">
@@ -2292,34 +2280,34 @@
         <v>13</v>
       </c>
       <c r="G34" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="H34" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="I34" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="J34" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="K34" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="L34" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="M34" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="N34" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="O34" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="P34" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="35">
@@ -2454,34 +2442,34 @@
         <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H37" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I37" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J37" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K37" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L37" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M37" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N37" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="O37" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="P37" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="38">
@@ -2508,34 +2496,34 @@
         <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>0.25</v>
+        <v>0.244898</v>
       </c>
       <c r="H38" t="n">
-        <v>0.75</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>0.25</v>
+        <v>0.244898</v>
       </c>
       <c r="J38" t="n">
-        <v>0.75</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>0.25</v>
+        <v>0.244898</v>
       </c>
       <c r="L38" t="n">
-        <v>0.75</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>0.25</v>
+        <v>0.244898</v>
       </c>
       <c r="N38" t="n">
-        <v>0.75</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="P38" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2994,34 +2982,34 @@
         <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H47" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I47" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J47" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K47" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L47" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M47" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="N47" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="O47" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="P47" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="48">
@@ -3480,34 +3468,34 @@
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="H56" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="I56" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="J56" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="K56" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="L56" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="M56" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="N56" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
       <c r="O56" t="n">
-        <v>0.272919</v>
+        <v>0.308594</v>
       </c>
       <c r="P56" t="n">
-        <v>0.727081</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="57">
@@ -3534,28 +3522,28 @@
         <v>12</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="H57" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="J57" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="L57" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="N57" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="O57" t="n">
         <v>0.8263470000000001</v>
@@ -3912,34 +3900,34 @@
         <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="H64" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="I64" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="J64" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="K64" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="L64" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="M64" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="N64" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
       <c r="O64" t="n">
-        <v>0.260417</v>
+        <v>0.272919</v>
       </c>
       <c r="P64" t="n">
-        <v>0.739583</v>
+        <v>0.727081</v>
       </c>
     </row>
     <row r="65">
@@ -4938,16 +4926,16 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="H83" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="I83" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="J83" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="K83" t="n">
         <v>0.40884</v>
@@ -4956,16 +4944,16 @@
         <v>0.59116</v>
       </c>
       <c r="M83" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="N83" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="O83" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="P83" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="84">
@@ -5100,34 +5088,34 @@
         <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H86" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I86" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J86" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K86" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L86" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M86" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="N86" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="O86" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="P86" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="87">
@@ -5262,34 +5250,34 @@
         <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H89" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I89" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J89" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K89" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L89" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M89" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N89" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="O89" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="P89" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="90">
@@ -5316,34 +5304,34 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H90" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I90" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J90" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K90" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L90" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M90" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N90" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="O90" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="P90" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="91">
@@ -5370,34 +5358,34 @@
         <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H91" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I91" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J91" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K91" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L91" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M91" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N91" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="O91" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="P91" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="92">
@@ -5469,92 +5457,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R3_D129</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R3_D129</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -5764,40 +5752,40 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="H5" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="I5" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="J5" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="K5" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="M5" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="N5" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="O5" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="P5" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.361446</v>
+        <v>0.40884</v>
       </c>
       <c r="R5" t="n">
-        <v>0.638554</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="6">
@@ -5884,22 +5872,22 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.853147</v>
+        <v>0.862069</v>
       </c>
       <c r="H7" t="n">
-        <v>0.146853</v>
+        <v>0.137931</v>
       </c>
       <c r="I7" t="n">
-        <v>0.853147</v>
+        <v>0.862069</v>
       </c>
       <c r="J7" t="n">
-        <v>0.146853</v>
+        <v>0.137931</v>
       </c>
       <c r="K7" t="n">
-        <v>0.853147</v>
+        <v>0.862069</v>
       </c>
       <c r="L7" t="n">
-        <v>0.146853</v>
+        <v>0.137931</v>
       </c>
       <c r="M7" t="n">
         <v>0.853147</v>
@@ -6004,34 +5992,34 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="M9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="O9" t="n">
-        <v>0.80786</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.19214</v>
+        <v>0.173653</v>
       </c>
       <c r="Q9" t="n">
         <v>0.80786</v>
@@ -6082,16 +6070,16 @@
         <v>0.275862</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.275862</v>
+        <v>0.321293</v>
       </c>
       <c r="Q10" t="n">
         <v>0.6787069999999999</v>
@@ -6724,40 +6712,40 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="H21" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="I21" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="J21" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="K21" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="L21" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="M21" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="N21" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="O21" t="n">
-        <v>0.100437</v>
+        <v>0.140351</v>
       </c>
       <c r="P21" t="n">
-        <v>0.899563</v>
+        <v>0.859649</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.100437</v>
+        <v>0.125</v>
       </c>
       <c r="R21" t="n">
-        <v>0.899563</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="22">
@@ -7162,10 +7150,10 @@
         <v>0.196581</v>
       </c>
       <c r="M28" t="n">
-        <v>0.783491</v>
+        <v>0.780929</v>
       </c>
       <c r="N28" t="n">
-        <v>0.216509</v>
+        <v>0.219071</v>
       </c>
       <c r="O28" t="n">
         <v>0.769477</v>
@@ -7204,22 +7192,22 @@
         <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H29" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I29" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J29" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K29" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L29" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M29" t="n">
         <v>0.162214</v>
@@ -7384,22 +7372,22 @@
         <v>13</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.665817</v>
       </c>
       <c r="H32" t="n">
-        <v>0.321293</v>
+        <v>0.334183</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.668762</v>
       </c>
       <c r="J32" t="n">
-        <v>0.321293</v>
+        <v>0.331238</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.668762</v>
       </c>
       <c r="L32" t="n">
-        <v>0.321293</v>
+        <v>0.331238</v>
       </c>
       <c r="M32" t="n">
         <v>0.6621</v>
@@ -7624,40 +7612,40 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="H36" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="I36" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="J36" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="K36" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="L36" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="M36" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="N36" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="O36" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="P36" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.186916</v>
+        <v>0.230483</v>
       </c>
       <c r="R36" t="n">
-        <v>0.813084</v>
+        <v>0.769517</v>
       </c>
     </row>
     <row r="37">
@@ -7894,10 +7882,10 @@
         <v>0.269565</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.7241379999999999</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="R40" t="n">
-        <v>0.275862</v>
+        <v>0.269565</v>
       </c>
     </row>
     <row r="41">
@@ -8242,10 +8230,10 @@
         <v>0.467095</v>
       </c>
       <c r="M46" t="n">
-        <v>0.532905</v>
+        <v>0.528181</v>
       </c>
       <c r="N46" t="n">
-        <v>0.467095</v>
+        <v>0.471819</v>
       </c>
       <c r="O46" t="n">
         <v>0.532905</v>
@@ -8830,16 +8818,16 @@
         <v>0.573034</v>
       </c>
       <c r="I56" t="n">
-        <v>0.428706</v>
+        <v>0.430037</v>
       </c>
       <c r="J56" t="n">
-        <v>0.571294</v>
+        <v>0.569963</v>
       </c>
       <c r="K56" t="n">
-        <v>0.428706</v>
+        <v>0.430037</v>
       </c>
       <c r="L56" t="n">
-        <v>0.571294</v>
+        <v>0.569963</v>
       </c>
       <c r="M56" t="n">
         <v>0.426966</v>
@@ -9148,10 +9136,10 @@
         <v>0.573034</v>
       </c>
       <c r="O61" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="P61" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
       <c r="Q61" t="n">
         <v>0.426966</v>
@@ -9424,40 +9412,40 @@
         <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H66" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="I66" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J66" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="K66" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L66" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="M66" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="N66" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="O66" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="P66" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="R66" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
     </row>
     <row r="67">
@@ -9484,34 +9472,34 @@
         <v>15</v>
       </c>
       <c r="G67" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I67" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K67" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M67" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N67" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O67" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P67" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="Q67" t="n">
         <v>0.8263470000000001</v>
@@ -9664,40 +9652,40 @@
         <v>18</v>
       </c>
       <c r="G70" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="H70" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="I70" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="J70" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="K70" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="L70" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="M70" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="N70" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="O70" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="P70" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.95</v>
+        <v>0.94152</v>
       </c>
       <c r="R70" t="n">
-        <v>0.05</v>
+        <v>0.05848</v>
       </c>
     </row>
     <row r="71">
@@ -10324,22 +10312,22 @@
         <v>16</v>
       </c>
       <c r="G81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="I81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="K81" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M81" t="n">
         <v>0.8263470000000001</v>
@@ -10864,40 +10852,40 @@
         <v>15</v>
       </c>
       <c r="G90" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H90" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I90" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J90" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K90" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L90" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M90" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N90" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O90" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="P90" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="R90" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="91">
@@ -12244,40 +12232,40 @@
         <v>7</v>
       </c>
       <c r="G113" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H113" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I113" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J113" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K113" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L113" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M113" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="N113" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="O113" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="P113" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="R113" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="114">
@@ -12724,40 +12712,40 @@
         <v>7</v>
       </c>
       <c r="G121" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="H121" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="I121" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="J121" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="K121" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="L121" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="M121" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="N121" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="O121" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="P121" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.243295</v>
+        <v>0.260417</v>
       </c>
       <c r="R121" t="n">
-        <v>0.756705</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="122">
@@ -14224,28 +14212,28 @@
         <v>13</v>
       </c>
       <c r="G146" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="H146" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="I146" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="J146" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="K146" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="L146" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="M146" t="n">
-        <v>0.40625</v>
+        <v>0.40884</v>
       </c>
       <c r="N146" t="n">
-        <v>0.59375</v>
+        <v>0.59116</v>
       </c>
       <c r="O146" t="n">
         <v>0.40625</v>
@@ -14584,22 +14572,22 @@
         <v>12</v>
       </c>
       <c r="G152" t="n">
-        <v>0.407485</v>
+        <v>0.40625</v>
       </c>
       <c r="H152" t="n">
-        <v>0.592515</v>
+        <v>0.59375</v>
       </c>
       <c r="I152" t="n">
-        <v>0.407485</v>
+        <v>0.40625</v>
       </c>
       <c r="J152" t="n">
-        <v>0.592515</v>
+        <v>0.59375</v>
       </c>
       <c r="K152" t="n">
-        <v>0.407485</v>
+        <v>0.40625</v>
       </c>
       <c r="L152" t="n">
-        <v>0.592515</v>
+        <v>0.59375</v>
       </c>
       <c r="M152" t="n">
         <v>0.40625</v>
@@ -14755,72 +14743,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -16185,82 +16173,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D123</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D123</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D124</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D124</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D126</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D126</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -16344,16 +16332,16 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I3" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J3" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K3" t="n">
         <v>0.556803</v>
@@ -16896,22 +16884,22 @@
         <v>0.567096</v>
       </c>
       <c r="K13" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L13" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M13" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N13" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="O13" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="P13" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="14">
@@ -18072,16 +18060,16 @@
         <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>0.594595</v>
+        <v>0.577889</v>
       </c>
       <c r="H35" t="n">
-        <v>0.405405</v>
+        <v>0.422111</v>
       </c>
       <c r="I35" t="n">
-        <v>0.594595</v>
+        <v>0.577889</v>
       </c>
       <c r="J35" t="n">
-        <v>0.405405</v>
+        <v>0.422111</v>
       </c>
       <c r="K35" t="n">
         <v>0.577889</v>
@@ -18666,34 +18654,34 @@
         <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H46" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I46" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J46" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K46" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L46" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M46" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N46" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="O46" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="P46" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="47">
@@ -19152,34 +19140,34 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="H55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="J55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="L55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="N55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.853147</v>
       </c>
       <c r="P55" t="n">
-        <v>0.173653</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="56">
@@ -19584,16 +19572,16 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H63" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I63" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J63" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K63" t="n">
         <v>0.272919</v>
@@ -19650,10 +19638,10 @@
         <v>0.573034</v>
       </c>
       <c r="K64" t="n">
-        <v>0.426966</v>
+        <v>0.415572</v>
       </c>
       <c r="L64" t="n">
-        <v>0.573034</v>
+        <v>0.5844279999999999</v>
       </c>
       <c r="M64" t="n">
         <v>0.426966</v>
@@ -20286,34 +20274,34 @@
         <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="H76" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="I76" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="J76" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="K76" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="L76" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="M76" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="N76" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
       <c r="O76" t="n">
-        <v>0.361011</v>
+        <v>0.332008</v>
       </c>
       <c r="P76" t="n">
-        <v>0.638989</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="77">
@@ -20493,72 +20481,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D128</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D128</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -21470,10 +21458,10 @@
         <v>0.340502</v>
       </c>
       <c r="M20" t="n">
-        <v>0.659498</v>
+        <v>0.636364</v>
       </c>
       <c r="N20" t="n">
-        <v>0.340502</v>
+        <v>0.363636</v>
       </c>
     </row>
     <row r="21">
@@ -21596,28 +21584,28 @@
         <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H23" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J23" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K23" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L23" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M23" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N23" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="24">
@@ -21752,10 +21740,10 @@
         <v>0.3379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M26" t="n">
         <v>0.659498</v>
@@ -21788,28 +21776,28 @@
         <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>0.269565</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="28">
@@ -22190,10 +22178,10 @@
         <v>0.638989</v>
       </c>
       <c r="M35" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N35" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="36">
@@ -22739,82 +22727,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D119</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D119</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D120</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D120</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D126</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D126</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -23708,34 +23696,34 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="O18" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="P18" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="19">
@@ -24194,34 +24182,34 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="H27" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="I27" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="J27" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="K27" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="L27" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="M27" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="N27" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
       <c r="O27" t="n">
-        <v>0.230483</v>
+        <v>0.186916</v>
       </c>
       <c r="P27" t="n">
-        <v>0.769517</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="28">
@@ -24626,16 +24614,16 @@
         <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="I35" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="K35" t="n">
         <v>0.243295</v>
@@ -25436,34 +25424,34 @@
         <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="I50" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="K50" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="M50" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="O50" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
     </row>
     <row r="51">
@@ -25805,52 +25793,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -25988,16 +25976,16 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
       <c r="I5" t="n">
-        <v>0.432904</v>
+        <v>0.426966</v>
       </c>
       <c r="J5" t="n">
-        <v>0.567096</v>
+        <v>0.573034</v>
       </c>
     </row>
     <row r="6">
@@ -26024,16 +26012,16 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.185358</v>
+        <v>0.243295</v>
       </c>
       <c r="H6" t="n">
-        <v>0.814642</v>
+        <v>0.756705</v>
       </c>
       <c r="I6" t="n">
-        <v>0.185358</v>
+        <v>0.243295</v>
       </c>
       <c r="J6" t="n">
-        <v>0.814642</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="7">
@@ -26060,16 +26048,16 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="H7" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
       <c r="I7" t="n">
-        <v>0.272919</v>
+        <v>0.283654</v>
       </c>
       <c r="J7" t="n">
-        <v>0.727081</v>
+        <v>0.716346</v>
       </c>
     </row>
   </sheetData>
@@ -26087,72 +26075,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D126</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D126</t>
         </is>
@@ -26524,10 +26512,10 @@
         <v>0.488449</v>
       </c>
       <c r="I9" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="J9" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="K9" t="n">
         <v>0.507576</v>
@@ -26914,10 +26902,10 @@
         <v>0.466565</v>
       </c>
       <c r="K17" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L17" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M17" t="n">
         <v>0.533435</v>
@@ -27532,22 +27520,22 @@
         <v>0.3379</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="31">
@@ -28162,16 +28150,16 @@
         <v>0.7551020000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="L43" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="N43" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="44">
@@ -28333,62 +28321,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -28556,10 +28544,10 @@
         <v>0.573034</v>
       </c>
       <c r="K5" t="n">
-        <v>0.426966</v>
+        <v>0.40884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.573034</v>
+        <v>0.59116</v>
       </c>
     </row>
     <row r="6">
@@ -29174,22 +29162,22 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H20" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I20" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J20" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K20" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L20" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="21">
@@ -29291,62 +29279,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -30510,22 +30498,22 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="H29" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="I29" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="J29" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
       <c r="K29" t="n">
-        <v>0.283654</v>
+        <v>0.272919</v>
       </c>
       <c r="L29" t="n">
-        <v>0.716346</v>
+        <v>0.727081</v>
       </c>
     </row>
   </sheetData>
@@ -30543,72 +30531,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>
@@ -30740,16 +30728,16 @@
         <v>0.08695700000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.92665</v>
+        <v>0.94152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07335</v>
+        <v>0.05848</v>
       </c>
       <c r="K4" t="n">
-        <v>0.92665</v>
+        <v>0.94152</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07335</v>
+        <v>0.05848</v>
       </c>
       <c r="M4" t="n">
         <v>0.94152</v>
@@ -30782,28 +30770,28 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H5" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I5" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J5" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K5" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="M5" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="N5" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="6">
@@ -33269,82 +33257,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -33482,28 +33470,28 @@
         <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.361429</v>
+        <v>0.361446</v>
       </c>
       <c r="H4" t="n">
-        <v>0.638571</v>
+        <v>0.638554</v>
       </c>
       <c r="I4" t="n">
-        <v>0.361429</v>
+        <v>0.361446</v>
       </c>
       <c r="J4" t="n">
-        <v>0.638571</v>
+        <v>0.638554</v>
       </c>
       <c r="K4" t="n">
-        <v>0.361429</v>
+        <v>0.361446</v>
       </c>
       <c r="L4" t="n">
-        <v>0.638571</v>
+        <v>0.638554</v>
       </c>
       <c r="M4" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N4" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O4" t="n">
         <v>0.361011</v>
@@ -34184,28 +34172,28 @@
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="O17" t="n">
         <v>0.659498</v>
@@ -35102,22 +35090,22 @@
         <v>15</v>
       </c>
       <c r="G34" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="J34" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="L34" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
       <c r="M34" t="n">
         <v>0.913043</v>
@@ -35768,10 +35756,10 @@
         <v>0.573034</v>
       </c>
       <c r="M46" t="n">
-        <v>0.424038</v>
+        <v>0.426966</v>
       </c>
       <c r="N46" t="n">
-        <v>0.575962</v>
+        <v>0.573034</v>
       </c>
       <c r="O46" t="n">
         <v>0.40884</v>
@@ -35966,34 +35954,34 @@
         <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H50" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I50" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J50" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K50" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L50" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M50" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N50" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="O50" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="P50" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="51">
@@ -37910,28 +37898,28 @@
         <v>11</v>
       </c>
       <c r="G86" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="H86" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="I86" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="J86" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="K86" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="L86" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="M86" t="n">
-        <v>0.308594</v>
+        <v>0.283654</v>
       </c>
       <c r="N86" t="n">
-        <v>0.691406</v>
+        <v>0.716346</v>
       </c>
       <c r="O86" t="n">
         <v>0.283654</v>
@@ -38414,16 +38402,16 @@
         <v>0.340502</v>
       </c>
       <c r="M95" t="n">
-        <v>0.636364</v>
+        <v>0.659498</v>
       </c>
       <c r="N95" t="n">
-        <v>0.363636</v>
+        <v>0.340502</v>
       </c>
       <c r="O95" t="n">
-        <v>0.636364</v>
+        <v>0.659498</v>
       </c>
       <c r="P95" t="n">
-        <v>0.363636</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="96">
@@ -39035,72 +39023,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -39466,22 +39454,22 @@
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.162214</v>
+        <v>0.140351</v>
       </c>
       <c r="H9" t="n">
-        <v>0.837786</v>
+        <v>0.859649</v>
       </c>
       <c r="I9" t="n">
-        <v>0.162214</v>
+        <v>0.140351</v>
       </c>
       <c r="J9" t="n">
-        <v>0.837786</v>
+        <v>0.859649</v>
       </c>
       <c r="K9" t="n">
-        <v>0.162214</v>
+        <v>0.140351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.837786</v>
+        <v>0.859649</v>
       </c>
       <c r="M9" t="n">
         <v>0.140351</v>
@@ -42289,62 +42277,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D121</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D121</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -43088,10 +43076,10 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.32283</v>
+        <v>0.332008</v>
       </c>
       <c r="H19" t="n">
-        <v>0.67717</v>
+        <v>0.667992</v>
       </c>
       <c r="I19" t="n">
         <v>0.308594</v>
@@ -43268,10 +43256,10 @@
         <v>0.3379</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6621</v>
+        <v>0.667076</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3379</v>
+        <v>0.332924</v>
       </c>
     </row>
     <row r="24">
@@ -43340,22 +43328,22 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="H25" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="I25" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="J25" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="K25" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="L25" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="26">
@@ -43382,22 +43370,22 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.40884</v>
+        <v>0.426966</v>
       </c>
       <c r="H26" t="n">
-        <v>0.59116</v>
+        <v>0.573034</v>
       </c>
       <c r="I26" t="n">
-        <v>0.40884</v>
+        <v>0.424208</v>
       </c>
       <c r="J26" t="n">
-        <v>0.59116</v>
+        <v>0.575792</v>
       </c>
       <c r="K26" t="n">
-        <v>0.40884</v>
+        <v>0.424208</v>
       </c>
       <c r="L26" t="n">
-        <v>0.59116</v>
+        <v>0.575792</v>
       </c>
     </row>
     <row r="27">
@@ -43541,72 +43529,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D121</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D121</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D122</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D122</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D123</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D123</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D124</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D124</t>
         </is>
@@ -43636,28 +43624,28 @@
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="H2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="I2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="J2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="K2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
       <c r="M2" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="N2" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="3">
@@ -44548,28 +44536,28 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="H21" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="J21" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="L21" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.260417</v>
+        <v>0.244898</v>
       </c>
       <c r="N21" t="n">
-        <v>0.739583</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="22">
@@ -44608,16 +44596,16 @@
         <v>0.59375</v>
       </c>
       <c r="K22" t="n">
-        <v>0.361446</v>
+        <v>0.4</v>
       </c>
       <c r="L22" t="n">
-        <v>0.638554</v>
+        <v>0.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0.361446</v>
+        <v>0.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.638554</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="23">
@@ -44692,28 +44680,28 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H24" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I24" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J24" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K24" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L24" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M24" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N24" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="25">
@@ -44971,72 +44959,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D120</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D120</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D122</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D122</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D128</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D128</t>
         </is>
@@ -45606,16 +45594,16 @@
         <v>0.727081</v>
       </c>
       <c r="K13" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="L13" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
       <c r="M13" t="n">
-        <v>0.272919</v>
+        <v>0.263158</v>
       </c>
       <c r="N13" t="n">
-        <v>0.727081</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="14">
@@ -46122,16 +46110,16 @@
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="H24" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="I24" t="n">
-        <v>0.659498</v>
+        <v>0.6621</v>
       </c>
       <c r="J24" t="n">
-        <v>0.340502</v>
+        <v>0.3379</v>
       </c>
       <c r="K24" t="n">
         <v>0.659498</v>
@@ -46278,16 +46266,16 @@
         <v>0.443197</v>
       </c>
       <c r="K27" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="L27" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
       <c r="M27" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="N27" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="28">
@@ -46326,16 +46314,16 @@
         <v>0.488449</v>
       </c>
       <c r="K28" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="L28" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
       <c r="M28" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="N28" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="29">
@@ -47217,82 +47205,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -47670,10 +47658,10 @@
         <v>0.25731</v>
       </c>
       <c r="O8" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
     </row>
     <row r="9">
@@ -48186,34 +48174,34 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="H18" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="I18" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="J18" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="K18" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="L18" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="M18" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="N18" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="O18" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="P18" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="19">
@@ -48348,34 +48336,34 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="H21" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="I21" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="J21" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="K21" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="L21" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="M21" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="N21" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
       <c r="O21" t="n">
-        <v>0.803419</v>
+        <v>0.769477</v>
       </c>
       <c r="P21" t="n">
-        <v>0.196581</v>
+        <v>0.230523</v>
       </c>
     </row>
     <row r="22">
@@ -49290,10 +49278,10 @@
         <v>0.423567</v>
       </c>
       <c r="O38" t="n">
-        <v>0.576433</v>
+        <v>0.556803</v>
       </c>
       <c r="P38" t="n">
-        <v>0.423567</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="39">
@@ -49770,10 +49758,10 @@
         <v>0.146853</v>
       </c>
       <c r="M47" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O47" t="n">
         <v>0.8263470000000001</v>
@@ -51318,34 +51306,34 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H76" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I76" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="J76" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="K76" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="L76" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="M76" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N76" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="O76" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="P76" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="77">
@@ -52020,34 +52008,34 @@
         <v>14</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="J89" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="K89" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="L89" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="M89" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N89" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O89" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="P89" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
     </row>
     <row r="90">
@@ -52290,16 +52278,16 @@
         <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>0.30839</v>
+        <v>0.308594</v>
       </c>
       <c r="H94" t="n">
-        <v>0.6916099999999999</v>
+        <v>0.691406</v>
       </c>
       <c r="I94" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J94" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K94" t="n">
         <v>0.283654</v>
@@ -52362,10 +52350,10 @@
         <v>0.7551020000000001</v>
       </c>
       <c r="M95" t="n">
-        <v>0.244898</v>
+        <v>0.243295</v>
       </c>
       <c r="N95" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.756705</v>
       </c>
       <c r="O95" t="n">
         <v>0.244898</v>
@@ -52452,34 +52440,34 @@
         <v>5</v>
       </c>
       <c r="G97" t="n">
-        <v>0.125</v>
+        <v>0.100437</v>
       </c>
       <c r="H97" t="n">
-        <v>0.875</v>
+        <v>0.899563</v>
       </c>
       <c r="I97" t="n">
-        <v>0.125</v>
+        <v>0.100437</v>
       </c>
       <c r="J97" t="n">
-        <v>0.875</v>
+        <v>0.899563</v>
       </c>
       <c r="K97" t="n">
-        <v>0.125</v>
+        <v>0.100437</v>
       </c>
       <c r="L97" t="n">
-        <v>0.875</v>
+        <v>0.899563</v>
       </c>
       <c r="M97" t="n">
-        <v>0.125</v>
+        <v>0.100437</v>
       </c>
       <c r="N97" t="n">
-        <v>0.875</v>
+        <v>0.899563</v>
       </c>
       <c r="O97" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="P97" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="98">
@@ -52506,22 +52494,22 @@
         <v>10</v>
       </c>
       <c r="G98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="H98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="J98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="L98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M98" t="n">
         <v>0.243295</v>
@@ -52530,10 +52518,10 @@
         <v>0.756705</v>
       </c>
       <c r="O98" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="P98" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
     </row>
     <row r="99">
@@ -52614,34 +52602,34 @@
         <v>4</v>
       </c>
       <c r="G100" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="H100" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="J100" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="K100" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="L100" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="M100" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="N100" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
       <c r="O100" t="n">
-        <v>0.07783</v>
+        <v>0.100437</v>
       </c>
       <c r="P100" t="n">
-        <v>0.92217</v>
+        <v>0.899563</v>
       </c>
     </row>
     <row r="101">
@@ -52938,34 +52926,34 @@
         <v>4</v>
       </c>
       <c r="G106" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="H106" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="J106" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="K106" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="L106" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="M106" t="n">
-        <v>0.243295</v>
+        <v>0.244898</v>
       </c>
       <c r="N106" t="n">
-        <v>0.756705</v>
+        <v>0.7551020000000001</v>
       </c>
       <c r="O106" t="n">
-        <v>0.243295</v>
+        <v>0.25</v>
       </c>
       <c r="P106" t="n">
-        <v>0.756705</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="107">
@@ -53793,72 +53781,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D123</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D123</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D124</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D124</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D125</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D125</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D126</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D126</t>
         </is>
@@ -54656,16 +54644,16 @@
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H18" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I18" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J18" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K18" t="n">
         <v>0.162214</v>
@@ -56039,72 +56027,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D125</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D125</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D126</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D126</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D127</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D127</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D128</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D128</t>
         </is>
@@ -56296,10 +56284,10 @@
         <v>0.492424</v>
       </c>
       <c r="M5" t="n">
-        <v>0.507576</v>
+        <v>0.511551</v>
       </c>
       <c r="N5" t="n">
-        <v>0.492424</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="6">
@@ -57469,72 +57457,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D121</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D121</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D122</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D122</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>
@@ -57678,10 +57666,10 @@
         <v>0.443197</v>
       </c>
       <c r="M4" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N4" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="5">
@@ -59283,102 +59271,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D120</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D120</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D121</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D121</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R3_D122</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R3_D122</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R4_D123</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R4_D123</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D124</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D124</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D125</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D125</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D126</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D126</t>
         </is>
@@ -60398,22 +60386,22 @@
         <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="H17" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="I17" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="J17" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="K17" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="L17" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
       <c r="M17" t="n">
         <v>0.882667</v>
@@ -60530,46 +60518,46 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="H19" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="J19" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="L19" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="N19" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="P19" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="R19" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.6621</v>
       </c>
       <c r="T19" t="n">
-        <v>0.321293</v>
+        <v>0.3379</v>
       </c>
     </row>
     <row r="20">
@@ -60944,28 +60932,28 @@
         <v>0.146853</v>
       </c>
       <c r="M25" t="n">
-        <v>0.862069</v>
+        <v>0.853147</v>
       </c>
       <c r="N25" t="n">
-        <v>0.137931</v>
+        <v>0.146853</v>
       </c>
       <c r="O25" t="n">
-        <v>0.862069</v>
+        <v>0.853147</v>
       </c>
       <c r="P25" t="n">
-        <v>0.137931</v>
+        <v>0.146853</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.862069</v>
+        <v>0.853147</v>
       </c>
       <c r="R25" t="n">
-        <v>0.137931</v>
+        <v>0.146853</v>
       </c>
       <c r="S25" t="n">
-        <v>0.862069</v>
+        <v>0.853147</v>
       </c>
       <c r="T25" t="n">
-        <v>0.137931</v>
+        <v>0.146853</v>
       </c>
     </row>
     <row r="26">
@@ -61028,10 +61016,10 @@
         <v>0.08695700000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>0.94152</v>
+        <v>0.913043</v>
       </c>
       <c r="T26" t="n">
-        <v>0.05848</v>
+        <v>0.08695700000000001</v>
       </c>
     </row>
     <row r="27">
@@ -61454,22 +61442,22 @@
         <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>0.361446</v>
+        <v>0.4</v>
       </c>
       <c r="H33" t="n">
-        <v>0.638554</v>
+        <v>0.6</v>
       </c>
       <c r="I33" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="J33" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="K33" t="n">
-        <v>0.361446</v>
+        <v>0.40625</v>
       </c>
       <c r="L33" t="n">
-        <v>0.638554</v>
+        <v>0.59375</v>
       </c>
       <c r="M33" t="n">
         <v>0.361446</v>
@@ -61520,46 +61508,46 @@
         <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="H34" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="I34" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="J34" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="K34" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="L34" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="M34" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="N34" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="O34" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="P34" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="R34" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
       <c r="S34" t="n">
-        <v>0.460746</v>
+        <v>0.432904</v>
       </c>
       <c r="T34" t="n">
-        <v>0.539254</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="35">
@@ -61784,22 +61772,22 @@
         <v>13</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="H38" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="J38" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7304349999999999</v>
+        <v>0.74269</v>
       </c>
       <c r="L38" t="n">
-        <v>0.269565</v>
+        <v>0.25731</v>
       </c>
       <c r="M38" t="n">
         <v>0.7304349999999999</v>
@@ -62246,46 +62234,46 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="H45" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="I45" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="J45" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="K45" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="L45" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="M45" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="N45" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="O45" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="P45" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="R45" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
       <c r="S45" t="n">
-        <v>0.263158</v>
+        <v>0.260417</v>
       </c>
       <c r="T45" t="n">
-        <v>0.736842</v>
+        <v>0.739583</v>
       </c>
     </row>
     <row r="46">
@@ -62540,16 +62528,16 @@
         <v>0.813084</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="R49" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="S49" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="T49" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="50">
@@ -62924,28 +62912,28 @@
         <v>0.492424</v>
       </c>
       <c r="M55" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="N55" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="O55" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="P55" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="R55" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
       <c r="S55" t="n">
-        <v>0.507576</v>
+        <v>0.460746</v>
       </c>
       <c r="T55" t="n">
-        <v>0.492424</v>
+        <v>0.539254</v>
       </c>
     </row>
     <row r="56">
@@ -63698,34 +63686,34 @@
         <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H67" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I67" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J67" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K67" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L67" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M67" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N67" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="O67" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="P67" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="Q67" t="n">
         <v>0.556803</v>
@@ -65405,82 +65393,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D126</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D126</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D127</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D127</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D128</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D128</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -67634,16 +67622,16 @@
         <v>0.340502</v>
       </c>
       <c r="M41" t="n">
+        <v>0.659498</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.340502</v>
+      </c>
+      <c r="O41" t="n">
         <v>0.636364</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>0.363636</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.594595</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0.405405</v>
       </c>
     </row>
     <row r="42">
@@ -67778,34 +67766,34 @@
         <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="H44" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="I44" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="J44" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="K44" t="n">
-        <v>0.659498</v>
+        <v>0.594595</v>
       </c>
       <c r="L44" t="n">
-        <v>0.340502</v>
+        <v>0.405405</v>
       </c>
       <c r="M44" t="n">
-        <v>0.659498</v>
+        <v>0.577889</v>
       </c>
       <c r="N44" t="n">
-        <v>0.340502</v>
+        <v>0.422111</v>
       </c>
       <c r="O44" t="n">
-        <v>0.594595</v>
+        <v>0.577889</v>
       </c>
       <c r="P44" t="n">
-        <v>0.405405</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="45">
@@ -68588,34 +68576,34 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H59" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I59" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J59" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K59" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L59" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M59" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N59" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O59" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P59" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="60">
@@ -69065,82 +69053,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D131</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D132</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D132</t>
         </is>
@@ -69602,34 +69590,34 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="H10" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="I10" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="J10" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="K10" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L10" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M10" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N10" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="O10" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="P10" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="11">
@@ -69722,22 +69710,22 @@
         <v>0.467095</v>
       </c>
       <c r="K12" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M12" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N12" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="O12" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="P12" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="13">
@@ -69764,34 +69752,34 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H13" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I13" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J13" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K13" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L13" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M13" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N13" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="O13" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="P13" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="14">
@@ -70034,34 +70022,34 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H18" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I18" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J18" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K18" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L18" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M18" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N18" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O18" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P18" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="19">
@@ -70088,34 +70076,34 @@
         <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="H19" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="I19" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="J19" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="K19" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="L19" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="M19" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="N19" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
       <c r="O19" t="n">
-        <v>0.533435</v>
+        <v>0.532905</v>
       </c>
       <c r="P19" t="n">
-        <v>0.466565</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="20">
@@ -70142,34 +70130,34 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H20" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I20" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J20" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K20" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L20" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M20" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N20" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="O20" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="P20" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="21">
@@ -70358,34 +70346,34 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="M24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="N24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="O24" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="P24" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="25">
@@ -70412,34 +70400,34 @@
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="H25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="I25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="J25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="K25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="L25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="M25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="N25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
       <c r="O25" t="n">
-        <v>0.332008</v>
+        <v>0.361011</v>
       </c>
       <c r="P25" t="n">
-        <v>0.667992</v>
+        <v>0.638989</v>
       </c>
     </row>
     <row r="26">
@@ -70520,28 +70508,28 @@
         <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="H27" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="I27" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="J27" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="K27" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="L27" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="M27" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="N27" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="O27" t="n">
         <v>0.576433</v>
@@ -70736,34 +70724,34 @@
         <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H31" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I31" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J31" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K31" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L31" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M31" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N31" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O31" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P31" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="32">
@@ -70814,10 +70802,10 @@
         <v>0.117333</v>
       </c>
       <c r="O32" t="n">
-        <v>0.882667</v>
+        <v>0.862069</v>
       </c>
       <c r="P32" t="n">
-        <v>0.117333</v>
+        <v>0.137931</v>
       </c>
     </row>
     <row r="33">
@@ -71024,10 +71012,10 @@
         <v>0.275862</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6787069999999999</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.321293</v>
+        <v>0.275862</v>
       </c>
       <c r="O36" t="n">
         <v>0.6787069999999999</v>
@@ -71240,10 +71228,10 @@
         <v>0.756705</v>
       </c>
       <c r="M40" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="N40" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="O40" t="n">
         <v>0.243295</v>
@@ -71384,28 +71372,28 @@
         <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>0.18448</v>
+        <v>0.185358</v>
       </c>
       <c r="H43" t="n">
-        <v>0.81552</v>
+        <v>0.814642</v>
       </c>
       <c r="I43" t="n">
-        <v>0.18448</v>
+        <v>0.185358</v>
       </c>
       <c r="J43" t="n">
-        <v>0.81552</v>
+        <v>0.814642</v>
       </c>
       <c r="K43" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="L43" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="M43" t="n">
-        <v>0.162214</v>
+        <v>0.185358</v>
       </c>
       <c r="N43" t="n">
-        <v>0.837786</v>
+        <v>0.814642</v>
       </c>
       <c r="O43" t="n">
         <v>0.185358</v>
@@ -71591,72 +71579,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -72166,22 +72154,22 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
+        <v>0.361446</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.638554</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.361446</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.638554</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.4</v>
       </c>
-      <c r="H12" t="n">
+      <c r="L12" t="n">
         <v>0.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.40625</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.59375</v>
       </c>
       <c r="M12" t="n">
         <v>0.361446</v>
@@ -72685,92 +72673,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R3_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R3_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D125</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D126</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D126</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D127</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D127</t>
         </is>
@@ -73400,10 +73388,10 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.952055</v>
+        <v>0.971631</v>
       </c>
       <c r="H12" t="n">
-        <v>0.047945</v>
+        <v>0.028369</v>
       </c>
       <c r="I12" t="n">
         <v>0.971631</v>
@@ -74720,10 +74708,10 @@
         <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>0.74269</v>
+        <v>0.7304349999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0.25731</v>
+        <v>0.269565</v>
       </c>
       <c r="I34" t="n">
         <v>0.74269</v>
@@ -75158,22 +75146,22 @@
         <v>0.59116</v>
       </c>
       <c r="M41" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="N41" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="O41" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="P41" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="R41" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="42">
@@ -75680,40 +75668,40 @@
         <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H50" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I50" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J50" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K50" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L50" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M50" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N50" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O50" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P50" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="R50" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="51">
@@ -75800,40 +75788,40 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="H52" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="I52" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="J52" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="K52" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="L52" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="M52" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="N52" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="O52" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="P52" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.308594</v>
+        <v>0.332008</v>
       </c>
       <c r="R52" t="n">
-        <v>0.691406</v>
+        <v>0.667992</v>
       </c>
     </row>
     <row r="53">
@@ -75920,40 +75908,40 @@
         <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>0.036697</v>
+        <v>0.045455</v>
       </c>
       <c r="H54" t="n">
-        <v>0.963303</v>
+        <v>0.954545</v>
       </c>
       <c r="I54" t="n">
-        <v>0.036697</v>
+        <v>0.040484</v>
       </c>
       <c r="J54" t="n">
-        <v>0.963303</v>
+        <v>0.959516</v>
       </c>
       <c r="K54" t="n">
-        <v>0.036697</v>
+        <v>0.040484</v>
       </c>
       <c r="L54" t="n">
-        <v>0.963303</v>
+        <v>0.959516</v>
       </c>
       <c r="M54" t="n">
-        <v>0.036697</v>
+        <v>0.040484</v>
       </c>
       <c r="N54" t="n">
-        <v>0.963303</v>
+        <v>0.959516</v>
       </c>
       <c r="O54" t="n">
-        <v>0.036697</v>
+        <v>0.040484</v>
       </c>
       <c r="P54" t="n">
-        <v>0.963303</v>
+        <v>0.959516</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.036697</v>
+        <v>0.03946</v>
       </c>
       <c r="R54" t="n">
-        <v>0.963303</v>
+        <v>0.9605399999999999</v>
       </c>
     </row>
     <row r="55">
@@ -76100,40 +76088,40 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H57" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I57" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J57" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K57" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L57" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M57" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N57" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="O57" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="P57" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="R57" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="58">
@@ -76751,62 +76739,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D124</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D124</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D127</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D127</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -77172,16 +77160,16 @@
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H10" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I10" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J10" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K10" t="n">
         <v>0.511551</v>
@@ -77298,16 +77286,16 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.140351</v>
+        <v>0.125</v>
       </c>
       <c r="H13" t="n">
-        <v>0.859649</v>
+        <v>0.875</v>
       </c>
       <c r="I13" t="n">
-        <v>0.140351</v>
+        <v>0.109695</v>
       </c>
       <c r="J13" t="n">
-        <v>0.859649</v>
+        <v>0.890305</v>
       </c>
       <c r="K13" t="n">
         <v>0.100437</v>
@@ -77508,22 +77496,22 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="H18" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="I18" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="J18" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
       <c r="K18" t="n">
-        <v>0.186916</v>
+        <v>0.185358</v>
       </c>
       <c r="L18" t="n">
-        <v>0.813084</v>
+        <v>0.814642</v>
       </c>
     </row>
     <row r="19">
@@ -77640,10 +77628,10 @@
         <v>0.573034</v>
       </c>
       <c r="I21" t="n">
-        <v>0.432904</v>
+        <v>0.432358</v>
       </c>
       <c r="J21" t="n">
-        <v>0.567096</v>
+        <v>0.567642</v>
       </c>
       <c r="K21" t="n">
         <v>0.426966</v>
@@ -77802,16 +77790,16 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="H25" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="I25" t="n">
-        <v>0.140351</v>
+        <v>0.100437</v>
       </c>
       <c r="J25" t="n">
-        <v>0.859649</v>
+        <v>0.899563</v>
       </c>
       <c r="K25" t="n">
         <v>0.100437</v>
@@ -78003,72 +77991,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D121</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D121</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>
@@ -78290,28 +78278,28 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="H6" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="I6" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="J6" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="K6" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="L6" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
       <c r="M6" t="n">
-        <v>0.576433</v>
+        <v>0.577889</v>
       </c>
       <c r="N6" t="n">
-        <v>0.423567</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="7">
@@ -78866,28 +78854,28 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="H18" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="J18" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="L18" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8263470000000001</v>
+        <v>0.80786</v>
       </c>
       <c r="N18" t="n">
-        <v>0.173653</v>
+        <v>0.19214</v>
       </c>
     </row>
     <row r="19">
@@ -79154,28 +79142,28 @@
         <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H24" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I24" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J24" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K24" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L24" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M24" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N24" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="25">
@@ -79490,28 +79478,28 @@
         <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="H31" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="I31" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="J31" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="K31" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="L31" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
       <c r="M31" t="n">
-        <v>0.532905</v>
+        <v>0.511551</v>
       </c>
       <c r="N31" t="n">
-        <v>0.467095</v>
+        <v>0.488449</v>
       </c>
     </row>
     <row r="32">
@@ -80018,28 +80006,28 @@
         <v>10</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6399</v>
+        <v>0.577889</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3601</v>
+        <v>0.422111</v>
       </c>
       <c r="I42" t="n">
-        <v>0.636364</v>
+        <v>0.577889</v>
       </c>
       <c r="J42" t="n">
-        <v>0.363636</v>
+        <v>0.422111</v>
       </c>
       <c r="K42" t="n">
-        <v>0.636364</v>
+        <v>0.577889</v>
       </c>
       <c r="L42" t="n">
-        <v>0.363636</v>
+        <v>0.422111</v>
       </c>
       <c r="M42" t="n">
-        <v>0.636364</v>
+        <v>0.577889</v>
       </c>
       <c r="N42" t="n">
-        <v>0.363636</v>
+        <v>0.422111</v>
       </c>
     </row>
     <row r="43">
@@ -80258,10 +80246,10 @@
         <v>11</v>
       </c>
       <c r="G47" t="n">
-        <v>0.803419</v>
+        <v>0.771621</v>
       </c>
       <c r="H47" t="n">
-        <v>0.196581</v>
+        <v>0.228379</v>
       </c>
       <c r="I47" t="n">
         <v>0.803419</v>
@@ -80738,28 +80726,28 @@
         <v>6</v>
       </c>
       <c r="G57" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="H57" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
       <c r="I57" t="n">
-        <v>0.361011</v>
+        <v>0.361333</v>
       </c>
       <c r="J57" t="n">
-        <v>0.638989</v>
+        <v>0.638667</v>
       </c>
       <c r="K57" t="n">
-        <v>0.361011</v>
+        <v>0.361333</v>
       </c>
       <c r="L57" t="n">
-        <v>0.638989</v>
+        <v>0.638667</v>
       </c>
       <c r="M57" t="n">
-        <v>0.361011</v>
+        <v>0.361446</v>
       </c>
       <c r="N57" t="n">
-        <v>0.638989</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="58">
@@ -81257,82 +81245,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D127</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D127</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R2_D128</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R2_D128</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -82226,34 +82214,34 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="H18" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="I18" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="J18" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="K18" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="L18" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="M18" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="N18" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
       <c r="O18" t="n">
-        <v>0.230483</v>
+        <v>0.243295</v>
       </c>
       <c r="P18" t="n">
-        <v>0.769517</v>
+        <v>0.756705</v>
       </c>
     </row>
     <row r="19">
@@ -82604,34 +82592,34 @@
         <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="H25" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="I25" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="J25" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="K25" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="L25" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="M25" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="N25" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
       <c r="O25" t="n">
-        <v>0.511551</v>
+        <v>0.507576</v>
       </c>
       <c r="P25" t="n">
-        <v>0.488449</v>
+        <v>0.492424</v>
       </c>
     </row>
     <row r="26">
@@ -84332,28 +84320,28 @@
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>0.162214</v>
+        <v>0.140351</v>
       </c>
       <c r="H57" t="n">
-        <v>0.837786</v>
+        <v>0.859649</v>
       </c>
       <c r="I57" t="n">
-        <v>0.162214</v>
+        <v>0.140351</v>
       </c>
       <c r="J57" t="n">
-        <v>0.837786</v>
+        <v>0.859649</v>
       </c>
       <c r="K57" t="n">
-        <v>0.162214</v>
+        <v>0.140351</v>
       </c>
       <c r="L57" t="n">
-        <v>0.837786</v>
+        <v>0.859649</v>
       </c>
       <c r="M57" t="n">
-        <v>0.162214</v>
+        <v>0.140351</v>
       </c>
       <c r="N57" t="n">
-        <v>0.837786</v>
+        <v>0.859649</v>
       </c>
       <c r="O57" t="n">
         <v>0.140351</v>
@@ -86114,34 +86102,34 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="H90" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="K90" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="L90" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N90" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
       <c r="O90" t="n">
-        <v>0.6621</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.3379</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="91">
@@ -86612,22 +86600,22 @@
         <v>0.146853</v>
       </c>
       <c r="K99" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="L99" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="M99" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="N99" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
       <c r="O99" t="n">
-        <v>0.853147</v>
+        <v>0.8263470000000001</v>
       </c>
       <c r="P99" t="n">
-        <v>0.146853</v>
+        <v>0.173653</v>
       </c>
     </row>
     <row r="100">
@@ -87833,72 +87821,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D128</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D128</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D129</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D129</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D130</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D130</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D131</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D131</t>
         </is>
@@ -90244,16 +90232,16 @@
         <v>0.443197</v>
       </c>
       <c r="K50" t="n">
-        <v>0.533435</v>
+        <v>0.540246</v>
       </c>
       <c r="L50" t="n">
-        <v>0.466565</v>
+        <v>0.459754</v>
       </c>
       <c r="M50" t="n">
-        <v>0.533435</v>
+        <v>0.556803</v>
       </c>
       <c r="N50" t="n">
-        <v>0.466565</v>
+        <v>0.443197</v>
       </c>
     </row>
     <row r="51">
@@ -90328,28 +90316,28 @@
         <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>0.40625</v>
+        <v>0.4</v>
       </c>
       <c r="H52" t="n">
-        <v>0.59375</v>
+        <v>0.6</v>
       </c>
       <c r="I52" t="n">
-        <v>0.40625</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
-        <v>0.59375</v>
+        <v>0.6</v>
       </c>
       <c r="K52" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="L52" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
       <c r="M52" t="n">
-        <v>0.40625</v>
+        <v>0.361446</v>
       </c>
       <c r="N52" t="n">
-        <v>0.59375</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="53">
@@ -90394,10 +90382,10 @@
         <v>0.321293</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6752320000000001</v>
+        <v>0.6787069999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>0.324768</v>
+        <v>0.321293</v>
       </c>
     </row>
     <row r="54">
@@ -90559,72 +90547,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D124</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D124</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D125</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D125</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D127</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D127</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D128</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D128</t>
         </is>
@@ -90846,28 +90834,28 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="H6" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="I6" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="J6" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="K6" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="L6" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
       <c r="M6" t="n">
-        <v>0.185358</v>
+        <v>0.186916</v>
       </c>
       <c r="N6" t="n">
-        <v>0.814642</v>
+        <v>0.813084</v>
       </c>
     </row>
     <row r="7">
@@ -90894,10 +90882,10 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.230483</v>
+        <v>0.23888</v>
       </c>
       <c r="H7" t="n">
-        <v>0.769517</v>
+        <v>0.76112</v>
       </c>
       <c r="I7" t="n">
         <v>0.230483</v>
@@ -91278,10 +91266,10 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.40884</v>
+        <v>0.40625</v>
       </c>
       <c r="H15" t="n">
-        <v>0.59116</v>
+        <v>0.59375</v>
       </c>
       <c r="I15" t="n">
         <v>0.40625</v>
@@ -91716,22 +91704,22 @@
         <v>0.466565</v>
       </c>
       <c r="I24" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="J24" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="K24" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="L24" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
       <c r="M24" t="n">
-        <v>0.532905</v>
+        <v>0.533435</v>
       </c>
       <c r="N24" t="n">
-        <v>0.467095</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="25">
@@ -91998,28 +91986,28 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="H30" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="I30" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="J30" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="K30" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="L30" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
       <c r="M30" t="n">
-        <v>0.283654</v>
+        <v>0.308594</v>
       </c>
       <c r="N30" t="n">
-        <v>0.716346</v>
+        <v>0.691406</v>
       </c>
     </row>
     <row r="31">
@@ -92238,28 +92226,28 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4</v>
+        <v>0.361446</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6</v>
+        <v>0.638554</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>0.361446</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6</v>
+        <v>0.638554</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4</v>
+        <v>0.361446</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6</v>
+        <v>0.638554</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4</v>
+        <v>0.361446</v>
       </c>
       <c r="N35" t="n">
-        <v>0.6</v>
+        <v>0.638554</v>
       </c>
     </row>
     <row r="36">
@@ -92334,10 +92322,10 @@
         <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="H37" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="I37" t="n">
         <v>0.511551</v>
@@ -92436,22 +92424,22 @@
         <v>0.467095</v>
       </c>
       <c r="I39" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="J39" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="K39" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="L39" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
       <c r="M39" t="n">
-        <v>0.511551</v>
+        <v>0.532905</v>
       </c>
       <c r="N39" t="n">
-        <v>0.488449</v>
+        <v>0.467095</v>
       </c>
     </row>
     <row r="40">
@@ -92805,72 +92793,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team1_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team1_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>team1_seed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>team2_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>team2_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>team2_seed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prob_team1_wins_R1_D122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>prob_team2_wins_R1_D122</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob_team1_wins_QF_D123</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>prob_team2_wins_QF_D123</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob_team1_wins_SF_D124</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prob_team2_wins_SF_D124</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>prob_team1_wins_Final_D125</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>prob_team2_wins_Final_D125</t>
         </is>
@@ -93044,28 +93032,28 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="H5" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="I5" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="J5" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="K5" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
       <c r="M5" t="n">
-        <v>0.556803</v>
+        <v>0.533435</v>
       </c>
       <c r="N5" t="n">
-        <v>0.443197</v>
+        <v>0.466565</v>
       </c>
     </row>
     <row r="6">
@@ -94148,28 +94136,28 @@
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.431179</v>
+        <v>0.432904</v>
       </c>
       <c r="H28" t="n">
-        <v>0.568821</v>
+        <v>0.567096</v>
       </c>
       <c r="I28" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="J28" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="K28" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="L28" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
       <c r="M28" t="n">
-        <v>0.426966</v>
+        <v>0.432904</v>
       </c>
       <c r="N28" t="n">
-        <v>0.573034</v>
+        <v>0.567096</v>
       </c>
     </row>
     <row r="29">
@@ -94196,28 +94184,28 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="H29" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="I29" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="J29" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="K29" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="L29" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
       <c r="M29" t="n">
-        <v>0.556803</v>
+        <v>0.576433</v>
       </c>
       <c r="N29" t="n">
-        <v>0.443197</v>
+        <v>0.423567</v>
       </c>
     </row>
     <row r="30">
@@ -94346,22 +94334,22 @@
         <v>0.3379</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6621</v>
+        <v>0.659498</v>
       </c>
       <c r="N32" t="n">
-        <v>0.3379</v>
+        <v>0.340502</v>
       </c>
     </row>
     <row r="33">
